--- a/research/traditional_assets/database/data/spain/spain_oilfield_svcs_equip.xlsx
+++ b/research/traditional_assets/database/data/spain/spain_oilfield_svcs_equip.xlsx
@@ -588,28 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.09420000000000001</v>
-      </c>
-      <c r="F2">
-        <v>-0.01</v>
+        <v>-0.0767</v>
       </c>
       <c r="G2">
-        <v>0.01731817903314748</v>
+        <v>-0.05071395402832598</v>
       </c>
       <c r="H2">
-        <v>0.01632865633233258</v>
+        <v>-0.05273392152310193</v>
       </c>
       <c r="I2">
-        <v>-0.05327492187978678</v>
+        <v>-0.01451126073833295</v>
       </c>
       <c r="J2">
-        <v>-0.05327492187978678</v>
+        <v>-0.01451126073833295</v>
       </c>
       <c r="K2">
-        <v>-176.2</v>
+        <v>-81.59999999999999</v>
       </c>
       <c r="L2">
-        <v>-0.05397953556767355</v>
+        <v>-0.02368237752495937</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -633,73 +630,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>801.9</v>
+        <v>930.1</v>
       </c>
       <c r="V2">
-        <v>1.8984375</v>
+        <v>1.779074215761286</v>
       </c>
       <c r="W2">
-        <v>-0.5373589508996646</v>
+        <v>-0.5375494071146244</v>
       </c>
       <c r="X2">
-        <v>0.1695986662598678</v>
+        <v>0.2139536949688168</v>
       </c>
       <c r="Y2">
-        <v>-0.7069576171595323</v>
+        <v>-0.7515031020834413</v>
       </c>
       <c r="Z2">
-        <v>15.09805735430157</v>
+        <v>13.36021713842575</v>
       </c>
       <c r="AA2">
-        <v>-0.8043478260869564</v>
+        <v>-0.1938735944164405</v>
       </c>
       <c r="AB2">
-        <v>0.07511613112880952</v>
+        <v>0.1170827542125021</v>
       </c>
       <c r="AC2">
-        <v>-0.879463957215766</v>
+        <v>-0.3109563486289426</v>
       </c>
       <c r="AD2">
-        <v>908</v>
+        <v>828</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>908</v>
+        <v>828</v>
       </c>
       <c r="AG2">
-        <v>106.1</v>
+        <v>-102.1</v>
       </c>
       <c r="AH2">
-        <v>0.682501503307276</v>
+        <v>0.6129700917974534</v>
       </c>
       <c r="AI2">
-        <v>0.8474892663804368</v>
+        <v>0.778049238864875</v>
       </c>
       <c r="AJ2">
-        <v>0.2007568590350048</v>
+        <v>-0.2426907535060614</v>
       </c>
       <c r="AK2">
-        <v>0.3936920222634509</v>
+        <v>-0.7613721103653993</v>
       </c>
       <c r="AL2">
-        <v>19.3</v>
+        <v>23</v>
       </c>
       <c r="AM2">
-        <v>15.3</v>
+        <v>20.41</v>
       </c>
       <c r="AN2">
-        <v>-5.68922305764411</v>
+        <v>-19.07834101382489</v>
       </c>
       <c r="AO2">
-        <v>-9.010362694300518</v>
+        <v>-2.173913043478261</v>
       </c>
       <c r="AP2">
-        <v>-0.6647869674185465</v>
+        <v>2.352534562211982</v>
       </c>
       <c r="AQ2">
-        <v>-11.36601307189543</v>
+        <v>-2.449779519843214</v>
       </c>
     </row>
     <row r="3">
@@ -719,28 +716,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.09420000000000001</v>
-      </c>
-      <c r="F3">
-        <v>-0.01</v>
+        <v>-0.0767</v>
       </c>
       <c r="G3">
-        <v>0.01731817903314748</v>
+        <v>-0.05071395402832598</v>
       </c>
       <c r="H3">
-        <v>0.01632865633233258</v>
+        <v>-0.05273392152310193</v>
       </c>
       <c r="I3">
-        <v>-0.05327492187978678</v>
+        <v>-0.01451126073833295</v>
       </c>
       <c r="J3">
-        <v>-0.05327492187978678</v>
+        <v>-0.01451126073833295</v>
       </c>
       <c r="K3">
-        <v>-176.2</v>
+        <v>-81.59999999999999</v>
       </c>
       <c r="L3">
-        <v>-0.05397953556767355</v>
+        <v>-0.02368237752495937</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -764,73 +758,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>801.9</v>
+        <v>930.1</v>
       </c>
       <c r="V3">
-        <v>1.8984375</v>
+        <v>1.779074215761286</v>
       </c>
       <c r="W3">
-        <v>-0.5373589508996646</v>
+        <v>-0.5375494071146244</v>
       </c>
       <c r="X3">
-        <v>0.1695986662598678</v>
+        <v>0.2139536949688168</v>
       </c>
       <c r="Y3">
-        <v>-0.7069576171595323</v>
+        <v>-0.7515031020834413</v>
       </c>
       <c r="Z3">
-        <v>15.09805735430157</v>
+        <v>13.36021713842575</v>
       </c>
       <c r="AA3">
-        <v>-0.8043478260869564</v>
+        <v>-0.1938735944164405</v>
       </c>
       <c r="AB3">
-        <v>0.07511613112880952</v>
+        <v>0.1170827542125021</v>
       </c>
       <c r="AC3">
-        <v>-0.879463957215766</v>
+        <v>-0.3109563486289426</v>
       </c>
       <c r="AD3">
-        <v>908</v>
+        <v>828</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>908</v>
+        <v>828</v>
       </c>
       <c r="AG3">
-        <v>106.1</v>
+        <v>-102.1</v>
       </c>
       <c r="AH3">
-        <v>0.682501503307276</v>
+        <v>0.6129700917974534</v>
       </c>
       <c r="AI3">
-        <v>0.8474892663804368</v>
+        <v>0.778049238864875</v>
       </c>
       <c r="AJ3">
-        <v>0.2007568590350048</v>
+        <v>-0.2426907535060614</v>
       </c>
       <c r="AK3">
-        <v>0.3936920222634509</v>
+        <v>-0.7613721103653993</v>
       </c>
       <c r="AL3">
-        <v>19.3</v>
+        <v>23</v>
       </c>
       <c r="AM3">
-        <v>15.3</v>
+        <v>20.41</v>
       </c>
       <c r="AN3">
-        <v>-5.68922305764411</v>
+        <v>-19.07834101382489</v>
       </c>
       <c r="AO3">
-        <v>-9.010362694300518</v>
+        <v>-2.173913043478261</v>
       </c>
       <c r="AP3">
-        <v>-0.6647869674185465</v>
+        <v>2.352534562211982</v>
       </c>
       <c r="AQ3">
-        <v>-11.36601307189543</v>
+        <v>-2.449779519843214</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/spain/spain_oilfield_svcs_equip.xlsx
+++ b/research/traditional_assets/database/data/spain/spain_oilfield_svcs_equip.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="bme_tre" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,25 +590,31 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0767</v>
+        <v>0.01</v>
+      </c>
+      <c r="E2">
+        <v>0.6890000000000001</v>
+      </c>
+      <c r="F2">
+        <v>0.028</v>
       </c>
       <c r="G2">
-        <v>-0.05071395402832598</v>
+        <v>0.003606411398040962</v>
       </c>
       <c r="H2">
-        <v>-0.05273392152310193</v>
+        <v>0.002064275884400551</v>
       </c>
       <c r="I2">
-        <v>-0.01451126073833295</v>
+        <v>0.03268436816967538</v>
       </c>
       <c r="J2">
-        <v>-0.01451126073833295</v>
+        <v>0.01720389036868204</v>
       </c>
       <c r="K2">
-        <v>-81.59999999999999</v>
+        <v>57.1</v>
       </c>
       <c r="L2">
-        <v>-0.02368237752495937</v>
+        <v>0.01155589735286975</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -615,7 +623,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,79 +632,79 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>930.1</v>
+        <v>1061.6</v>
       </c>
       <c r="V2">
-        <v>1.779074215761286</v>
+        <v>1.473216763807938</v>
       </c>
       <c r="W2">
-        <v>-0.5375494071146244</v>
+        <v>0.2536650377609951</v>
       </c>
       <c r="X2">
-        <v>0.2139536949688168</v>
+        <v>0.1412407732055044</v>
       </c>
       <c r="Y2">
-        <v>-0.7515031020834413</v>
+        <v>0.1124242645554907</v>
       </c>
       <c r="Z2">
-        <v>13.36021713842575</v>
+        <v>40.17235772357727</v>
       </c>
       <c r="AA2">
-        <v>-0.1938735944164405</v>
+        <v>0.6911208381279007</v>
       </c>
       <c r="AB2">
-        <v>0.1170827542125021</v>
+        <v>0.09347852477475618</v>
       </c>
       <c r="AC2">
-        <v>-0.3109563486289426</v>
+        <v>0.5976423133531445</v>
       </c>
       <c r="AD2">
-        <v>828</v>
+        <v>814.1</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>828</v>
+        <v>814.1</v>
       </c>
       <c r="AG2">
-        <v>-102.1</v>
+        <v>-247.4999999999999</v>
       </c>
       <c r="AH2">
-        <v>0.6129700917974534</v>
+        <v>0.5304619795399752</v>
       </c>
       <c r="AI2">
-        <v>0.778049238864875</v>
+        <v>0.6196529152077942</v>
       </c>
       <c r="AJ2">
-        <v>-0.2426907535060614</v>
+        <v>-0.5231452124286616</v>
       </c>
       <c r="AK2">
-        <v>-0.7613721103653993</v>
+        <v>-0.9813639968279135</v>
       </c>
       <c r="AL2">
-        <v>23</v>
+        <v>33.9</v>
       </c>
       <c r="AM2">
-        <v>20.41</v>
+        <v>21.7</v>
       </c>
       <c r="AN2">
-        <v>-19.07834101382489</v>
+        <v>4.895369813589897</v>
       </c>
       <c r="AO2">
-        <v>-2.173913043478261</v>
+        <v>4.76401179941003</v>
       </c>
       <c r="AP2">
-        <v>2.352534562211982</v>
+        <v>-1.488274203247143</v>
       </c>
       <c r="AQ2">
-        <v>-2.449779519843214</v>
+        <v>7.442396313364055</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +724,31 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0767</v>
+        <v>0.01</v>
+      </c>
+      <c r="E3">
+        <v>0.6890000000000001</v>
+      </c>
+      <c r="F3">
+        <v>0.028</v>
       </c>
       <c r="G3">
-        <v>-0.05071395402832598</v>
+        <v>0.003606411398040962</v>
       </c>
       <c r="H3">
-        <v>-0.05273392152310193</v>
+        <v>0.002064275884400551</v>
       </c>
       <c r="I3">
-        <v>-0.01451126073833295</v>
+        <v>0.03268436816967538</v>
       </c>
       <c r="J3">
-        <v>-0.01451126073833295</v>
+        <v>0.01720389036868204</v>
       </c>
       <c r="K3">
-        <v>-81.59999999999999</v>
+        <v>57.1</v>
       </c>
       <c r="L3">
-        <v>-0.02368237752495937</v>
+        <v>0.01155589735286975</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -743,7 +757,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -752,79 +766,8851 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>930.1</v>
+        <v>1061.6</v>
       </c>
       <c r="V3">
-        <v>1.779074215761286</v>
+        <v>1.473216763807938</v>
       </c>
       <c r="W3">
-        <v>-0.5375494071146244</v>
+        <v>0.2536650377609951</v>
       </c>
       <c r="X3">
-        <v>0.2139536949688168</v>
+        <v>0.1412407732055044</v>
       </c>
       <c r="Y3">
-        <v>-0.7515031020834413</v>
+        <v>0.1124242645554907</v>
       </c>
       <c r="Z3">
-        <v>13.36021713842575</v>
+        <v>40.17235772357727</v>
       </c>
       <c r="AA3">
-        <v>-0.1938735944164405</v>
+        <v>0.6911208381279007</v>
       </c>
       <c r="AB3">
-        <v>0.1170827542125021</v>
+        <v>0.09347852477475618</v>
       </c>
       <c r="AC3">
-        <v>-0.3109563486289426</v>
+        <v>0.5976423133531445</v>
       </c>
       <c r="AD3">
-        <v>828</v>
+        <v>814.1</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>828</v>
+        <v>814.1</v>
       </c>
       <c r="AG3">
-        <v>-102.1</v>
+        <v>-247.4999999999999</v>
       </c>
       <c r="AH3">
-        <v>0.6129700917974534</v>
+        <v>0.5304619795399752</v>
       </c>
       <c r="AI3">
-        <v>0.778049238864875</v>
+        <v>0.6196529152077942</v>
       </c>
       <c r="AJ3">
-        <v>-0.2426907535060614</v>
+        <v>-0.5231452124286616</v>
       </c>
       <c r="AK3">
-        <v>-0.7613721103653993</v>
+        <v>-0.9813639968279135</v>
       </c>
       <c r="AL3">
-        <v>23</v>
+        <v>33.9</v>
       </c>
       <c r="AM3">
-        <v>20.41</v>
+        <v>21.7</v>
       </c>
       <c r="AN3">
-        <v>-19.07834101382489</v>
+        <v>4.895369813589897</v>
       </c>
       <c r="AO3">
-        <v>-2.173913043478261</v>
+        <v>4.76401179941003</v>
       </c>
       <c r="AP3">
-        <v>2.352534562211982</v>
+        <v>-1.488274203247143</v>
       </c>
       <c r="AQ3">
-        <v>-2.449779519843214</v>
+        <v>7.442396313364055</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>current_interest_coverage</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_interest_coverage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_capital</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>current_equity_value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>current_enterprise_value</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_capital</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_rating</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_equity</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>current_beta</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_coverage_ratio</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_interest_expense</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_debt_rating</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_drop_ebitda</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_ev_implied_growth</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Técnicas Reunidas, S.A. (BME:TRE)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BME:TRE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Oilfield Svcs/Equip.</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>4.05309734513274</v>
+      </c>
+      <c r="F2">
+        <v>4.50590989705406</v>
+      </c>
+      <c r="G2">
+        <v>4.8953698135899</v>
+      </c>
+      <c r="H2">
+        <v>3.69140108238124</v>
+      </c>
+      <c r="I2">
+        <v>0.530461979539975</v>
+      </c>
+      <c r="J2">
+        <v>0.4</v>
+      </c>
+      <c r="K2">
+        <v>720.6</v>
+      </c>
+      <c r="L2">
+        <v>930.9935146721911</v>
+      </c>
+      <c r="M2">
+        <v>473.1</v>
+      </c>
+      <c r="N2">
+        <v>483.273514672191</v>
+      </c>
+      <c r="O2">
+        <v>814.1</v>
+      </c>
+      <c r="P2">
+        <v>613.88</v>
+      </c>
+      <c r="Q2">
+        <v>0.0934785247747562</v>
+      </c>
+      <c r="R2">
+        <v>0.0884584936651438</v>
+      </c>
+      <c r="S2">
+        <v>0.051201806657575</v>
+      </c>
+      <c r="T2">
+        <v>0.038175</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="W2">
+        <v>0.141240773205504</v>
+      </c>
+      <c r="X2">
+        <v>0.12198082277524</v>
+      </c>
+      <c r="Y2">
+        <v>1.4765738602817</v>
+      </c>
+      <c r="Z2">
+        <v>1.19896233446278</v>
+      </c>
+      <c r="AA2">
+        <v>814.1</v>
+      </c>
+      <c r="AB2">
+        <v>0.06826907554343334</v>
+      </c>
+      <c r="AC2">
+        <v>4.053097345132744</v>
+      </c>
+      <c r="AD2">
+        <v>814.1</v>
+      </c>
+      <c r="AE2">
+        <v>33.9</v>
+      </c>
+      <c r="AF2">
+        <v>28.9</v>
+      </c>
+      <c r="AG2">
+        <v>166.3</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0.0388</v>
+      </c>
+      <c r="AJ2">
+        <v>720.6</v>
+      </c>
+      <c r="AK2">
+        <v>0.06937734437880483</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="AM2">
+        <v>0.25</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>2</v>
+      </c>
+      <c r="AQ2">
+        <v>7.105427357601002e-15</v>
+      </c>
+      <c r="AR2">
+        <v>33.9</v>
+      </c>
+      <c r="AS2">
+        <v>814.1</v>
+      </c>
+      <c r="AT2">
+        <v>1061.6</v>
+      </c>
+      <c r="AV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <v>10000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.09425388185015982</v>
+      </c>
+      <c r="C2">
+        <v>1533.166737440447</v>
+      </c>
+      <c r="D2">
+        <v>471.5667374404468</v>
+      </c>
+      <c r="E2">
+        <v>-814.1</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>1061.6</v>
+      </c>
+      <c r="H2">
+        <v>720.6</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K2">
+        <v>28.9</v>
+      </c>
+      <c r="L2">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="O2">
+        <v>35.1984693877551</v>
+      </c>
+      <c r="P2">
+        <v>105.5954081632653</v>
+      </c>
+      <c r="Q2">
+        <v>134.4954081632653</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.09425388185015982</v>
+      </c>
+      <c r="T2">
+        <v>0.7993082229751833</v>
+      </c>
+      <c r="U2">
+        <v>0.0447</v>
+      </c>
+      <c r="V2">
+        <v>0.25</v>
+      </c>
+      <c r="W2">
+        <v>0.033525</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.0940624971455344</v>
+      </c>
+      <c r="C3">
+        <v>1518.197274663047</v>
+      </c>
+      <c r="D3">
+        <v>471.9442746630468</v>
+      </c>
+      <c r="E3">
+        <v>-798.753</v>
+      </c>
+      <c r="F3">
+        <v>15.347</v>
+      </c>
+      <c r="G3">
+        <v>1061.6</v>
+      </c>
+      <c r="H3">
+        <v>720.6</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K3">
+        <v>28.9</v>
+      </c>
+      <c r="L3">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M3">
+        <v>0.6860109000000001</v>
+      </c>
+      <c r="N3">
+        <v>140.1078666510204</v>
+      </c>
+      <c r="O3">
+        <v>35.0269666627551</v>
+      </c>
+      <c r="P3">
+        <v>105.0808999882653</v>
+      </c>
+      <c r="Q3">
+        <v>133.9808999882653</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.09467398701569132</v>
+      </c>
+      <c r="T3">
+        <v>0.8053635883007529</v>
+      </c>
+      <c r="U3">
+        <v>0.0447</v>
+      </c>
+      <c r="V3">
+        <v>0.25</v>
+      </c>
+      <c r="W3">
+        <v>0.033525</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>205.2356275257731</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.09387111244090901</v>
+      </c>
+      <c r="C4">
+        <v>1503.22841688404</v>
+      </c>
+      <c r="D4">
+        <v>472.3224168840398</v>
+      </c>
+      <c r="E4">
+        <v>-783.4060000000001</v>
+      </c>
+      <c r="F4">
+        <v>30.694</v>
+      </c>
+      <c r="G4">
+        <v>1061.6</v>
+      </c>
+      <c r="H4">
+        <v>720.6</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K4">
+        <v>28.9</v>
+      </c>
+      <c r="L4">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M4">
+        <v>1.3720218</v>
+      </c>
+      <c r="N4">
+        <v>139.4218557510204</v>
+      </c>
+      <c r="O4">
+        <v>34.8554639377551</v>
+      </c>
+      <c r="P4">
+        <v>104.5663918132653</v>
+      </c>
+      <c r="Q4">
+        <v>133.4663918132653</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.0951026657560296</v>
+      </c>
+      <c r="T4">
+        <v>0.8115425325105178</v>
+      </c>
+      <c r="U4">
+        <v>0.0447</v>
+      </c>
+      <c r="V4">
+        <v>0.25</v>
+      </c>
+      <c r="W4">
+        <v>0.033525</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>102.6178137628866</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.09367972773628361</v>
+      </c>
+      <c r="C5">
+        <v>1488.260165558845</v>
+      </c>
+      <c r="D5">
+        <v>472.7011655588447</v>
+      </c>
+      <c r="E5">
+        <v>-768.059</v>
+      </c>
+      <c r="F5">
+        <v>46.041</v>
+      </c>
+      <c r="G5">
+        <v>1061.6</v>
+      </c>
+      <c r="H5">
+        <v>720.6</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K5">
+        <v>28.9</v>
+      </c>
+      <c r="L5">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M5">
+        <v>2.0580327</v>
+      </c>
+      <c r="N5">
+        <v>138.7358448510204</v>
+      </c>
+      <c r="O5">
+        <v>34.6839612127551</v>
+      </c>
+      <c r="P5">
+        <v>104.0518836382653</v>
+      </c>
+      <c r="Q5">
+        <v>132.9518836382653</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.09554018323328207</v>
+      </c>
+      <c r="T5">
+        <v>0.8178488776318241</v>
+      </c>
+      <c r="U5">
+        <v>0.0447</v>
+      </c>
+      <c r="V5">
+        <v>0.25</v>
+      </c>
+      <c r="W5">
+        <v>0.033525</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>68.41187584192437</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.09348834303165822</v>
+      </c>
+      <c r="C6">
+        <v>1473.292522147553</v>
+      </c>
+      <c r="D6">
+        <v>473.0805221475524</v>
+      </c>
+      <c r="E6">
+        <v>-752.712</v>
+      </c>
+      <c r="F6">
+        <v>61.38800000000001</v>
+      </c>
+      <c r="G6">
+        <v>1061.6</v>
+      </c>
+      <c r="H6">
+        <v>720.6</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K6">
+        <v>28.9</v>
+      </c>
+      <c r="L6">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M6">
+        <v>2.7440436</v>
+      </c>
+      <c r="N6">
+        <v>138.0498339510204</v>
+      </c>
+      <c r="O6">
+        <v>34.5124584877551</v>
+      </c>
+      <c r="P6">
+        <v>103.5373754632653</v>
+      </c>
+      <c r="Q6">
+        <v>132.4373754632653</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.09598681565797731</v>
+      </c>
+      <c r="T6">
+        <v>0.8242866049431579</v>
+      </c>
+      <c r="U6">
+        <v>0.0447</v>
+      </c>
+      <c r="V6">
+        <v>0.25</v>
+      </c>
+      <c r="W6">
+        <v>0.033525</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>51.30890688144328</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.09329695832703282</v>
+      </c>
+      <c r="C7">
+        <v>1458.325488114945</v>
+      </c>
+      <c r="D7">
+        <v>473.4604881149452</v>
+      </c>
+      <c r="E7">
+        <v>-737.365</v>
+      </c>
+      <c r="F7">
+        <v>76.735</v>
+      </c>
+      <c r="G7">
+        <v>1061.6</v>
+      </c>
+      <c r="H7">
+        <v>720.6</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K7">
+        <v>28.9</v>
+      </c>
+      <c r="L7">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M7">
+        <v>3.4300545</v>
+      </c>
+      <c r="N7">
+        <v>137.3638230510204</v>
+      </c>
+      <c r="O7">
+        <v>34.3409557627551</v>
+      </c>
+      <c r="P7">
+        <v>103.0228672882653</v>
+      </c>
+      <c r="Q7">
+        <v>131.9228672882653</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.09644285087056086</v>
+      </c>
+      <c r="T7">
+        <v>0.8308598633557827</v>
+      </c>
+      <c r="U7">
+        <v>0.0447</v>
+      </c>
+      <c r="V7">
+        <v>0.25</v>
+      </c>
+      <c r="W7">
+        <v>0.033525</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>41.04712550515463</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.09310557362240741</v>
+      </c>
+      <c r="C8">
+        <v>1443.359064930514</v>
+      </c>
+      <c r="D8">
+        <v>473.8410649305143</v>
+      </c>
+      <c r="E8">
+        <v>-722.018</v>
+      </c>
+      <c r="F8">
+        <v>92.08199999999999</v>
+      </c>
+      <c r="G8">
+        <v>1061.6</v>
+      </c>
+      <c r="H8">
+        <v>720.6</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K8">
+        <v>28.9</v>
+      </c>
+      <c r="L8">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M8">
+        <v>4.1160654</v>
+      </c>
+      <c r="N8">
+        <v>136.6778121510204</v>
+      </c>
+      <c r="O8">
+        <v>34.1694530377551</v>
+      </c>
+      <c r="P8">
+        <v>102.5083591132653</v>
+      </c>
+      <c r="Q8">
+        <v>131.4083591132653</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.0969085889600079</v>
+      </c>
+      <c r="T8">
+        <v>0.8375729783303782</v>
+      </c>
+      <c r="U8">
+        <v>0.0447</v>
+      </c>
+      <c r="V8">
+        <v>0.25</v>
+      </c>
+      <c r="W8">
+        <v>0.033525</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>34.20593792096219</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.092914188917782</v>
+      </c>
+      <c r="C9">
+        <v>1428.39325406848</v>
+      </c>
+      <c r="D9">
+        <v>474.2222540684803</v>
+      </c>
+      <c r="E9">
+        <v>-706.671</v>
+      </c>
+      <c r="F9">
+        <v>107.429</v>
+      </c>
+      <c r="G9">
+        <v>1061.6</v>
+      </c>
+      <c r="H9">
+        <v>720.6</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K9">
+        <v>28.9</v>
+      </c>
+      <c r="L9">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M9">
+        <v>4.802076300000001</v>
+      </c>
+      <c r="N9">
+        <v>135.9918012510204</v>
+      </c>
+      <c r="O9">
+        <v>33.9979503127551</v>
+      </c>
+      <c r="P9">
+        <v>101.9938509382653</v>
+      </c>
+      <c r="Q9">
+        <v>130.8938509382653</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.09738434292234624</v>
+      </c>
+      <c r="T9">
+        <v>0.8444304613689436</v>
+      </c>
+      <c r="U9">
+        <v>0.0447</v>
+      </c>
+      <c r="V9">
+        <v>0.25</v>
+      </c>
+      <c r="W9">
+        <v>0.033525</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>29.31937536082473</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.09272280421315662</v>
+      </c>
+      <c r="C10">
+        <v>1413.42805700781</v>
+      </c>
+      <c r="D10">
+        <v>474.6040570078105</v>
+      </c>
+      <c r="E10">
+        <v>-691.3240000000001</v>
+      </c>
+      <c r="F10">
+        <v>122.776</v>
+      </c>
+      <c r="G10">
+        <v>1061.6</v>
+      </c>
+      <c r="H10">
+        <v>720.6</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K10">
+        <v>28.9</v>
+      </c>
+      <c r="L10">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M10">
+        <v>5.488087200000001</v>
+      </c>
+      <c r="N10">
+        <v>135.3057903510204</v>
+      </c>
+      <c r="O10">
+        <v>33.8264475877551</v>
+      </c>
+      <c r="P10">
+        <v>101.4793427632653</v>
+      </c>
+      <c r="Q10">
+        <v>130.3793427632653</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.09787043936212676</v>
+      </c>
+      <c r="T10">
+        <v>0.8514370201257389</v>
+      </c>
+      <c r="U10">
+        <v>0.0447</v>
+      </c>
+      <c r="V10">
+        <v>0.25</v>
+      </c>
+      <c r="W10">
+        <v>0.033525</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>25.65445344072164</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.09253141950853121</v>
+      </c>
+      <c r="C11">
+        <v>1398.46347523224</v>
+      </c>
+      <c r="D11">
+        <v>474.9864752322401</v>
+      </c>
+      <c r="E11">
+        <v>-675.9770000000001</v>
+      </c>
+      <c r="F11">
+        <v>138.123</v>
+      </c>
+      <c r="G11">
+        <v>1061.6</v>
+      </c>
+      <c r="H11">
+        <v>720.6</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K11">
+        <v>28.9</v>
+      </c>
+      <c r="L11">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M11">
+        <v>6.1740981</v>
+      </c>
+      <c r="N11">
+        <v>134.6197794510204</v>
+      </c>
+      <c r="O11">
+        <v>33.6549448627551</v>
+      </c>
+      <c r="P11">
+        <v>100.9648345882653</v>
+      </c>
+      <c r="Q11">
+        <v>129.8648345882653</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.09836721924014419</v>
+      </c>
+      <c r="T11">
+        <v>0.8585975691848809</v>
+      </c>
+      <c r="U11">
+        <v>0.0447</v>
+      </c>
+      <c r="V11">
+        <v>0.25</v>
+      </c>
+      <c r="W11">
+        <v>0.033525</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>22.80395861397479</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.0923400348039058</v>
+      </c>
+      <c r="C12">
+        <v>1383.499510230289</v>
+      </c>
+      <c r="D12">
+        <v>475.3695102302894</v>
+      </c>
+      <c r="E12">
+        <v>-660.63</v>
+      </c>
+      <c r="F12">
+        <v>153.47</v>
+      </c>
+      <c r="G12">
+        <v>1061.6</v>
+      </c>
+      <c r="H12">
+        <v>720.6</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K12">
+        <v>28.9</v>
+      </c>
+      <c r="L12">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M12">
+        <v>6.860109</v>
+      </c>
+      <c r="N12">
+        <v>133.9337685510204</v>
+      </c>
+      <c r="O12">
+        <v>33.48344213775511</v>
+      </c>
+      <c r="P12">
+        <v>100.4503264132653</v>
+      </c>
+      <c r="Q12">
+        <v>129.3503264132653</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.09887503867100646</v>
+      </c>
+      <c r="T12">
+        <v>0.8659172415564486</v>
+      </c>
+      <c r="U12">
+        <v>0.0447</v>
+      </c>
+      <c r="V12">
+        <v>0.25</v>
+      </c>
+      <c r="W12">
+        <v>0.033525</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>20.52356275257732</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.09214865009928043</v>
+      </c>
+      <c r="C13">
+        <v>1368.536163495284</v>
+      </c>
+      <c r="D13">
+        <v>475.7531634952845</v>
+      </c>
+      <c r="E13">
+        <v>-645.283</v>
+      </c>
+      <c r="F13">
+        <v>168.817</v>
+      </c>
+      <c r="G13">
+        <v>1061.6</v>
+      </c>
+      <c r="H13">
+        <v>720.6</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K13">
+        <v>28.9</v>
+      </c>
+      <c r="L13">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M13">
+        <v>7.546119900000001</v>
+      </c>
+      <c r="N13">
+        <v>133.2477576510204</v>
+      </c>
+      <c r="O13">
+        <v>33.3119394127551</v>
+      </c>
+      <c r="P13">
+        <v>99.93581823826531</v>
+      </c>
+      <c r="Q13">
+        <v>128.8358182382653</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.09939426977447238</v>
+      </c>
+      <c r="T13">
+        <v>0.8734014009476021</v>
+      </c>
+      <c r="U13">
+        <v>0.0447</v>
+      </c>
+      <c r="V13">
+        <v>0.25</v>
+      </c>
+      <c r="W13">
+        <v>0.033525</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>18.65778432052483</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.09195726539465501</v>
+      </c>
+      <c r="C14">
+        <v>1353.573436525376</v>
+      </c>
+      <c r="D14">
+        <v>476.1374365253762</v>
+      </c>
+      <c r="E14">
+        <v>-629.936</v>
+      </c>
+      <c r="F14">
+        <v>184.164</v>
+      </c>
+      <c r="G14">
+        <v>1061.6</v>
+      </c>
+      <c r="H14">
+        <v>720.6</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K14">
+        <v>28.9</v>
+      </c>
+      <c r="L14">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M14">
+        <v>8.2321308</v>
+      </c>
+      <c r="N14">
+        <v>132.5617467510204</v>
+      </c>
+      <c r="O14">
+        <v>33.14043668775511</v>
+      </c>
+      <c r="P14">
+        <v>99.42131006326531</v>
+      </c>
+      <c r="Q14">
+        <v>128.3213100632653</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.09992530158483524</v>
+      </c>
+      <c r="T14">
+        <v>0.8810556548703725</v>
+      </c>
+      <c r="U14">
+        <v>0.0447</v>
+      </c>
+      <c r="V14">
+        <v>0.25</v>
+      </c>
+      <c r="W14">
+        <v>0.033525</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>17.1029689604811</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.09176588069002961</v>
+      </c>
+      <c r="C15">
+        <v>1338.611330823559</v>
+      </c>
+      <c r="D15">
+        <v>476.5223308235593</v>
+      </c>
+      <c r="E15">
+        <v>-614.5889999999999</v>
+      </c>
+      <c r="F15">
+        <v>199.511</v>
+      </c>
+      <c r="G15">
+        <v>1061.6</v>
+      </c>
+      <c r="H15">
+        <v>720.6</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K15">
+        <v>28.9</v>
+      </c>
+      <c r="L15">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M15">
+        <v>8.918141700000001</v>
+      </c>
+      <c r="N15">
+        <v>131.8757358510204</v>
+      </c>
+      <c r="O15">
+        <v>32.9689339627551</v>
+      </c>
+      <c r="P15">
+        <v>98.90680188826531</v>
+      </c>
+      <c r="Q15">
+        <v>127.8068018882653</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1004685410230226</v>
+      </c>
+      <c r="T15">
+        <v>0.8888858686534366</v>
+      </c>
+      <c r="U15">
+        <v>0.0447</v>
+      </c>
+      <c r="V15">
+        <v>0.25</v>
+      </c>
+      <c r="W15">
+        <v>0.033525</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>15.78735596352101</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.09157449598540422</v>
+      </c>
+      <c r="C16">
+        <v>1323.649847897693</v>
+      </c>
+      <c r="D16">
+        <v>476.9078478976926</v>
+      </c>
+      <c r="E16">
+        <v>-599.242</v>
+      </c>
+      <c r="F16">
+        <v>214.858</v>
+      </c>
+      <c r="G16">
+        <v>1061.6</v>
+      </c>
+      <c r="H16">
+        <v>720.6</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K16">
+        <v>28.9</v>
+      </c>
+      <c r="L16">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M16">
+        <v>9.604152600000003</v>
+      </c>
+      <c r="N16">
+        <v>131.1897249510204</v>
+      </c>
+      <c r="O16">
+        <v>32.79743123775511</v>
+      </c>
+      <c r="P16">
+        <v>98.39229371326532</v>
+      </c>
+      <c r="Q16">
+        <v>127.2922937132653</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1010244139365165</v>
+      </c>
+      <c r="T16">
+        <v>0.8968981804314557</v>
+      </c>
+      <c r="U16">
+        <v>0.0447</v>
+      </c>
+      <c r="V16">
+        <v>0.25</v>
+      </c>
+      <c r="W16">
+        <v>0.033525</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>14.65968768041236</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.09138311128077881</v>
+      </c>
+      <c r="C17">
+        <v>1308.688989260518</v>
+      </c>
+      <c r="D17">
+        <v>477.2939892605185</v>
+      </c>
+      <c r="E17">
+        <v>-583.895</v>
+      </c>
+      <c r="F17">
+        <v>230.205</v>
+      </c>
+      <c r="G17">
+        <v>1061.6</v>
+      </c>
+      <c r="H17">
+        <v>720.6</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K17">
+        <v>28.9</v>
+      </c>
+      <c r="L17">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M17">
+        <v>10.2901635</v>
+      </c>
+      <c r="N17">
+        <v>130.5037140510204</v>
+      </c>
+      <c r="O17">
+        <v>32.6259285127551</v>
+      </c>
+      <c r="P17">
+        <v>97.8777855382653</v>
+      </c>
+      <c r="Q17">
+        <v>126.7777855382653</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.101593366212681</v>
+      </c>
+      <c r="T17">
+        <v>0.905099017192487</v>
+      </c>
+      <c r="U17">
+        <v>0.0447</v>
+      </c>
+      <c r="V17">
+        <v>0.25</v>
+      </c>
+      <c r="W17">
+        <v>0.033525</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>13.68237516838487</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.0911917265761534</v>
+      </c>
+      <c r="C18">
+        <v>1293.728756429682</v>
+      </c>
+      <c r="D18">
+        <v>477.6807564296823</v>
+      </c>
+      <c r="E18">
+        <v>-568.548</v>
+      </c>
+      <c r="F18">
+        <v>245.552</v>
+      </c>
+      <c r="G18">
+        <v>1061.6</v>
+      </c>
+      <c r="H18">
+        <v>720.6</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K18">
+        <v>28.9</v>
+      </c>
+      <c r="L18">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M18">
+        <v>10.9761744</v>
+      </c>
+      <c r="N18">
+        <v>129.8177031510204</v>
+      </c>
+      <c r="O18">
+        <v>32.45442578775511</v>
+      </c>
+      <c r="P18">
+        <v>97.36327736326533</v>
+      </c>
+      <c r="Q18">
+        <v>126.2632773632653</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1021758649716112</v>
+      </c>
+      <c r="T18">
+        <v>0.913495111971638</v>
+      </c>
+      <c r="U18">
+        <v>0.0447</v>
+      </c>
+      <c r="V18">
+        <v>0.25</v>
+      </c>
+      <c r="W18">
+        <v>0.033525</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>12.82722672036082</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.09114059187152802</v>
+      </c>
+      <c r="C19">
+        <v>1278.485200105824</v>
+      </c>
+      <c r="D19">
+        <v>477.7842001058238</v>
+      </c>
+      <c r="E19">
+        <v>-553.201</v>
+      </c>
+      <c r="F19">
+        <v>260.899</v>
+      </c>
+      <c r="G19">
+        <v>1061.6</v>
+      </c>
+      <c r="H19">
+        <v>720.6</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K19">
+        <v>28.9</v>
+      </c>
+      <c r="L19">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M19">
+        <v>11.9491742</v>
+      </c>
+      <c r="N19">
+        <v>128.8447033510204</v>
+      </c>
+      <c r="O19">
+        <v>32.21117583775511</v>
+      </c>
+      <c r="P19">
+        <v>96.63352751326532</v>
+      </c>
+      <c r="Q19">
+        <v>125.5335275132653</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1027723998452145</v>
+      </c>
+      <c r="T19">
+        <v>0.9220935222876363</v>
+      </c>
+      <c r="U19">
+        <v>0.0458</v>
+      </c>
+      <c r="V19">
+        <v>0.25</v>
+      </c>
+      <c r="W19">
+        <v>0.03435</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>11.78272868019787</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.09095745716690262</v>
+      </c>
+      <c r="C20">
+        <v>1263.509042897015</v>
+      </c>
+      <c r="D20">
+        <v>478.1550428970155</v>
+      </c>
+      <c r="E20">
+        <v>-537.854</v>
+      </c>
+      <c r="F20">
+        <v>276.246</v>
+      </c>
+      <c r="G20">
+        <v>1061.6</v>
+      </c>
+      <c r="H20">
+        <v>720.6</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K20">
+        <v>28.9</v>
+      </c>
+      <c r="L20">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M20">
+        <v>12.6520668</v>
+      </c>
+      <c r="N20">
+        <v>128.1418107510204</v>
+      </c>
+      <c r="O20">
+        <v>32.0354526877551</v>
+      </c>
+      <c r="P20">
+        <v>96.1063580632653</v>
+      </c>
+      <c r="Q20">
+        <v>125.0063580632653</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1033834843498812</v>
+      </c>
+      <c r="T20">
+        <v>0.9309016499284147</v>
+      </c>
+      <c r="U20">
+        <v>0.0458</v>
+      </c>
+      <c r="V20">
+        <v>0.25</v>
+      </c>
+      <c r="W20">
+        <v>0.03435</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>11.1281326424091</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.09077432246227723</v>
+      </c>
+      <c r="C21">
+        <v>1248.533461811073</v>
+      </c>
+      <c r="D21">
+        <v>478.5264618110727</v>
+      </c>
+      <c r="E21">
+        <v>-522.5070000000001</v>
+      </c>
+      <c r="F21">
+        <v>291.593</v>
+      </c>
+      <c r="G21">
+        <v>1061.6</v>
+      </c>
+      <c r="H21">
+        <v>720.6</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K21">
+        <v>28.9</v>
+      </c>
+      <c r="L21">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M21">
+        <v>13.3549594</v>
+      </c>
+      <c r="N21">
+        <v>127.4389181510204</v>
+      </c>
+      <c r="O21">
+        <v>31.8597295377551</v>
+      </c>
+      <c r="P21">
+        <v>95.57918861326532</v>
+      </c>
+      <c r="Q21">
+        <v>124.4791886132653</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1040096573608361</v>
+      </c>
+      <c r="T21">
+        <v>0.9399272622022991</v>
+      </c>
+      <c r="U21">
+        <v>0.0458</v>
+      </c>
+      <c r="V21">
+        <v>0.25</v>
+      </c>
+      <c r="W21">
+        <v>0.03435</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>10.54244145070336</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.09059118775765182</v>
+      </c>
+      <c r="C22">
+        <v>1233.558458191593</v>
+      </c>
+      <c r="D22">
+        <v>478.8984581915931</v>
+      </c>
+      <c r="E22">
+        <v>-507.16</v>
+      </c>
+      <c r="F22">
+        <v>306.94</v>
+      </c>
+      <c r="G22">
+        <v>1061.6</v>
+      </c>
+      <c r="H22">
+        <v>720.6</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K22">
+        <v>28.9</v>
+      </c>
+      <c r="L22">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M22">
+        <v>14.057852</v>
+      </c>
+      <c r="N22">
+        <v>126.7360255510204</v>
+      </c>
+      <c r="O22">
+        <v>31.6840063877551</v>
+      </c>
+      <c r="P22">
+        <v>95.05201916326531</v>
+      </c>
+      <c r="Q22">
+        <v>123.9520191632653</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1046514846970648</v>
+      </c>
+      <c r="T22">
+        <v>0.9491785147830302</v>
+      </c>
+      <c r="U22">
+        <v>0.0458</v>
+      </c>
+      <c r="V22">
+        <v>0.25</v>
+      </c>
+      <c r="W22">
+        <v>0.03435</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>10.01531937816819</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.09075455305302642</v>
+      </c>
+      <c r="C23">
+        <v>1217.879591028644</v>
+      </c>
+      <c r="D23">
+        <v>478.5665910286437</v>
+      </c>
+      <c r="E23">
+        <v>-491.813</v>
+      </c>
+      <c r="F23">
+        <v>322.287</v>
+      </c>
+      <c r="G23">
+        <v>1061.6</v>
+      </c>
+      <c r="H23">
+        <v>720.6</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K23">
+        <v>28.9</v>
+      </c>
+      <c r="L23">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M23">
+        <v>15.469776</v>
+      </c>
+      <c r="N23">
+        <v>125.3241015510204</v>
+      </c>
+      <c r="O23">
+        <v>31.3310253877551</v>
+      </c>
+      <c r="P23">
+        <v>93.99307616326531</v>
+      </c>
+      <c r="Q23">
+        <v>122.8930761632653</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1053095608266157</v>
+      </c>
+      <c r="T23">
+        <v>0.9586639762898559</v>
+      </c>
+      <c r="U23">
+        <v>0.048</v>
+      </c>
+      <c r="V23">
+        <v>0.25</v>
+      </c>
+      <c r="W23">
+        <v>0.036</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>9.101222768256012</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.09058791834840102</v>
+      </c>
+      <c r="C24">
+        <v>1202.871104505611</v>
+      </c>
+      <c r="D24">
+        <v>478.9051045056115</v>
+      </c>
+      <c r="E24">
+        <v>-476.466</v>
+      </c>
+      <c r="F24">
+        <v>337.634</v>
+      </c>
+      <c r="G24">
+        <v>1061.6</v>
+      </c>
+      <c r="H24">
+        <v>720.6</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K24">
+        <v>28.9</v>
+      </c>
+      <c r="L24">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M24">
+        <v>16.206432</v>
+      </c>
+      <c r="N24">
+        <v>124.5874455510204</v>
+      </c>
+      <c r="O24">
+        <v>31.1468613877551</v>
+      </c>
+      <c r="P24">
+        <v>93.4405841632653</v>
+      </c>
+      <c r="Q24">
+        <v>122.3405841632653</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1059845107030782</v>
+      </c>
+      <c r="T24">
+        <v>0.9683926547583951</v>
+      </c>
+      <c r="U24">
+        <v>0.048</v>
+      </c>
+      <c r="V24">
+        <v>0.25</v>
+      </c>
+      <c r="W24">
+        <v>0.036</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>8.687530824244375</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.09042128364377562</v>
+      </c>
+      <c r="C25">
+        <v>1187.86309721573</v>
+      </c>
+      <c r="D25">
+        <v>479.2440972157295</v>
+      </c>
+      <c r="E25">
+        <v>-461.119</v>
+      </c>
+      <c r="F25">
+        <v>352.9810000000001</v>
+      </c>
+      <c r="G25">
+        <v>1061.6</v>
+      </c>
+      <c r="H25">
+        <v>720.6</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K25">
+        <v>28.9</v>
+      </c>
+      <c r="L25">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M25">
+        <v>16.943088</v>
+      </c>
+      <c r="N25">
+        <v>123.8507895510204</v>
+      </c>
+      <c r="O25">
+        <v>30.9626973877551</v>
+      </c>
+      <c r="P25">
+        <v>92.88809216326531</v>
+      </c>
+      <c r="Q25">
+        <v>121.7880921632653</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1066769917451632</v>
+      </c>
+      <c r="T25">
+        <v>0.9783740261741692</v>
+      </c>
+      <c r="U25">
+        <v>0.048</v>
+      </c>
+      <c r="V25">
+        <v>0.25</v>
+      </c>
+      <c r="W25">
+        <v>0.036</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>8.309812092755488</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.09025464893915022</v>
+      </c>
+      <c r="C26">
+        <v>1172.855570177393</v>
+      </c>
+      <c r="D26">
+        <v>479.5835701773935</v>
+      </c>
+      <c r="E26">
+        <v>-445.772</v>
+      </c>
+      <c r="F26">
+        <v>368.328</v>
+      </c>
+      <c r="G26">
+        <v>1061.6</v>
+      </c>
+      <c r="H26">
+        <v>720.6</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K26">
+        <v>28.9</v>
+      </c>
+      <c r="L26">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M26">
+        <v>17.679744</v>
+      </c>
+      <c r="N26">
+        <v>123.1141335510204</v>
+      </c>
+      <c r="O26">
+        <v>30.7785333877551</v>
+      </c>
+      <c r="P26">
+        <v>92.33560016326531</v>
+      </c>
+      <c r="Q26">
+        <v>121.2356001632653</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1073876959725661</v>
+      </c>
+      <c r="T26">
+        <v>0.9886180652587795</v>
+      </c>
+      <c r="U26">
+        <v>0.048</v>
+      </c>
+      <c r="V26">
+        <v>0.25</v>
+      </c>
+      <c r="W26">
+        <v>0.036</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>7.963569922224011</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.09036926423452483</v>
+      </c>
+      <c r="C27">
+        <v>1157.275021028157</v>
+      </c>
+      <c r="D27">
+        <v>479.3500210281572</v>
+      </c>
+      <c r="E27">
+        <v>-430.425</v>
+      </c>
+      <c r="F27">
+        <v>383.675</v>
+      </c>
+      <c r="G27">
+        <v>1061.6</v>
+      </c>
+      <c r="H27">
+        <v>720.6</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K27">
+        <v>28.9</v>
+      </c>
+      <c r="L27">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M27">
+        <v>18.9919125</v>
+      </c>
+      <c r="N27">
+        <v>121.8019650510204</v>
+      </c>
+      <c r="O27">
+        <v>30.4504912627551</v>
+      </c>
+      <c r="P27">
+        <v>91.35147378826531</v>
+      </c>
+      <c r="Q27">
+        <v>120.2514737882653</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1081173523126998</v>
+      </c>
+      <c r="T27">
+        <v>0.9991352787189791</v>
+      </c>
+      <c r="U27">
+        <v>0.0495</v>
+      </c>
+      <c r="V27">
+        <v>0.25</v>
+      </c>
+      <c r="W27">
+        <v>0.03712500000000001</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>7.413359636688533</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.09021387952989943</v>
+      </c>
+      <c r="C28">
+        <v>1142.244700018205</v>
+      </c>
+      <c r="D28">
+        <v>479.6667000182053</v>
+      </c>
+      <c r="E28">
+        <v>-415.078</v>
+      </c>
+      <c r="F28">
+        <v>399.022</v>
+      </c>
+      <c r="G28">
+        <v>1061.6</v>
+      </c>
+      <c r="H28">
+        <v>720.6</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K28">
+        <v>28.9</v>
+      </c>
+      <c r="L28">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M28">
+        <v>19.751589</v>
+      </c>
+      <c r="N28">
+        <v>121.0422885510204</v>
+      </c>
+      <c r="O28">
+        <v>30.2605721377551</v>
+      </c>
+      <c r="P28">
+        <v>90.78171641326531</v>
+      </c>
+      <c r="Q28">
+        <v>119.6817164132653</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1088667290944587</v>
+      </c>
+      <c r="T28">
+        <v>1.009936741191617</v>
+      </c>
+      <c r="U28">
+        <v>0.0495</v>
+      </c>
+      <c r="V28">
+        <v>0.25</v>
+      </c>
+      <c r="W28">
+        <v>0.03712500000000001</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>7.128230419892819</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.09005849482527403</v>
+      </c>
+      <c r="C29">
+        <v>1127.214797708055</v>
+      </c>
+      <c r="D29">
+        <v>479.9837977080554</v>
+      </c>
+      <c r="E29">
+        <v>-399.731</v>
+      </c>
+      <c r="F29">
+        <v>414.369</v>
+      </c>
+      <c r="G29">
+        <v>1061.6</v>
+      </c>
+      <c r="H29">
+        <v>720.6</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K29">
+        <v>28.9</v>
+      </c>
+      <c r="L29">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M29">
+        <v>20.5112655</v>
+      </c>
+      <c r="N29">
+        <v>120.2826120510204</v>
+      </c>
+      <c r="O29">
+        <v>30.0706530127551</v>
+      </c>
+      <c r="P29">
+        <v>90.21195903826531</v>
+      </c>
+      <c r="Q29">
+        <v>119.1119590382653</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1096366367469507</v>
+      </c>
+      <c r="T29">
+        <v>1.021034134142957</v>
+      </c>
+      <c r="U29">
+        <v>0.0495</v>
+      </c>
+      <c r="V29">
+        <v>0.25</v>
+      </c>
+      <c r="W29">
+        <v>0.03712500000000001</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>6.864221885822714</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.08990311012064862</v>
+      </c>
+      <c r="C30">
+        <v>1112.185314928638</v>
+      </c>
+      <c r="D30">
+        <v>480.3013149286381</v>
+      </c>
+      <c r="E30">
+        <v>-384.384</v>
+      </c>
+      <c r="F30">
+        <v>429.7160000000001</v>
+      </c>
+      <c r="G30">
+        <v>1061.6</v>
+      </c>
+      <c r="H30">
+        <v>720.6</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K30">
+        <v>28.9</v>
+      </c>
+      <c r="L30">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M30">
+        <v>21.27094200000001</v>
+      </c>
+      <c r="N30">
+        <v>119.5229355510204</v>
+      </c>
+      <c r="O30">
+        <v>29.8807338877551</v>
+      </c>
+      <c r="P30">
+        <v>89.64220166326531</v>
+      </c>
+      <c r="Q30">
+        <v>118.5422016632653</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1104279307231231</v>
+      </c>
+      <c r="T30">
+        <v>1.032439788009612</v>
+      </c>
+      <c r="U30">
+        <v>0.0495</v>
+      </c>
+      <c r="V30">
+        <v>0.25</v>
+      </c>
+      <c r="W30">
+        <v>0.03712500000000001</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>6.619071104186188</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.08974772541602323</v>
+      </c>
+      <c r="C31">
+        <v>1097.156252513084</v>
+      </c>
+      <c r="D31">
+        <v>480.6192525130841</v>
+      </c>
+      <c r="E31">
+        <v>-369.037</v>
+      </c>
+      <c r="F31">
+        <v>445.063</v>
+      </c>
+      <c r="G31">
+        <v>1061.6</v>
+      </c>
+      <c r="H31">
+        <v>720.6</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K31">
+        <v>28.9</v>
+      </c>
+      <c r="L31">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M31">
+        <v>22.0306185</v>
+      </c>
+      <c r="N31">
+        <v>118.7632590510204</v>
+      </c>
+      <c r="O31">
+        <v>29.6908147627551</v>
+      </c>
+      <c r="P31">
+        <v>89.0724442882653</v>
+      </c>
+      <c r="Q31">
+        <v>117.9724442882653</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1112415146704552</v>
+      </c>
+      <c r="T31">
+        <v>1.04416672790068</v>
+      </c>
+      <c r="U31">
+        <v>0.0495</v>
+      </c>
+      <c r="V31">
+        <v>0.25</v>
+      </c>
+      <c r="W31">
+        <v>0.03712500000000001</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>6.390827273007356</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.08959234071139782</v>
+      </c>
+      <c r="C32">
+        <v>1082.127611296731</v>
+      </c>
+      <c r="D32">
+        <v>480.9376112967313</v>
+      </c>
+      <c r="E32">
+        <v>-353.69</v>
+      </c>
+      <c r="F32">
+        <v>460.41</v>
+      </c>
+      <c r="G32">
+        <v>1061.6</v>
+      </c>
+      <c r="H32">
+        <v>720.6</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K32">
+        <v>28.9</v>
+      </c>
+      <c r="L32">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M32">
+        <v>22.790295</v>
+      </c>
+      <c r="N32">
+        <v>118.0035825510204</v>
+      </c>
+      <c r="O32">
+        <v>29.5008956377551</v>
+      </c>
+      <c r="P32">
+        <v>88.50268691326531</v>
+      </c>
+      <c r="Q32">
+        <v>117.4026869132653</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1120783438734255</v>
+      </c>
+      <c r="T32">
+        <v>1.056228723217207</v>
+      </c>
+      <c r="U32">
+        <v>0.0495</v>
+      </c>
+      <c r="V32">
+        <v>0.25</v>
+      </c>
+      <c r="W32">
+        <v>0.03712500000000001</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>6.177799697240443</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.08976245600677242</v>
+      </c>
+      <c r="C33">
+        <v>1066.432093723795</v>
+      </c>
+      <c r="D33">
+        <v>480.5890937237953</v>
+      </c>
+      <c r="E33">
+        <v>-338.343</v>
+      </c>
+      <c r="F33">
+        <v>475.757</v>
+      </c>
+      <c r="G33">
+        <v>1061.6</v>
+      </c>
+      <c r="H33">
+        <v>720.6</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K33">
+        <v>28.9</v>
+      </c>
+      <c r="L33">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M33">
+        <v>24.2160313</v>
+      </c>
+      <c r="N33">
+        <v>116.5778462510204</v>
+      </c>
+      <c r="O33">
+        <v>29.1444615627551</v>
+      </c>
+      <c r="P33">
+        <v>87.43338468826531</v>
+      </c>
+      <c r="Q33">
+        <v>116.3333846882653</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1129394289953223</v>
+      </c>
+      <c r="T33">
+        <v>1.068640341586386</v>
+      </c>
+      <c r="U33">
+        <v>0.0509</v>
+      </c>
+      <c r="V33">
+        <v>0.25</v>
+      </c>
+      <c r="W33">
+        <v>0.038175</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>5.814077286521364</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.08961757130214704</v>
+      </c>
+      <c r="C34">
+        <v>1051.381889112219</v>
+      </c>
+      <c r="D34">
+        <v>480.8858891122196</v>
+      </c>
+      <c r="E34">
+        <v>-322.996</v>
+      </c>
+      <c r="F34">
+        <v>491.104</v>
+      </c>
+      <c r="G34">
+        <v>1061.6</v>
+      </c>
+      <c r="H34">
+        <v>720.6</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K34">
+        <v>28.9</v>
+      </c>
+      <c r="L34">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M34">
+        <v>24.9971936</v>
+      </c>
+      <c r="N34">
+        <v>115.7966839510204</v>
+      </c>
+      <c r="O34">
+        <v>28.9491709877551</v>
+      </c>
+      <c r="P34">
+        <v>86.8475129632653</v>
+      </c>
+      <c r="Q34">
+        <v>115.7475129632653</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1138258401502162</v>
+      </c>
+      <c r="T34">
+        <v>1.08141700755466</v>
+      </c>
+      <c r="U34">
+        <v>0.0509</v>
+      </c>
+      <c r="V34">
+        <v>0.25</v>
+      </c>
+      <c r="W34">
+        <v>0.038175</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>5.632387371317571</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.08947268659752163</v>
+      </c>
+      <c r="C35">
+        <v>1036.332051308535</v>
+      </c>
+      <c r="D35">
+        <v>481.1830513085353</v>
+      </c>
+      <c r="E35">
+        <v>-307.649</v>
+      </c>
+      <c r="F35">
+        <v>506.451</v>
+      </c>
+      <c r="G35">
+        <v>1061.6</v>
+      </c>
+      <c r="H35">
+        <v>720.6</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K35">
+        <v>28.9</v>
+      </c>
+      <c r="L35">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M35">
+        <v>25.7783559</v>
+      </c>
+      <c r="N35">
+        <v>115.0155216510204</v>
+      </c>
+      <c r="O35">
+        <v>28.7538804127551</v>
+      </c>
+      <c r="P35">
+        <v>86.2616412382653</v>
+      </c>
+      <c r="Q35">
+        <v>115.1616412382653</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1147387113395845</v>
+      </c>
+      <c r="T35">
+        <v>1.094575066536912</v>
+      </c>
+      <c r="U35">
+        <v>0.0509</v>
+      </c>
+      <c r="V35">
+        <v>0.25</v>
+      </c>
+      <c r="W35">
+        <v>0.038175</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>5.461708966126129</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.08932780189289623</v>
+      </c>
+      <c r="C36">
+        <v>1021.282580993167</v>
+      </c>
+      <c r="D36">
+        <v>481.4805809931667</v>
+      </c>
+      <c r="E36">
+        <v>-292.302</v>
+      </c>
+      <c r="F36">
+        <v>521.798</v>
+      </c>
+      <c r="G36">
+        <v>1061.6</v>
+      </c>
+      <c r="H36">
+        <v>720.6</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K36">
+        <v>28.9</v>
+      </c>
+      <c r="L36">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M36">
+        <v>26.5595182</v>
+      </c>
+      <c r="N36">
+        <v>114.2343593510204</v>
+      </c>
+      <c r="O36">
+        <v>28.5585898377551</v>
+      </c>
+      <c r="P36">
+        <v>85.67576951326531</v>
+      </c>
+      <c r="Q36">
+        <v>114.5757695132653</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.115679245292267</v>
+      </c>
+      <c r="T36">
+        <v>1.108131854579232</v>
+      </c>
+      <c r="U36">
+        <v>0.0509</v>
+      </c>
+      <c r="V36">
+        <v>0.25</v>
+      </c>
+      <c r="W36">
+        <v>0.038175</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>5.30107046712242</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.08918291718827083</v>
+      </c>
+      <c r="C37">
+        <v>1006.233478848222</v>
+      </c>
+      <c r="D37">
+        <v>481.7784788482222</v>
+      </c>
+      <c r="E37">
+        <v>-276.9549999999999</v>
+      </c>
+      <c r="F37">
+        <v>537.1450000000001</v>
+      </c>
+      <c r="G37">
+        <v>1061.6</v>
+      </c>
+      <c r="H37">
+        <v>720.6</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K37">
+        <v>28.9</v>
+      </c>
+      <c r="L37">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M37">
+        <v>27.3406805</v>
+      </c>
+      <c r="N37">
+        <v>113.4531970510204</v>
+      </c>
+      <c r="O37">
+        <v>28.3632992627551</v>
+      </c>
+      <c r="P37">
+        <v>85.0898977882653</v>
+      </c>
+      <c r="Q37">
+        <v>113.9898977882653</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1166487187511859</v>
+      </c>
+      <c r="T37">
+        <v>1.122105774561315</v>
+      </c>
+      <c r="U37">
+        <v>0.0509</v>
+      </c>
+      <c r="V37">
+        <v>0.25</v>
+      </c>
+      <c r="W37">
+        <v>0.038175</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>5.149611310918921</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.08903803248364543</v>
+      </c>
+      <c r="C38">
+        <v>991.1847455574996</v>
+      </c>
+      <c r="D38">
+        <v>482.0767455574995</v>
+      </c>
+      <c r="E38">
+        <v>-261.6080000000001</v>
+      </c>
+      <c r="F38">
+        <v>552.492</v>
+      </c>
+      <c r="G38">
+        <v>1061.6</v>
+      </c>
+      <c r="H38">
+        <v>720.6</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K38">
+        <v>28.9</v>
+      </c>
+      <c r="L38">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M38">
+        <v>28.1218428</v>
+      </c>
+      <c r="N38">
+        <v>112.6720347510204</v>
+      </c>
+      <c r="O38">
+        <v>28.1680086877551</v>
+      </c>
+      <c r="P38">
+        <v>84.50402606326531</v>
+      </c>
+      <c r="Q38">
+        <v>113.4040260632653</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.117648488255696</v>
+      </c>
+      <c r="T38">
+        <v>1.136516379542839</v>
+      </c>
+      <c r="U38">
+        <v>0.0509</v>
+      </c>
+      <c r="V38">
+        <v>0.25</v>
+      </c>
+      <c r="W38">
+        <v>0.038175</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>5.006566552282286</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.08889314777902003</v>
+      </c>
+      <c r="C39">
+        <v>976.1363818064905</v>
+      </c>
+      <c r="D39">
+        <v>482.3753818064905</v>
+      </c>
+      <c r="E39">
+        <v>-246.261</v>
+      </c>
+      <c r="F39">
+        <v>567.8390000000001</v>
+      </c>
+      <c r="G39">
+        <v>1061.6</v>
+      </c>
+      <c r="H39">
+        <v>720.6</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K39">
+        <v>28.9</v>
+      </c>
+      <c r="L39">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M39">
+        <v>28.90300510000001</v>
+      </c>
+      <c r="N39">
+        <v>111.8908724510204</v>
+      </c>
+      <c r="O39">
+        <v>27.9727181127551</v>
+      </c>
+      <c r="P39">
+        <v>83.91815433826531</v>
+      </c>
+      <c r="Q39">
+        <v>112.8181543382653</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.118679996474635</v>
+      </c>
+      <c r="T39">
+        <v>1.151384464047585</v>
+      </c>
+      <c r="U39">
+        <v>0.0509</v>
+      </c>
+      <c r="V39">
+        <v>0.25</v>
+      </c>
+      <c r="W39">
+        <v>0.038175</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>4.871253942761141</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.08874826307439464</v>
+      </c>
+      <c r="C40">
+        <v>961.0883882823865</v>
+      </c>
+      <c r="D40">
+        <v>482.6743882823867</v>
+      </c>
+      <c r="E40">
+        <v>-230.914</v>
+      </c>
+      <c r="F40">
+        <v>583.186</v>
+      </c>
+      <c r="G40">
+        <v>1061.6</v>
+      </c>
+      <c r="H40">
+        <v>720.6</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K40">
+        <v>28.9</v>
+      </c>
+      <c r="L40">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M40">
+        <v>29.6841674</v>
+      </c>
+      <c r="N40">
+        <v>111.1097101510204</v>
+      </c>
+      <c r="O40">
+        <v>27.7774275377551</v>
+      </c>
+      <c r="P40">
+        <v>83.33228261326531</v>
+      </c>
+      <c r="Q40">
+        <v>112.2322826132653</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1197447791522494</v>
+      </c>
+      <c r="T40">
+        <v>1.166732164181518</v>
+      </c>
+      <c r="U40">
+        <v>0.0509</v>
+      </c>
+      <c r="V40">
+        <v>0.25</v>
+      </c>
+      <c r="W40">
+        <v>0.038175</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>4.743063049530585</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.08860337836976923</v>
+      </c>
+      <c r="C41">
+        <v>946.0407656740848</v>
+      </c>
+      <c r="D41">
+        <v>482.9737656740848</v>
+      </c>
+      <c r="E41">
+        <v>-215.567</v>
+      </c>
+      <c r="F41">
+        <v>598.533</v>
+      </c>
+      <c r="G41">
+        <v>1061.6</v>
+      </c>
+      <c r="H41">
+        <v>720.6</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K41">
+        <v>28.9</v>
+      </c>
+      <c r="L41">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M41">
+        <v>30.4653297</v>
+      </c>
+      <c r="N41">
+        <v>110.3285478510204</v>
+      </c>
+      <c r="O41">
+        <v>27.5821369627551</v>
+      </c>
+      <c r="P41">
+        <v>82.74641088826532</v>
+      </c>
+      <c r="Q41">
+        <v>111.6464108882653</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1208444727373266</v>
+      </c>
+      <c r="T41">
+        <v>1.182583067598529</v>
+      </c>
+      <c r="U41">
+        <v>0.0509</v>
+      </c>
+      <c r="V41">
+        <v>0.25</v>
+      </c>
+      <c r="W41">
+        <v>0.038175</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>4.621446048260571</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.08845849366514384</v>
+      </c>
+      <c r="C42">
+        <v>930.9935146721911</v>
+      </c>
+      <c r="D42">
+        <v>483.2735146721911</v>
+      </c>
+      <c r="E42">
+        <v>-200.22</v>
+      </c>
+      <c r="F42">
+        <v>613.88</v>
+      </c>
+      <c r="G42">
+        <v>1061.6</v>
+      </c>
+      <c r="H42">
+        <v>720.6</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K42">
+        <v>28.9</v>
+      </c>
+      <c r="L42">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M42">
+        <v>31.246492</v>
+      </c>
+      <c r="N42">
+        <v>109.5473855510204</v>
+      </c>
+      <c r="O42">
+        <v>27.3868463877551</v>
+      </c>
+      <c r="P42">
+        <v>82.16053916326531</v>
+      </c>
+      <c r="Q42">
+        <v>111.0605391632653</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1219808227752397</v>
+      </c>
+      <c r="T42">
+        <v>1.198962334462775</v>
+      </c>
+      <c r="U42">
+        <v>0.0509</v>
+      </c>
+      <c r="V42">
+        <v>0.25</v>
+      </c>
+      <c r="W42">
+        <v>0.038175</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>4.505909897054057</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.08911310896051844</v>
+      </c>
+      <c r="C43">
+        <v>914.2951433777059</v>
+      </c>
+      <c r="D43">
+        <v>481.922143377706</v>
+      </c>
+      <c r="E43">
+        <v>-184.8729999999999</v>
+      </c>
+      <c r="F43">
+        <v>629.2270000000001</v>
+      </c>
+      <c r="G43">
+        <v>1061.6</v>
+      </c>
+      <c r="H43">
+        <v>720.6</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K43">
+        <v>28.9</v>
+      </c>
+      <c r="L43">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M43">
+        <v>33.6636445</v>
+      </c>
+      <c r="N43">
+        <v>107.1302330510204</v>
+      </c>
+      <c r="O43">
+        <v>26.7825582627551</v>
+      </c>
+      <c r="P43">
+        <v>80.34767478826531</v>
+      </c>
+      <c r="Q43">
+        <v>109.2476747882653</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1231556931534211</v>
+      </c>
+      <c r="T43">
+        <v>1.215896830712249</v>
+      </c>
+      <c r="U43">
+        <v>0.0535</v>
+      </c>
+      <c r="V43">
+        <v>0.25</v>
+      </c>
+      <c r="W43">
+        <v>0.040125</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>4.182371803237775</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.08898772425589305</v>
+      </c>
+      <c r="C44">
+        <v>899.2063989252825</v>
+      </c>
+      <c r="D44">
+        <v>482.1803989252827</v>
+      </c>
+      <c r="E44">
+        <v>-169.5260000000001</v>
+      </c>
+      <c r="F44">
+        <v>644.574</v>
+      </c>
+      <c r="G44">
+        <v>1061.6</v>
+      </c>
+      <c r="H44">
+        <v>720.6</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K44">
+        <v>28.9</v>
+      </c>
+      <c r="L44">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M44">
+        <v>34.484709</v>
+      </c>
+      <c r="N44">
+        <v>106.3091685510204</v>
+      </c>
+      <c r="O44">
+        <v>26.57729213775511</v>
+      </c>
+      <c r="P44">
+        <v>79.73187641326531</v>
+      </c>
+      <c r="Q44">
+        <v>108.6318764132653</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1243710763032638</v>
+      </c>
+      <c r="T44">
+        <v>1.233415275108257</v>
+      </c>
+      <c r="U44">
+        <v>0.0535</v>
+      </c>
+      <c r="V44">
+        <v>0.25</v>
+      </c>
+      <c r="W44">
+        <v>0.040125</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>4.082791522208305</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.08973308955126764</v>
+      </c>
+      <c r="C45">
+        <v>882.3282211133323</v>
+      </c>
+      <c r="D45">
+        <v>480.6492211133325</v>
+      </c>
+      <c r="E45">
+        <v>-154.179</v>
+      </c>
+      <c r="F45">
+        <v>659.921</v>
+      </c>
+      <c r="G45">
+        <v>1061.6</v>
+      </c>
+      <c r="H45">
+        <v>720.6</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K45">
+        <v>28.9</v>
+      </c>
+      <c r="L45">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M45">
+        <v>37.08756020000001</v>
+      </c>
+      <c r="N45">
+        <v>103.7063173510204</v>
+      </c>
+      <c r="O45">
+        <v>25.9265793377551</v>
+      </c>
+      <c r="P45">
+        <v>77.7797380132653</v>
+      </c>
+      <c r="Q45">
+        <v>106.6797380132653</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1256291044759081</v>
+      </c>
+      <c r="T45">
+        <v>1.251548401763774</v>
+      </c>
+      <c r="U45">
+        <v>0.0562</v>
+      </c>
+      <c r="V45">
+        <v>0.25</v>
+      </c>
+      <c r="W45">
+        <v>0.04215</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>3.796256124473251</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.08962795484664224</v>
+      </c>
+      <c r="C46">
+        <v>867.1966062938566</v>
+      </c>
+      <c r="D46">
+        <v>480.8646062938568</v>
+      </c>
+      <c r="E46">
+        <v>-138.832</v>
+      </c>
+      <c r="F46">
+        <v>675.268</v>
+      </c>
+      <c r="G46">
+        <v>1061.6</v>
+      </c>
+      <c r="H46">
+        <v>720.6</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K46">
+        <v>28.9</v>
+      </c>
+      <c r="L46">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M46">
+        <v>37.95006160000001</v>
+      </c>
+      <c r="N46">
+        <v>102.8438159510204</v>
+      </c>
+      <c r="O46">
+        <v>25.7109539877551</v>
+      </c>
+      <c r="P46">
+        <v>77.13286196326531</v>
+      </c>
+      <c r="Q46">
+        <v>106.0328619632653</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1269320622261469</v>
+      </c>
+      <c r="T46">
+        <v>1.270329140085559</v>
+      </c>
+      <c r="U46">
+        <v>0.0562</v>
+      </c>
+      <c r="V46">
+        <v>0.25</v>
+      </c>
+      <c r="W46">
+        <v>0.04215</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>3.709977576189768</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.08952282014201683</v>
+      </c>
+      <c r="C47">
+        <v>852.0651845947339</v>
+      </c>
+      <c r="D47">
+        <v>481.0801845947341</v>
+      </c>
+      <c r="E47">
+        <v>-123.485</v>
+      </c>
+      <c r="F47">
+        <v>690.615</v>
+      </c>
+      <c r="G47">
+        <v>1061.6</v>
+      </c>
+      <c r="H47">
+        <v>720.6</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K47">
+        <v>28.9</v>
+      </c>
+      <c r="L47">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M47">
+        <v>38.812563</v>
+      </c>
+      <c r="N47">
+        <v>101.9813145510204</v>
+      </c>
+      <c r="O47">
+        <v>25.4953286377551</v>
+      </c>
+      <c r="P47">
+        <v>76.48598591326531</v>
+      </c>
+      <c r="Q47">
+        <v>105.3859859132653</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1282824002582124</v>
+      </c>
+      <c r="T47">
+        <v>1.289792814346318</v>
+      </c>
+      <c r="U47">
+        <v>0.0562</v>
+      </c>
+      <c r="V47">
+        <v>0.25</v>
+      </c>
+      <c r="W47">
+        <v>0.04215</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>3.627533630052219</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.08941768543739145</v>
+      </c>
+      <c r="C48">
+        <v>836.9339562758163</v>
+      </c>
+      <c r="D48">
+        <v>481.2959562758164</v>
+      </c>
+      <c r="E48">
+        <v>-108.1379999999999</v>
+      </c>
+      <c r="F48">
+        <v>705.9620000000001</v>
+      </c>
+      <c r="G48">
+        <v>1061.6</v>
+      </c>
+      <c r="H48">
+        <v>720.6</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K48">
+        <v>28.9</v>
+      </c>
+      <c r="L48">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M48">
+        <v>39.6750644</v>
+      </c>
+      <c r="N48">
+        <v>101.1188131510204</v>
+      </c>
+      <c r="O48">
+        <v>25.2797032877551</v>
+      </c>
+      <c r="P48">
+        <v>75.83910986326532</v>
+      </c>
+      <c r="Q48">
+        <v>104.7391098632653</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1296827508099841</v>
+      </c>
+      <c r="T48">
+        <v>1.309977365431551</v>
+      </c>
+      <c r="U48">
+        <v>0.0562</v>
+      </c>
+      <c r="V48">
+        <v>0.25</v>
+      </c>
+      <c r="W48">
+        <v>0.04215</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>3.548674203311953</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.09096930073276605</v>
+      </c>
+      <c r="C49">
+        <v>818.4220425884358</v>
+      </c>
+      <c r="D49">
+        <v>478.131042588436</v>
+      </c>
+      <c r="E49">
+        <v>-92.79099999999994</v>
+      </c>
+      <c r="F49">
+        <v>721.3090000000001</v>
+      </c>
+      <c r="G49">
+        <v>1061.6</v>
+      </c>
+      <c r="H49">
+        <v>720.6</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K49">
+        <v>28.9</v>
+      </c>
+      <c r="L49">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M49">
+        <v>43.92771810000001</v>
+      </c>
+      <c r="N49">
+        <v>96.86615945102041</v>
+      </c>
+      <c r="O49">
+        <v>24.2165398627551</v>
+      </c>
+      <c r="P49">
+        <v>72.64961958826531</v>
+      </c>
+      <c r="Q49">
+        <v>101.5496195882653</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1311359447788038</v>
+      </c>
+      <c r="T49">
+        <v>1.33092359768981</v>
+      </c>
+      <c r="U49">
+        <v>0.0609</v>
+      </c>
+      <c r="V49">
+        <v>0.25</v>
+      </c>
+      <c r="W49">
+        <v>0.045675</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>3.205126139958096</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.09089941602814064</v>
+      </c>
+      <c r="C50">
+        <v>803.2166947893247</v>
+      </c>
+      <c r="D50">
+        <v>478.2726947893249</v>
+      </c>
+      <c r="E50">
+        <v>-77.44400000000007</v>
+      </c>
+      <c r="F50">
+        <v>736.6559999999999</v>
+      </c>
+      <c r="G50">
+        <v>1061.6</v>
+      </c>
+      <c r="H50">
+        <v>720.6</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K50">
+        <v>28.9</v>
+      </c>
+      <c r="L50">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M50">
+        <v>44.8623504</v>
+      </c>
+      <c r="N50">
+        <v>95.93152715102042</v>
+      </c>
+      <c r="O50">
+        <v>23.9828817877551</v>
+      </c>
+      <c r="P50">
+        <v>71.94864536326531</v>
+      </c>
+      <c r="Q50">
+        <v>100.8486453632653</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1326450308233474</v>
+      </c>
+      <c r="T50">
+        <v>1.352675454265695</v>
+      </c>
+      <c r="U50">
+        <v>0.0609</v>
+      </c>
+      <c r="V50">
+        <v>0.25</v>
+      </c>
+      <c r="W50">
+        <v>0.045675</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>3.13835267870897</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.09082953132351523</v>
+      </c>
+      <c r="C51">
+        <v>788.0114309474999</v>
+      </c>
+      <c r="D51">
+        <v>478.4144309474999</v>
+      </c>
+      <c r="E51">
+        <v>-62.09699999999998</v>
+      </c>
+      <c r="F51">
+        <v>752.003</v>
+      </c>
+      <c r="G51">
+        <v>1061.6</v>
+      </c>
+      <c r="H51">
+        <v>720.6</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K51">
+        <v>28.9</v>
+      </c>
+      <c r="L51">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M51">
+        <v>45.79698270000001</v>
+      </c>
+      <c r="N51">
+        <v>94.99689485102041</v>
+      </c>
+      <c r="O51">
+        <v>23.7492237127551</v>
+      </c>
+      <c r="P51">
+        <v>71.2476711382653</v>
+      </c>
+      <c r="Q51">
+        <v>100.1476711382653</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.134213296712775</v>
+      </c>
+      <c r="T51">
+        <v>1.375280324824948</v>
+      </c>
+      <c r="U51">
+        <v>0.0609</v>
+      </c>
+      <c r="V51">
+        <v>0.25</v>
+      </c>
+      <c r="W51">
+        <v>0.045675</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>3.074304664857766</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.09075964661888984</v>
+      </c>
+      <c r="C52">
+        <v>772.8062511376255</v>
+      </c>
+      <c r="D52">
+        <v>478.5562511376256</v>
+      </c>
+      <c r="E52">
+        <v>-46.75</v>
+      </c>
+      <c r="F52">
+        <v>767.35</v>
+      </c>
+      <c r="G52">
+        <v>1061.6</v>
+      </c>
+      <c r="H52">
+        <v>720.6</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K52">
+        <v>28.9</v>
+      </c>
+      <c r="L52">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M52">
+        <v>46.73161500000001</v>
+      </c>
+      <c r="N52">
+        <v>94.06226255102041</v>
+      </c>
+      <c r="O52">
+        <v>23.5155656377551</v>
+      </c>
+      <c r="P52">
+        <v>70.54669691326531</v>
+      </c>
+      <c r="Q52">
+        <v>99.4466969132653</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1358442932377797</v>
+      </c>
+      <c r="T52">
+        <v>1.398789390206571</v>
+      </c>
+      <c r="U52">
+        <v>0.0609</v>
+      </c>
+      <c r="V52">
+        <v>0.25</v>
+      </c>
+      <c r="W52">
+        <v>0.045675</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>3.012818571560611</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.09424701191426443</v>
+      </c>
+      <c r="C53">
+        <v>750.4832790456529</v>
+      </c>
+      <c r="D53">
+        <v>471.5802790456531</v>
+      </c>
+      <c r="E53">
+        <v>-31.40300000000002</v>
+      </c>
+      <c r="F53">
+        <v>782.697</v>
+      </c>
+      <c r="G53">
+        <v>1061.6</v>
+      </c>
+      <c r="H53">
+        <v>720.6</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K53">
+        <v>28.9</v>
+      </c>
+      <c r="L53">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M53">
+        <v>54.9453294</v>
+      </c>
+      <c r="N53">
+        <v>85.84854815102042</v>
+      </c>
+      <c r="O53">
+        <v>21.46213703775511</v>
+      </c>
+      <c r="P53">
+        <v>64.38641111326532</v>
+      </c>
+      <c r="Q53">
+        <v>93.28641111326533</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1375418610495193</v>
+      </c>
+      <c r="T53">
+        <v>1.42325800927724</v>
+      </c>
+      <c r="U53">
+        <v>0.0702</v>
+      </c>
+      <c r="V53">
+        <v>0.25</v>
+      </c>
+      <c r="W53">
+        <v>0.05265</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>2.562435771856896</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.09424687720963904</v>
+      </c>
+      <c r="C54">
+        <v>735.1365445750978</v>
+      </c>
+      <c r="D54">
+        <v>471.5805445750981</v>
+      </c>
+      <c r="E54">
+        <v>-16.05599999999993</v>
+      </c>
+      <c r="F54">
+        <v>798.0440000000001</v>
+      </c>
+      <c r="G54">
+        <v>1061.6</v>
+      </c>
+      <c r="H54">
+        <v>720.6</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K54">
+        <v>28.9</v>
+      </c>
+      <c r="L54">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M54">
+        <v>56.0226888</v>
+      </c>
+      <c r="N54">
+        <v>84.77118875102042</v>
+      </c>
+      <c r="O54">
+        <v>21.1927971877551</v>
+      </c>
+      <c r="P54">
+        <v>63.57839156326531</v>
+      </c>
+      <c r="Q54">
+        <v>92.47839156326532</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1393101608534147</v>
+      </c>
+      <c r="T54">
+        <v>1.44874615414252</v>
+      </c>
+      <c r="U54">
+        <v>0.0702</v>
+      </c>
+      <c r="V54">
+        <v>0.25</v>
+      </c>
+      <c r="W54">
+        <v>0.05265</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>2.513158160859648</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.09611499250501365</v>
+      </c>
+      <c r="C55">
+        <v>716.1356500983225</v>
+      </c>
+      <c r="D55">
+        <v>467.9266500983225</v>
+      </c>
+      <c r="E55">
+        <v>-0.7089999999999463</v>
+      </c>
+      <c r="F55">
+        <v>813.3910000000001</v>
+      </c>
+      <c r="G55">
+        <v>1061.6</v>
+      </c>
+      <c r="H55">
+        <v>720.6</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K55">
+        <v>28.9</v>
+      </c>
+      <c r="L55">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M55">
+        <v>60.9229859</v>
+      </c>
+      <c r="N55">
+        <v>79.87089165102041</v>
+      </c>
+      <c r="O55">
+        <v>19.9677229127551</v>
+      </c>
+      <c r="P55">
+        <v>59.90316873826531</v>
+      </c>
+      <c r="Q55">
+        <v>88.8031687382653</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1411537074574759</v>
+      </c>
+      <c r="T55">
+        <v>1.475318900916961</v>
+      </c>
+      <c r="U55">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V55">
+        <v>0.25</v>
+      </c>
+      <c r="W55">
+        <v>0.056175</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>2.311014069174512</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.09615010780038823</v>
+      </c>
+      <c r="C56">
+        <v>700.720509286471</v>
+      </c>
+      <c r="D56">
+        <v>467.8585092864712</v>
+      </c>
+      <c r="E56">
+        <v>14.63800000000003</v>
+      </c>
+      <c r="F56">
+        <v>828.7380000000001</v>
+      </c>
+      <c r="G56">
+        <v>1061.6</v>
+      </c>
+      <c r="H56">
+        <v>720.6</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K56">
+        <v>28.9</v>
+      </c>
+      <c r="L56">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M56">
+        <v>62.0724762</v>
+      </c>
+      <c r="N56">
+        <v>78.72140135102042</v>
+      </c>
+      <c r="O56">
+        <v>19.6803503377551</v>
+      </c>
+      <c r="P56">
+        <v>59.04105101326532</v>
+      </c>
+      <c r="Q56">
+        <v>87.94105101326531</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1430774082617136</v>
+      </c>
+      <c r="T56">
+        <v>1.503046984507682</v>
+      </c>
+      <c r="U56">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V56">
+        <v>0.25</v>
+      </c>
+      <c r="W56">
+        <v>0.056175</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>2.268217512337947</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.09618522309576284</v>
+      </c>
+      <c r="C57">
+        <v>685.3053883174484</v>
+      </c>
+      <c r="D57">
+        <v>467.7903883174485</v>
+      </c>
+      <c r="E57">
+        <v>29.98500000000001</v>
+      </c>
+      <c r="F57">
+        <v>844.085</v>
+      </c>
+      <c r="G57">
+        <v>1061.6</v>
+      </c>
+      <c r="H57">
+        <v>720.6</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K57">
+        <v>28.9</v>
+      </c>
+      <c r="L57">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M57">
+        <v>63.2219665</v>
+      </c>
+      <c r="N57">
+        <v>77.57191105102041</v>
+      </c>
+      <c r="O57">
+        <v>19.3929777627551</v>
+      </c>
+      <c r="P57">
+        <v>58.17893328826531</v>
+      </c>
+      <c r="Q57">
+        <v>87.0789332882653</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.145086606879473</v>
+      </c>
+      <c r="T57">
+        <v>1.532007427369102</v>
+      </c>
+      <c r="U57">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V57">
+        <v>0.25</v>
+      </c>
+      <c r="W57">
+        <v>0.056175</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>2.226977193931802</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.09622033839113743</v>
+      </c>
+      <c r="C58">
+        <v>669.8902871825882</v>
+      </c>
+      <c r="D58">
+        <v>467.7222871825884</v>
+      </c>
+      <c r="E58">
+        <v>45.33200000000011</v>
+      </c>
+      <c r="F58">
+        <v>859.4320000000001</v>
+      </c>
+      <c r="G58">
+        <v>1061.6</v>
+      </c>
+      <c r="H58">
+        <v>720.6</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K58">
+        <v>28.9</v>
+      </c>
+      <c r="L58">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M58">
+        <v>64.3714568</v>
+      </c>
+      <c r="N58">
+        <v>76.42242075102041</v>
+      </c>
+      <c r="O58">
+        <v>19.1056051877551</v>
+      </c>
+      <c r="P58">
+        <v>57.31681556326531</v>
+      </c>
+      <c r="Q58">
+        <v>86.2168155632653</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1471871327071305</v>
+      </c>
+      <c r="T58">
+        <v>1.562284253996949</v>
+      </c>
+      <c r="U58">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V58">
+        <v>0.25</v>
+      </c>
+      <c r="W58">
+        <v>0.056175</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>2.187209744040163</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.09625545368651203</v>
+      </c>
+      <c r="C59">
+        <v>654.4752058732296</v>
+      </c>
+      <c r="D59">
+        <v>467.6542058732297</v>
+      </c>
+      <c r="E59">
+        <v>60.67900000000009</v>
+      </c>
+      <c r="F59">
+        <v>874.7790000000001</v>
+      </c>
+      <c r="G59">
+        <v>1061.6</v>
+      </c>
+      <c r="H59">
+        <v>720.6</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K59">
+        <v>28.9</v>
+      </c>
+      <c r="L59">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M59">
+        <v>65.5209471</v>
+      </c>
+      <c r="N59">
+        <v>75.27293045102041</v>
+      </c>
+      <c r="O59">
+        <v>18.8182326127551</v>
+      </c>
+      <c r="P59">
+        <v>56.45469783826531</v>
+      </c>
+      <c r="Q59">
+        <v>85.35469783826531</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1493853574104931</v>
+      </c>
+      <c r="T59">
+        <v>1.593969305119116</v>
+      </c>
+      <c r="U59">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V59">
+        <v>0.25</v>
+      </c>
+      <c r="W59">
+        <v>0.056175</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>2.148837643267528</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.09629056898188665</v>
+      </c>
+      <c r="C60">
+        <v>639.0601443807161</v>
+      </c>
+      <c r="D60">
+        <v>467.5861443807162</v>
+      </c>
+      <c r="E60">
+        <v>76.02599999999995</v>
+      </c>
+      <c r="F60">
+        <v>890.126</v>
+      </c>
+      <c r="G60">
+        <v>1061.6</v>
+      </c>
+      <c r="H60">
+        <v>720.6</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K60">
+        <v>28.9</v>
+      </c>
+      <c r="L60">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M60">
+        <v>66.6704374</v>
+      </c>
+      <c r="N60">
+        <v>74.12344015102042</v>
+      </c>
+      <c r="O60">
+        <v>18.5308600377551</v>
+      </c>
+      <c r="P60">
+        <v>55.59258011326531</v>
+      </c>
+      <c r="Q60">
+        <v>84.49258011326532</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1516882594806825</v>
+      </c>
+      <c r="T60">
+        <v>1.62716316819948</v>
+      </c>
+      <c r="U60">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V60">
+        <v>0.25</v>
+      </c>
+      <c r="W60">
+        <v>0.056175</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>2.111788718383606</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.09632568427726124</v>
+      </c>
+      <c r="C61">
+        <v>623.6451026963971</v>
+      </c>
+      <c r="D61">
+        <v>467.5181026963971</v>
+      </c>
+      <c r="E61">
+        <v>91.37299999999993</v>
+      </c>
+      <c r="F61">
+        <v>905.473</v>
+      </c>
+      <c r="G61">
+        <v>1061.6</v>
+      </c>
+      <c r="H61">
+        <v>720.6</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K61">
+        <v>28.9</v>
+      </c>
+      <c r="L61">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M61">
+        <v>67.81992769999999</v>
+      </c>
+      <c r="N61">
+        <v>72.97394985102042</v>
+      </c>
+      <c r="O61">
+        <v>18.24348746275511</v>
+      </c>
+      <c r="P61">
+        <v>54.73046238826532</v>
+      </c>
+      <c r="Q61">
+        <v>83.63046238826531</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.1541034982372225</v>
+      </c>
+      <c r="T61">
+        <v>1.661976244113033</v>
+      </c>
+      <c r="U61">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V61">
+        <v>0.25</v>
+      </c>
+      <c r="W61">
+        <v>0.056175</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>2.07599568925846</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.09636079957263584</v>
+      </c>
+      <c r="C62">
+        <v>608.2300808116262</v>
+      </c>
+      <c r="D62">
+        <v>467.4500808116262</v>
+      </c>
+      <c r="E62">
+        <v>106.72</v>
+      </c>
+      <c r="F62">
+        <v>920.8200000000001</v>
+      </c>
+      <c r="G62">
+        <v>1061.6</v>
+      </c>
+      <c r="H62">
+        <v>720.6</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K62">
+        <v>28.9</v>
+      </c>
+      <c r="L62">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M62">
+        <v>68.969418</v>
+      </c>
+      <c r="N62">
+        <v>71.82445955102041</v>
+      </c>
+      <c r="O62">
+        <v>17.9561148877551</v>
+      </c>
+      <c r="P62">
+        <v>53.8683446632653</v>
+      </c>
+      <c r="Q62">
+        <v>82.76834466326531</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.1566394989315896</v>
+      </c>
+      <c r="T62">
+        <v>1.698529973822265</v>
+      </c>
+      <c r="U62">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V62">
+        <v>0.25</v>
+      </c>
+      <c r="W62">
+        <v>0.056175</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>2.041395761104152</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.09639591486801044</v>
+      </c>
+      <c r="C63">
+        <v>592.8150787177623</v>
+      </c>
+      <c r="D63">
+        <v>467.3820787177625</v>
+      </c>
+      <c r="E63">
+        <v>122.067</v>
+      </c>
+      <c r="F63">
+        <v>936.167</v>
+      </c>
+      <c r="G63">
+        <v>1061.6</v>
+      </c>
+      <c r="H63">
+        <v>720.6</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K63">
+        <v>28.9</v>
+      </c>
+      <c r="L63">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M63">
+        <v>70.1189083</v>
+      </c>
+      <c r="N63">
+        <v>70.67496925102041</v>
+      </c>
+      <c r="O63">
+        <v>17.6687423127551</v>
+      </c>
+      <c r="P63">
+        <v>53.00622693826531</v>
+      </c>
+      <c r="Q63">
+        <v>81.90622693826532</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.1593055509436165</v>
+      </c>
+      <c r="T63">
+        <v>1.736958253772995</v>
+      </c>
+      <c r="U63">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V63">
+        <v>0.25</v>
+      </c>
+      <c r="W63">
+        <v>0.056175</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>2.007930256823756</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.104010530163385</v>
+      </c>
+      <c r="C64">
+        <v>563.1751142120494</v>
+      </c>
+      <c r="D64">
+        <v>453.0891142120496</v>
+      </c>
+      <c r="E64">
+        <v>137.414</v>
+      </c>
+      <c r="F64">
+        <v>951.514</v>
+      </c>
+      <c r="G64">
+        <v>1061.6</v>
+      </c>
+      <c r="H64">
+        <v>720.6</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K64">
+        <v>28.9</v>
+      </c>
+      <c r="L64">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M64">
+        <v>86.77807680000001</v>
+      </c>
+      <c r="N64">
+        <v>54.01580075102041</v>
+      </c>
+      <c r="O64">
+        <v>13.5039501877551</v>
+      </c>
+      <c r="P64">
+        <v>40.51185056326531</v>
+      </c>
+      <c r="Q64">
+        <v>69.4118505632653</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.1621119214825922</v>
+      </c>
+      <c r="T64">
+        <v>1.777409074773763</v>
+      </c>
+      <c r="U64">
+        <v>0.0912</v>
+      </c>
+      <c r="V64">
+        <v>0.25</v>
+      </c>
+      <c r="W64">
+        <v>0.0684</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>1.622459067346148</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.1041678954587597</v>
+      </c>
+      <c r="C65">
+        <v>547.541946587725</v>
+      </c>
+      <c r="D65">
+        <v>452.802946587725</v>
+      </c>
+      <c r="E65">
+        <v>152.761</v>
+      </c>
+      <c r="F65">
+        <v>966.861</v>
+      </c>
+      <c r="G65">
+        <v>1061.6</v>
+      </c>
+      <c r="H65">
+        <v>720.6</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K65">
+        <v>28.9</v>
+      </c>
+      <c r="L65">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M65">
+        <v>88.1777232</v>
+      </c>
+      <c r="N65">
+        <v>52.61615435102041</v>
+      </c>
+      <c r="O65">
+        <v>13.1540385877551</v>
+      </c>
+      <c r="P65">
+        <v>39.46211576326531</v>
+      </c>
+      <c r="Q65">
+        <v>68.36211576326531</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.1650699877263774</v>
+      </c>
+      <c r="T65">
+        <v>1.820046426639438</v>
+      </c>
+      <c r="U65">
+        <v>0.0912</v>
+      </c>
+      <c r="V65">
+        <v>0.25</v>
+      </c>
+      <c r="W65">
+        <v>0.0684</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>1.596705748816844</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.1043252607541343</v>
+      </c>
+      <c r="C66">
+        <v>531.9091402178069</v>
+      </c>
+      <c r="D66">
+        <v>452.5171402178071</v>
+      </c>
+      <c r="E66">
+        <v>168.1080000000001</v>
+      </c>
+      <c r="F66">
+        <v>982.2080000000001</v>
+      </c>
+      <c r="G66">
+        <v>1061.6</v>
+      </c>
+      <c r="H66">
+        <v>720.6</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K66">
+        <v>28.9</v>
+      </c>
+      <c r="L66">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M66">
+        <v>89.57736960000001</v>
+      </c>
+      <c r="N66">
+        <v>51.2165079510204</v>
+      </c>
+      <c r="O66">
+        <v>12.8041269877551</v>
+      </c>
+      <c r="P66">
+        <v>38.41238096326531</v>
+      </c>
+      <c r="Q66">
+        <v>67.3123809632653</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.1681923909837063</v>
+      </c>
+      <c r="T66">
+        <v>1.865052520275428</v>
+      </c>
+      <c r="U66">
+        <v>0.0912</v>
+      </c>
+      <c r="V66">
+        <v>0.25</v>
+      </c>
+      <c r="W66">
+        <v>0.0684</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>1.571757221491581</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.1044826260495089</v>
+      </c>
+      <c r="C67">
+        <v>516.2766944186626</v>
+      </c>
+      <c r="D67">
+        <v>452.2316944186629</v>
+      </c>
+      <c r="E67">
+        <v>183.455</v>
+      </c>
+      <c r="F67">
+        <v>997.5550000000001</v>
+      </c>
+      <c r="G67">
+        <v>1061.6</v>
+      </c>
+      <c r="H67">
+        <v>720.6</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K67">
+        <v>28.9</v>
+      </c>
+      <c r="L67">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M67">
+        <v>90.97701600000001</v>
+      </c>
+      <c r="N67">
+        <v>49.81686155102041</v>
+      </c>
+      <c r="O67">
+        <v>12.4542153877551</v>
+      </c>
+      <c r="P67">
+        <v>37.36264616326531</v>
+      </c>
+      <c r="Q67">
+        <v>66.26264616326532</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.171493217284311</v>
+      </c>
+      <c r="T67">
+        <v>1.912630390690617</v>
+      </c>
+      <c r="U67">
+        <v>0.0912</v>
+      </c>
+      <c r="V67">
+        <v>0.25</v>
+      </c>
+      <c r="W67">
+        <v>0.0684</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>1.547576341160941</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.1046399913448834</v>
+      </c>
+      <c r="C68">
+        <v>500.6446085083828</v>
+      </c>
+      <c r="D68">
+        <v>451.946608508383</v>
+      </c>
+      <c r="E68">
+        <v>198.802</v>
+      </c>
+      <c r="F68">
+        <v>1012.902</v>
+      </c>
+      <c r="G68">
+        <v>1061.6</v>
+      </c>
+      <c r="H68">
+        <v>720.6</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K68">
+        <v>28.9</v>
+      </c>
+      <c r="L68">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M68">
+        <v>92.3766624</v>
+      </c>
+      <c r="N68">
+        <v>48.41721515102041</v>
+      </c>
+      <c r="O68">
+        <v>12.1043037877551</v>
+      </c>
+      <c r="P68">
+        <v>36.31291136326531</v>
+      </c>
+      <c r="Q68">
+        <v>65.21291136326531</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.1749882098378925</v>
+      </c>
+      <c r="T68">
+        <v>1.963006959365524</v>
+      </c>
+      <c r="U68">
+        <v>0.0912</v>
+      </c>
+      <c r="V68">
+        <v>0.25</v>
+      </c>
+      <c r="W68">
+        <v>0.0684</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>1.524128214779715</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.104797356640258</v>
+      </c>
+      <c r="C69">
+        <v>485.0128818067767</v>
+      </c>
+      <c r="D69">
+        <v>451.6618818067768</v>
+      </c>
+      <c r="E69">
+        <v>214.149</v>
+      </c>
+      <c r="F69">
+        <v>1028.249</v>
+      </c>
+      <c r="G69">
+        <v>1061.6</v>
+      </c>
+      <c r="H69">
+        <v>720.6</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K69">
+        <v>28.9</v>
+      </c>
+      <c r="L69">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M69">
+        <v>93.77630880000001</v>
+      </c>
+      <c r="N69">
+        <v>47.01756875102041</v>
+      </c>
+      <c r="O69">
+        <v>11.7543921877551</v>
+      </c>
+      <c r="P69">
+        <v>35.2631765632653</v>
+      </c>
+      <c r="Q69">
+        <v>64.1631765632653</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.1786950201219941</v>
+      </c>
+      <c r="T69">
+        <v>2.016436653414667</v>
+      </c>
+      <c r="U69">
+        <v>0.0912</v>
+      </c>
+      <c r="V69">
+        <v>0.25</v>
+      </c>
+      <c r="W69">
+        <v>0.0684</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>1.50138003246957</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.1433012213371892</v>
+      </c>
+      <c r="C70">
+        <v>409.3421001951006</v>
+      </c>
+      <c r="D70">
+        <v>391.3381001951008</v>
+      </c>
+      <c r="E70">
+        <v>229.496</v>
+      </c>
+      <c r="F70">
+        <v>1043.596</v>
+      </c>
+      <c r="G70">
+        <v>1061.6</v>
+      </c>
+      <c r="H70">
+        <v>720.6</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K70">
+        <v>28.9</v>
+      </c>
+      <c r="L70">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M70">
+        <v>163.4271336</v>
+      </c>
+      <c r="N70">
+        <v>-22.6332560489796</v>
+      </c>
+      <c r="O70">
+        <v>-5.658314012244901</v>
+      </c>
+      <c r="P70">
+        <v>-16.9749420367347</v>
+      </c>
+      <c r="Q70">
+        <v>11.9250579632653</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.1867134459787324</v>
+      </c>
+      <c r="T70">
+        <v>2.132013660988742</v>
+      </c>
+      <c r="U70">
+        <v>0.1566</v>
+      </c>
+      <c r="V70">
+        <v>0.2153771446172822</v>
+      </c>
+      <c r="W70">
+        <v>0.1228719391529336</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.8615085784691288</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.1444792213371892</v>
+      </c>
+      <c r="C71">
+        <v>392.4025349428803</v>
+      </c>
+      <c r="D71">
+        <v>389.7455349428806</v>
+      </c>
+      <c r="E71">
+        <v>244.8430000000002</v>
+      </c>
+      <c r="F71">
+        <v>1058.943</v>
+      </c>
+      <c r="G71">
+        <v>1061.6</v>
+      </c>
+      <c r="H71">
+        <v>720.6</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K71">
+        <v>28.9</v>
+      </c>
+      <c r="L71">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M71">
+        <v>165.8304738</v>
+      </c>
+      <c r="N71">
+        <v>-25.03659624897963</v>
+      </c>
+      <c r="O71">
+        <v>-6.259149062244909</v>
+      </c>
+      <c r="P71">
+        <v>-18.77744718673473</v>
+      </c>
+      <c r="Q71">
+        <v>10.12255281326527</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.1914848474619173</v>
+      </c>
+      <c r="T71">
+        <v>2.200788295214185</v>
+      </c>
+      <c r="U71">
+        <v>0.1566</v>
+      </c>
+      <c r="V71">
+        <v>0.2122557367242781</v>
+      </c>
+      <c r="W71">
+        <v>0.1233607516289781</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.8490229468971123</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.1456572213371892</v>
+      </c>
+      <c r="C72">
+        <v>375.4758791645477</v>
+      </c>
+      <c r="D72">
+        <v>388.1658791645479</v>
+      </c>
+      <c r="E72">
+        <v>260.1900000000002</v>
+      </c>
+      <c r="F72">
+        <v>1074.29</v>
+      </c>
+      <c r="G72">
+        <v>1061.6</v>
+      </c>
+      <c r="H72">
+        <v>720.6</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K72">
+        <v>28.9</v>
+      </c>
+      <c r="L72">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M72">
+        <v>168.2338140000001</v>
+      </c>
+      <c r="N72">
+        <v>-27.43993644897964</v>
+      </c>
+      <c r="O72">
+        <v>-6.859984112244909</v>
+      </c>
+      <c r="P72">
+        <v>-20.57995233673473</v>
+      </c>
+      <c r="Q72">
+        <v>8.320047663265271</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.1965743423773146</v>
+      </c>
+      <c r="T72">
+        <v>2.274147905054658</v>
+      </c>
+      <c r="U72">
+        <v>0.1566</v>
+      </c>
+      <c r="V72">
+        <v>0.2092235119139312</v>
+      </c>
+      <c r="W72">
+        <v>0.1238355980342784</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.8368940476557249</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.1468352213371892</v>
+      </c>
+      <c r="C73">
+        <v>358.5619765257379</v>
+      </c>
+      <c r="D73">
+        <v>386.598976525738</v>
+      </c>
+      <c r="E73">
+        <v>275.5369999999999</v>
+      </c>
+      <c r="F73">
+        <v>1089.637</v>
+      </c>
+      <c r="G73">
+        <v>1061.6</v>
+      </c>
+      <c r="H73">
+        <v>720.6</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K73">
+        <v>28.9</v>
+      </c>
+      <c r="L73">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M73">
+        <v>170.6371542</v>
+      </c>
+      <c r="N73">
+        <v>-29.84327664897958</v>
+      </c>
+      <c r="O73">
+        <v>-7.460819162244896</v>
+      </c>
+      <c r="P73">
+        <v>-22.38245748673469</v>
+      </c>
+      <c r="Q73">
+        <v>6.517542513265312</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.2020148369420495</v>
+      </c>
+      <c r="T73">
+        <v>2.352566798332404</v>
+      </c>
+      <c r="U73">
+        <v>0.1566</v>
+      </c>
+      <c r="V73">
+        <v>0.2062767018869745</v>
+      </c>
+      <c r="W73">
+        <v>0.1242970684844998</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.8251068075478981</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.1480132213371892</v>
+      </c>
+      <c r="C74">
+        <v>341.6606732062264</v>
+      </c>
+      <c r="D74">
+        <v>385.0446732062265</v>
+      </c>
+      <c r="E74">
+        <v>290.8839999999999</v>
+      </c>
+      <c r="F74">
+        <v>1104.984</v>
+      </c>
+      <c r="G74">
+        <v>1061.6</v>
+      </c>
+      <c r="H74">
+        <v>720.6</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K74">
+        <v>28.9</v>
+      </c>
+      <c r="L74">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M74">
+        <v>173.0404944</v>
+      </c>
+      <c r="N74">
+        <v>-32.24661684897958</v>
+      </c>
+      <c r="O74">
+        <v>-8.061654212244896</v>
+      </c>
+      <c r="P74">
+        <v>-24.18496263673469</v>
+      </c>
+      <c r="Q74">
+        <v>4.71503736326531</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.2078439382614084</v>
+      </c>
+      <c r="T74">
+        <v>2.43658704112999</v>
+      </c>
+      <c r="U74">
+        <v>0.1566</v>
+      </c>
+      <c r="V74">
+        <v>0.2034117476940999</v>
+      </c>
+      <c r="W74">
+        <v>0.124745720311104</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.8136469907763996</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.1491912213371892</v>
+      </c>
+      <c r="C75">
+        <v>324.771817849592</v>
+      </c>
+      <c r="D75">
+        <v>383.502817849592</v>
+      </c>
+      <c r="E75">
+        <v>306.2309999999999</v>
+      </c>
+      <c r="F75">
+        <v>1120.331</v>
+      </c>
+      <c r="G75">
+        <v>1061.6</v>
+      </c>
+      <c r="H75">
+        <v>720.6</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K75">
+        <v>28.9</v>
+      </c>
+      <c r="L75">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M75">
+        <v>175.4438346</v>
+      </c>
+      <c r="N75">
+        <v>-34.64995704897959</v>
+      </c>
+      <c r="O75">
+        <v>-8.662489262244897</v>
+      </c>
+      <c r="P75">
+        <v>-25.98746778673469</v>
+      </c>
+      <c r="Q75">
+        <v>2.912532213265308</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.2141048248636828</v>
+      </c>
+      <c r="T75">
+        <v>2.526831005616286</v>
+      </c>
+      <c r="U75">
+        <v>0.1566</v>
+      </c>
+      <c r="V75">
+        <v>0.2006252853969204</v>
+      </c>
+      <c r="W75">
+        <v>0.1251820803068423</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.8025011415876817</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.1910276161214306</v>
+      </c>
+      <c r="C76">
+        <v>261.6759954038346</v>
+      </c>
+      <c r="D76">
+        <v>335.7539954038347</v>
+      </c>
+      <c r="E76">
+        <v>321.5780000000001</v>
+      </c>
+      <c r="F76">
+        <v>1135.678</v>
+      </c>
+      <c r="G76">
+        <v>1061.6</v>
+      </c>
+      <c r="H76">
+        <v>720.6</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K76">
+        <v>28.9</v>
+      </c>
+      <c r="L76">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M76">
+        <v>237.1295664</v>
+      </c>
+      <c r="N76">
+        <v>-96.33568884897963</v>
+      </c>
+      <c r="O76">
+        <v>-24.08392221224491</v>
+      </c>
+      <c r="P76">
+        <v>-72.25176663673471</v>
+      </c>
+      <c r="Q76">
+        <v>-43.35176663673472</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.2286565288362912</v>
+      </c>
+      <c r="T76">
+        <v>2.736578209158053</v>
+      </c>
+      <c r="U76">
+        <v>0.2088</v>
+      </c>
+      <c r="V76">
+        <v>0.1484355996686675</v>
+      </c>
+      <c r="W76">
+        <v>0.1778066467891822</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.5937423986746698</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.1927276161214306</v>
+      </c>
+      <c r="C77">
+        <v>244.6388725028312</v>
+      </c>
+      <c r="D77">
+        <v>334.0638725028314</v>
+      </c>
+      <c r="E77">
+        <v>336.9250000000001</v>
+      </c>
+      <c r="F77">
+        <v>1151.025</v>
+      </c>
+      <c r="G77">
+        <v>1061.6</v>
+      </c>
+      <c r="H77">
+        <v>720.6</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K77">
+        <v>28.9</v>
+      </c>
+      <c r="L77">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M77">
+        <v>240.33402</v>
+      </c>
+      <c r="N77">
+        <v>-99.54014244897962</v>
+      </c>
+      <c r="O77">
+        <v>-24.88503561224491</v>
+      </c>
+      <c r="P77">
+        <v>-74.65510683673472</v>
+      </c>
+      <c r="Q77">
+        <v>-45.75510683673472</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.2362507899897429</v>
+      </c>
+      <c r="T77">
+        <v>2.846041337524375</v>
+      </c>
+      <c r="U77">
+        <v>0.2088</v>
+      </c>
+      <c r="V77">
+        <v>0.1464564583397519</v>
+      </c>
+      <c r="W77">
+        <v>0.1782198914986598</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.5858258333590076</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.1944276161214306</v>
+      </c>
+      <c r="C78">
+        <v>227.6186799038576</v>
+      </c>
+      <c r="D78">
+        <v>332.3906799038578</v>
+      </c>
+      <c r="E78">
+        <v>352.272</v>
+      </c>
+      <c r="F78">
+        <v>1166.372</v>
+      </c>
+      <c r="G78">
+        <v>1061.6</v>
+      </c>
+      <c r="H78">
+        <v>720.6</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K78">
+        <v>28.9</v>
+      </c>
+      <c r="L78">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M78">
+        <v>243.5384736</v>
+      </c>
+      <c r="N78">
+        <v>-102.7445960489796</v>
+      </c>
+      <c r="O78">
+        <v>-25.6861490122449</v>
+      </c>
+      <c r="P78">
+        <v>-77.05844703673472</v>
+      </c>
+      <c r="Q78">
+        <v>-48.15844703673472</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.2444779062393155</v>
+      </c>
+      <c r="T78">
+        <v>2.964626393254558</v>
+      </c>
+      <c r="U78">
+        <v>0.2088</v>
+      </c>
+      <c r="V78">
+        <v>0.1445293996773867</v>
+      </c>
+      <c r="W78">
+        <v>0.1786222613473616</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.578117598709547</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.1961276161214306</v>
+      </c>
+      <c r="C79">
+        <v>210.6151644833326</v>
+      </c>
+      <c r="D79">
+        <v>330.7341644833328</v>
+      </c>
+      <c r="E79">
+        <v>367.619</v>
+      </c>
+      <c r="F79">
+        <v>1181.719</v>
+      </c>
+      <c r="G79">
+        <v>1061.6</v>
+      </c>
+      <c r="H79">
+        <v>720.6</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K79">
+        <v>28.9</v>
+      </c>
+      <c r="L79">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M79">
+        <v>246.7429272</v>
+      </c>
+      <c r="N79">
+        <v>-105.9490496489796</v>
+      </c>
+      <c r="O79">
+        <v>-26.4872624122449</v>
+      </c>
+      <c r="P79">
+        <v>-79.46178723673471</v>
+      </c>
+      <c r="Q79">
+        <v>-50.56178723673471</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.2534204239018945</v>
+      </c>
+      <c r="T79">
+        <v>3.093523192961277</v>
+      </c>
+      <c r="U79">
+        <v>0.2088</v>
+      </c>
+      <c r="V79">
+        <v>0.1426523944867713</v>
+      </c>
+      <c r="W79">
+        <v>0.1790141800311622</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.5706095779470853</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.1978276161214306</v>
+      </c>
+      <c r="C80">
+        <v>193.6280781385601</v>
+      </c>
+      <c r="D80">
+        <v>329.0940781385602</v>
+      </c>
+      <c r="E80">
+        <v>382.966</v>
+      </c>
+      <c r="F80">
+        <v>1197.066</v>
+      </c>
+      <c r="G80">
+        <v>1061.6</v>
+      </c>
+      <c r="H80">
+        <v>720.6</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K80">
+        <v>28.9</v>
+      </c>
+      <c r="L80">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M80">
+        <v>249.9473808</v>
+      </c>
+      <c r="N80">
+        <v>-109.1535032489796</v>
+      </c>
+      <c r="O80">
+        <v>-27.2883758122449</v>
+      </c>
+      <c r="P80">
+        <v>-81.8651274367347</v>
+      </c>
+      <c r="Q80">
+        <v>-52.9651274367347</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.2631758977156169</v>
+      </c>
+      <c r="T80">
+        <v>3.234137883550427</v>
+      </c>
+      <c r="U80">
+        <v>0.2088</v>
+      </c>
+      <c r="V80">
+        <v>0.1408235176343768</v>
+      </c>
+      <c r="W80">
+        <v>0.1793960495179421</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.5632940705375074</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.1995276161214306</v>
+      </c>
+      <c r="C81">
+        <v>176.6571776638518</v>
+      </c>
+      <c r="D81">
+        <v>327.4701776638519</v>
+      </c>
+      <c r="E81">
+        <v>398.313</v>
+      </c>
+      <c r="F81">
+        <v>1212.413</v>
+      </c>
+      <c r="G81">
+        <v>1061.6</v>
+      </c>
+      <c r="H81">
+        <v>720.6</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K81">
+        <v>28.9</v>
+      </c>
+      <c r="L81">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M81">
+        <v>253.1518344</v>
+      </c>
+      <c r="N81">
+        <v>-112.3579568489796</v>
+      </c>
+      <c r="O81">
+        <v>-28.0894892122449</v>
+      </c>
+      <c r="P81">
+        <v>-84.2684676367347</v>
+      </c>
+      <c r="Q81">
+        <v>-55.3684676367347</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.2738604642735035</v>
+      </c>
+      <c r="T81">
+        <v>3.38814444943378</v>
+      </c>
+      <c r="U81">
+        <v>0.2088</v>
+      </c>
+      <c r="V81">
+        <v>0.1390409414617898</v>
+      </c>
+      <c r="W81">
+        <v>0.1797682514227783</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.5561637658471592</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2012276161214306</v>
+      </c>
+      <c r="C82">
+        <v>159.7022246303006</v>
+      </c>
+      <c r="D82">
+        <v>325.8622246303007</v>
+      </c>
+      <c r="E82">
+        <v>413.66</v>
+      </c>
+      <c r="F82">
+        <v>1227.76</v>
+      </c>
+      <c r="G82">
+        <v>1061.6</v>
+      </c>
+      <c r="H82">
+        <v>720.6</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K82">
+        <v>28.9</v>
+      </c>
+      <c r="L82">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M82">
+        <v>256.356288</v>
+      </c>
+      <c r="N82">
+        <v>-115.5624104489796</v>
+      </c>
+      <c r="O82">
+        <v>-28.8906026122449</v>
+      </c>
+      <c r="P82">
+        <v>-86.6718078367347</v>
+      </c>
+      <c r="Q82">
+        <v>-57.7718078367347</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.2856134874871786</v>
+      </c>
+      <c r="T82">
+        <v>3.557551671905469</v>
+      </c>
+      <c r="U82">
+        <v>0.2088</v>
+      </c>
+      <c r="V82">
+        <v>0.1373029296935174</v>
+      </c>
+      <c r="W82">
+        <v>0.1801311482799936</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.5492117187740697</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2029276161214306</v>
+      </c>
+      <c r="C83">
+        <v>142.7629852690775</v>
+      </c>
+      <c r="D83">
+        <v>324.2699852690778</v>
+      </c>
+      <c r="E83">
+        <v>429.0070000000002</v>
+      </c>
+      <c r="F83">
+        <v>1243.107</v>
+      </c>
+      <c r="G83">
+        <v>1061.6</v>
+      </c>
+      <c r="H83">
+        <v>720.6</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K83">
+        <v>28.9</v>
+      </c>
+      <c r="L83">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M83">
+        <v>259.5607416000001</v>
+      </c>
+      <c r="N83">
+        <v>-118.7668640489797</v>
+      </c>
+      <c r="O83">
+        <v>-29.69171601224492</v>
+      </c>
+      <c r="P83">
+        <v>-89.07514803673476</v>
+      </c>
+      <c r="Q83">
+        <v>-60.17514803673476</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.2986036710391354</v>
+      </c>
+      <c r="T83">
+        <v>3.744791233584705</v>
+      </c>
+      <c r="U83">
+        <v>0.2088</v>
+      </c>
+      <c r="V83">
+        <v>0.1356078317960666</v>
+      </c>
+      <c r="W83">
+        <v>0.1804850847209813</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.5424313271842662</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2046276161214306</v>
+      </c>
+      <c r="C84">
+        <v>125.8392303581354</v>
+      </c>
+      <c r="D84">
+        <v>322.6932303581356</v>
+      </c>
+      <c r="E84">
+        <v>444.3540000000002</v>
+      </c>
+      <c r="F84">
+        <v>1258.454</v>
+      </c>
+      <c r="G84">
+        <v>1061.6</v>
+      </c>
+      <c r="H84">
+        <v>720.6</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K84">
+        <v>28.9</v>
+      </c>
+      <c r="L84">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M84">
+        <v>262.7651952000001</v>
+      </c>
+      <c r="N84">
+        <v>-121.9713176489796</v>
+      </c>
+      <c r="O84">
+        <v>-30.49282941224491</v>
+      </c>
+      <c r="P84">
+        <v>-91.47848823673473</v>
+      </c>
+      <c r="Q84">
+        <v>-62.57848823673474</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.3130372083190874</v>
+      </c>
+      <c r="T84">
+        <v>3.952835191006077</v>
+      </c>
+      <c r="U84">
+        <v>0.2088</v>
+      </c>
+      <c r="V84">
+        <v>0.1339540777497731</v>
+      </c>
+      <c r="W84">
+        <v>0.1808303885658474</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.5358163109990923</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2063276161214306</v>
+      </c>
+      <c r="C85">
+        <v>108.930735112199</v>
+      </c>
+      <c r="D85">
+        <v>321.1317351121992</v>
+      </c>
+      <c r="E85">
+        <v>459.7010000000001</v>
+      </c>
+      <c r="F85">
+        <v>1273.801</v>
+      </c>
+      <c r="G85">
+        <v>1061.6</v>
+      </c>
+      <c r="H85">
+        <v>720.6</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K85">
+        <v>28.9</v>
+      </c>
+      <c r="L85">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M85">
+        <v>265.9696488000001</v>
+      </c>
+      <c r="N85">
+        <v>-125.1757712489797</v>
+      </c>
+      <c r="O85">
+        <v>-31.29394281224491</v>
+      </c>
+      <c r="P85">
+        <v>-93.88182843673474</v>
+      </c>
+      <c r="Q85">
+        <v>-64.98182843673473</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.3291688088084455</v>
+      </c>
+      <c r="T85">
+        <v>4.185354908124083</v>
+      </c>
+      <c r="U85">
+        <v>0.2088</v>
+      </c>
+      <c r="V85">
+        <v>0.132340173198571</v>
+      </c>
+      <c r="W85">
+        <v>0.1811673718361384</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.5293606927942839</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2080276161214306</v>
+      </c>
+      <c r="C86">
+        <v>92.03727907593679</v>
+      </c>
+      <c r="D86">
+        <v>319.5852790759368</v>
+      </c>
+      <c r="E86">
+        <v>475.0479999999999</v>
+      </c>
+      <c r="F86">
+        <v>1289.148</v>
+      </c>
+      <c r="G86">
+        <v>1061.6</v>
+      </c>
+      <c r="H86">
+        <v>720.6</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K86">
+        <v>28.9</v>
+      </c>
+      <c r="L86">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M86">
+        <v>269.1741024</v>
+      </c>
+      <c r="N86">
+        <v>-128.3802248489796</v>
+      </c>
+      <c r="O86">
+        <v>-32.09505621224489</v>
+      </c>
+      <c r="P86">
+        <v>-96.28516863673468</v>
+      </c>
+      <c r="Q86">
+        <v>-67.38516863673468</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.3473168593589732</v>
+      </c>
+      <c r="T86">
+        <v>4.446939589881835</v>
+      </c>
+      <c r="U86">
+        <v>0.2088</v>
+      </c>
+      <c r="V86">
+        <v>0.1307646949462071</v>
+      </c>
+      <c r="W86">
+        <v>0.181496331695232</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.5230587797848283</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2097276161214306</v>
+      </c>
+      <c r="C87">
+        <v>75.15864602020201</v>
+      </c>
+      <c r="D87">
+        <v>318.0536460202023</v>
+      </c>
+      <c r="E87">
+        <v>490.3950000000001</v>
+      </c>
+      <c r="F87">
+        <v>1304.495</v>
+      </c>
+      <c r="G87">
+        <v>1061.6</v>
+      </c>
+      <c r="H87">
+        <v>720.6</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K87">
+        <v>28.9</v>
+      </c>
+      <c r="L87">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M87">
+        <v>272.3785560000001</v>
+      </c>
+      <c r="N87">
+        <v>-131.5846784489796</v>
+      </c>
+      <c r="O87">
+        <v>-32.89616961224491</v>
+      </c>
+      <c r="P87">
+        <v>-98.68850883673474</v>
+      </c>
+      <c r="Q87">
+        <v>-69.78850883673474</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.3678846499829048</v>
+      </c>
+      <c r="T87">
+        <v>4.743402229207292</v>
+      </c>
+      <c r="U87">
+        <v>0.2088</v>
+      </c>
+      <c r="V87">
+        <v>0.1292262867703693</v>
+      </c>
+      <c r="W87">
+        <v>0.1818175513223469</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.5169051470814772</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2114276161214306</v>
+      </c>
+      <c r="C88">
+        <v>58.2946238412469</v>
+      </c>
+      <c r="D88">
+        <v>316.536623841247</v>
+      </c>
+      <c r="E88">
+        <v>505.7420000000001</v>
+      </c>
+      <c r="F88">
+        <v>1319.842</v>
+      </c>
+      <c r="G88">
+        <v>1061.6</v>
+      </c>
+      <c r="H88">
+        <v>720.6</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K88">
+        <v>28.9</v>
+      </c>
+      <c r="L88">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M88">
+        <v>275.5830096</v>
+      </c>
+      <c r="N88">
+        <v>-134.7891320489796</v>
+      </c>
+      <c r="O88">
+        <v>-33.6972830122449</v>
+      </c>
+      <c r="P88">
+        <v>-101.0918490367347</v>
+      </c>
+      <c r="Q88">
+        <v>-72.19184903673471</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.3913906964102551</v>
+      </c>
+      <c r="T88">
+        <v>5.082216674150669</v>
+      </c>
+      <c r="U88">
+        <v>0.2088</v>
+      </c>
+      <c r="V88">
+        <v>0.1277236555288534</v>
+      </c>
+      <c r="W88">
+        <v>0.1821313007255754</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.5108946221154136</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2131276161214306</v>
+      </c>
+      <c r="C89">
+        <v>41.44500446280131</v>
+      </c>
+      <c r="D89">
+        <v>315.0340044628015</v>
+      </c>
+      <c r="E89">
+        <v>521.0890000000001</v>
+      </c>
+      <c r="F89">
+        <v>1335.189</v>
+      </c>
+      <c r="G89">
+        <v>1061.6</v>
+      </c>
+      <c r="H89">
+        <v>720.6</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K89">
+        <v>28.9</v>
+      </c>
+      <c r="L89">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M89">
+        <v>278.7874632</v>
+      </c>
+      <c r="N89">
+        <v>-137.9935856489796</v>
+      </c>
+      <c r="O89">
+        <v>-34.49839641224491</v>
+      </c>
+      <c r="P89">
+        <v>-103.4951892367347</v>
+      </c>
+      <c r="Q89">
+        <v>-74.59518923673471</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.4185130576725825</v>
+      </c>
+      <c r="T89">
+        <v>5.473156418316106</v>
+      </c>
+      <c r="U89">
+        <v>0.2088</v>
+      </c>
+      <c r="V89">
+        <v>0.1262555675342689</v>
+      </c>
+      <c r="W89">
+        <v>0.1824378374988447</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.5050222701370755</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2419928402863457</v>
+      </c>
+      <c r="C90">
+        <v>2.599387055490524</v>
+      </c>
+      <c r="D90">
+        <v>291.5353870554907</v>
+      </c>
+      <c r="E90">
+        <v>536.436</v>
+      </c>
+      <c r="F90">
+        <v>1350.536</v>
+      </c>
+      <c r="G90">
+        <v>1061.6</v>
+      </c>
+      <c r="H90">
+        <v>720.6</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K90">
+        <v>28.9</v>
+      </c>
+      <c r="L90">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M90">
+        <v>322.5079968000001</v>
+      </c>
+      <c r="N90">
+        <v>-181.7141192489796</v>
+      </c>
+      <c r="O90">
+        <v>-45.42852981224491</v>
+      </c>
+      <c r="P90">
+        <v>-136.2855894367347</v>
+      </c>
+      <c r="Q90">
+        <v>-107.3855894367347</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.4565326805195901</v>
+      </c>
+      <c r="T90">
+        <v>6.021168499023866</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.1091398344754318</v>
+      </c>
+      <c r="W90">
+        <v>0.2127374075272669</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.4365593379017273</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2439928402863457</v>
+      </c>
+      <c r="C91">
+        <v>-14.24658132452987</v>
+      </c>
+      <c r="D91">
+        <v>290.0364186754702</v>
+      </c>
+      <c r="E91">
+        <v>551.783</v>
+      </c>
+      <c r="F91">
+        <v>1365.883</v>
+      </c>
+      <c r="G91">
+        <v>1061.6</v>
+      </c>
+      <c r="H91">
+        <v>720.6</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K91">
+        <v>28.9</v>
+      </c>
+      <c r="L91">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M91">
+        <v>326.1728604</v>
+      </c>
+      <c r="N91">
+        <v>-185.3789828489796</v>
+      </c>
+      <c r="O91">
+        <v>-46.34474571224491</v>
+      </c>
+      <c r="P91">
+        <v>-139.0342371367347</v>
+      </c>
+      <c r="Q91">
+        <v>-110.1342371367347</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.4945083787486437</v>
+      </c>
+      <c r="T91">
+        <v>6.56854745348058</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.107913544200427</v>
+      </c>
+      <c r="W91">
+        <v>0.2130302456449381</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.4316541768017079</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2459928402863457</v>
+      </c>
+      <c r="C92">
+        <v>-31.07721425897807</v>
+      </c>
+      <c r="D92">
+        <v>288.5527857410221</v>
+      </c>
+      <c r="E92">
+        <v>567.13</v>
+      </c>
+      <c r="F92">
+        <v>1381.23</v>
+      </c>
+      <c r="G92">
+        <v>1061.6</v>
+      </c>
+      <c r="H92">
+        <v>720.6</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K92">
+        <v>28.9</v>
+      </c>
+      <c r="L92">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M92">
+        <v>329.837724</v>
+      </c>
+      <c r="N92">
+        <v>-189.0438464489796</v>
+      </c>
+      <c r="O92">
+        <v>-47.26096161224491</v>
+      </c>
+      <c r="P92">
+        <v>-141.7828848367347</v>
+      </c>
+      <c r="Q92">
+        <v>-112.8828848367347</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.5400792166235082</v>
+      </c>
+      <c r="T92">
+        <v>7.22540219882864</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.1067145048204222</v>
+      </c>
+      <c r="W92">
+        <v>0.2133165762488832</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.426858019281689</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2479928402863457</v>
+      </c>
+      <c r="C93">
+        <v>-47.89274588789317</v>
+      </c>
+      <c r="D93">
+        <v>287.084254112107</v>
+      </c>
+      <c r="E93">
+        <v>582.477</v>
+      </c>
+      <c r="F93">
+        <v>1396.577</v>
+      </c>
+      <c r="G93">
+        <v>1061.6</v>
+      </c>
+      <c r="H93">
+        <v>720.6</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K93">
+        <v>28.9</v>
+      </c>
+      <c r="L93">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M93">
+        <v>333.5025876</v>
+      </c>
+      <c r="N93">
+        <v>-192.7087100489796</v>
+      </c>
+      <c r="O93">
+        <v>-48.1771775122449</v>
+      </c>
+      <c r="P93">
+        <v>-144.5315325367347</v>
+      </c>
+      <c r="Q93">
+        <v>-115.6315325367347</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.5957769073594537</v>
+      </c>
+      <c r="T93">
+        <v>8.028224665365157</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.1055418179542638</v>
+      </c>
+      <c r="W93">
+        <v>0.2135966138725218</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.422167271817055</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2499928402863457</v>
+      </c>
+      <c r="C94">
+        <v>-64.69340560901423</v>
+      </c>
+      <c r="D94">
+        <v>285.6305943909861</v>
+      </c>
+      <c r="E94">
+        <v>597.8240000000002</v>
+      </c>
+      <c r="F94">
+        <v>1411.924</v>
+      </c>
+      <c r="G94">
+        <v>1061.6</v>
+      </c>
+      <c r="H94">
+        <v>720.6</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K94">
+        <v>28.9</v>
+      </c>
+      <c r="L94">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M94">
+        <v>337.1674512000001</v>
+      </c>
+      <c r="N94">
+        <v>-196.3735736489797</v>
+      </c>
+      <c r="O94">
+        <v>-49.09339341224491</v>
+      </c>
+      <c r="P94">
+        <v>-147.2801802367347</v>
+      </c>
+      <c r="Q94">
+        <v>-118.3801802367347</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.6653990207793854</v>
+      </c>
+      <c r="T94">
+        <v>9.031752748535803</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.1043946242808478</v>
+      </c>
+      <c r="W94">
+        <v>0.2138705637217335</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.4175784971233913</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2519928402863457</v>
+      </c>
+      <c r="C95">
+        <v>-81.4794181972386</v>
+      </c>
+      <c r="D95">
+        <v>284.1915818027617</v>
+      </c>
+      <c r="E95">
+        <v>613.1710000000002</v>
+      </c>
+      <c r="F95">
+        <v>1427.271</v>
+      </c>
+      <c r="G95">
+        <v>1061.6</v>
+      </c>
+      <c r="H95">
+        <v>720.6</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K95">
+        <v>28.9</v>
+      </c>
+      <c r="L95">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M95">
+        <v>340.8323148000001</v>
+      </c>
+      <c r="N95">
+        <v>-200.0384372489796</v>
+      </c>
+      <c r="O95">
+        <v>-50.00960931224491</v>
+      </c>
+      <c r="P95">
+        <v>-150.0288279367347</v>
+      </c>
+      <c r="Q95">
+        <v>-121.1288279367347</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.754913166605012</v>
+      </c>
+      <c r="T95">
+        <v>10.32200314118378</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.1032721014391183</v>
+      </c>
+      <c r="W95">
+        <v>0.2141386221763386</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.4130884057564731</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2539928402863457</v>
+      </c>
+      <c r="C96">
+        <v>-98.25100392048876</v>
+      </c>
+      <c r="D96">
+        <v>282.7669960795116</v>
+      </c>
+      <c r="E96">
+        <v>628.5180000000001</v>
+      </c>
+      <c r="F96">
+        <v>1442.618</v>
+      </c>
+      <c r="G96">
+        <v>1061.6</v>
+      </c>
+      <c r="H96">
+        <v>720.6</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K96">
+        <v>28.9</v>
+      </c>
+      <c r="L96">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M96">
+        <v>344.4971784000001</v>
+      </c>
+      <c r="N96">
+        <v>-203.7033008489796</v>
+      </c>
+      <c r="O96">
+        <v>-50.92582521224491</v>
+      </c>
+      <c r="P96">
+        <v>-152.7774756367347</v>
+      </c>
+      <c r="Q96">
+        <v>-123.8774756367347</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>0.8742653610391808</v>
+      </c>
+      <c r="T96">
+        <v>12.04233699804774</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.1021734620621064</v>
+      </c>
+      <c r="W96">
+        <v>0.214400977259569</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.4086938482484256</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2559928402863457</v>
+      </c>
+      <c r="C97">
+        <v>-115.0083786521097</v>
+      </c>
+      <c r="D97">
+        <v>281.3566213478904</v>
+      </c>
+      <c r="E97">
+        <v>643.8650000000001</v>
+      </c>
+      <c r="F97">
+        <v>1457.965</v>
+      </c>
+      <c r="G97">
+        <v>1061.6</v>
+      </c>
+      <c r="H97">
+        <v>720.6</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K97">
+        <v>28.9</v>
+      </c>
+      <c r="L97">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M97">
+        <v>348.162042</v>
+      </c>
+      <c r="N97">
+        <v>-207.3681644489796</v>
+      </c>
+      <c r="O97">
+        <v>-51.84204111224491</v>
+      </c>
+      <c r="P97">
+        <v>-155.5261233367347</v>
+      </c>
+      <c r="Q97">
+        <v>-126.6261233367347</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.041358433247018</v>
+      </c>
+      <c r="T97">
+        <v>14.4508043976573</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.1010979519351369</v>
+      </c>
+      <c r="W97">
+        <v>0.2146578090778893</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.4043918077405474</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2579928402863457</v>
+      </c>
+      <c r="C98">
+        <v>-131.7517539799223</v>
+      </c>
+      <c r="D98">
+        <v>279.9602460200776</v>
+      </c>
+      <c r="E98">
+        <v>659.2119999999999</v>
+      </c>
+      <c r="F98">
+        <v>1473.312</v>
+      </c>
+      <c r="G98">
+        <v>1061.6</v>
+      </c>
+      <c r="H98">
+        <v>720.6</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K98">
+        <v>28.9</v>
+      </c>
+      <c r="L98">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M98">
+        <v>351.8269056</v>
+      </c>
+      <c r="N98">
+        <v>-211.0330280489796</v>
+      </c>
+      <c r="O98">
+        <v>-52.75825701224489</v>
+      </c>
+      <c r="P98">
+        <v>-158.2747710367347</v>
+      </c>
+      <c r="Q98">
+        <v>-129.3747710367347</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.291998041558769</v>
+      </c>
+      <c r="T98">
+        <v>18.06350549707158</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.1000448482691459</v>
+      </c>
+      <c r="W98">
+        <v>0.214909290233328</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.4001793930765835</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2599928402863456</v>
+      </c>
+      <c r="C99">
+        <v>-148.4813373120426</v>
+      </c>
+      <c r="D99">
+        <v>278.5776626879576</v>
+      </c>
+      <c r="E99">
+        <v>674.5590000000001</v>
+      </c>
+      <c r="F99">
+        <v>1488.659</v>
+      </c>
+      <c r="G99">
+        <v>1061.6</v>
+      </c>
+      <c r="H99">
+        <v>720.6</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K99">
+        <v>28.9</v>
+      </c>
+      <c r="L99">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M99">
+        <v>355.4917692</v>
+      </c>
+      <c r="N99">
+        <v>-214.6978916489796</v>
+      </c>
+      <c r="O99">
+        <v>-53.6744729122449</v>
+      </c>
+      <c r="P99">
+        <v>-161.0234187367347</v>
+      </c>
+      <c r="Q99">
+        <v>-132.1234187367347</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>1.709730722078359</v>
+      </c>
+      <c r="T99">
+        <v>24.08467399609544</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.09901345808080414</v>
+      </c>
+      <c r="W99">
+        <v>0.215155586210304</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.3960538323232166</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2619928402863457</v>
+      </c>
+      <c r="C100">
+        <v>-165.1973319795811</v>
+      </c>
+      <c r="D100">
+        <v>277.2086680204191</v>
+      </c>
+      <c r="E100">
+        <v>689.9060000000001</v>
+      </c>
+      <c r="F100">
+        <v>1504.006</v>
+      </c>
+      <c r="G100">
+        <v>1061.6</v>
+      </c>
+      <c r="H100">
+        <v>720.6</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K100">
+        <v>28.9</v>
+      </c>
+      <c r="L100">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M100">
+        <v>359.1566328</v>
+      </c>
+      <c r="N100">
+        <v>-218.3627552489796</v>
+      </c>
+      <c r="O100">
+        <v>-54.5906888122449</v>
+      </c>
+      <c r="P100">
+        <v>-163.7720664367347</v>
+      </c>
+      <c r="Q100">
+        <v>-134.8720664367347</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>2.545196083117538</v>
+      </c>
+      <c r="T100">
+        <v>36.12701099414316</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.09800311667181635</v>
+      </c>
+      <c r="W100">
+        <v>0.2153968557387703</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.3920124666872654</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2639928402863457</v>
+      </c>
+      <c r="C101">
+        <v>-181.8999373363313</v>
+      </c>
+      <c r="D101">
+        <v>275.8530626636689</v>
+      </c>
+      <c r="E101">
+        <v>705.253</v>
+      </c>
+      <c r="F101">
+        <v>1519.353</v>
+      </c>
+      <c r="G101">
+        <v>1061.6</v>
+      </c>
+      <c r="H101">
+        <v>720.6</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>169.6938775510204</v>
+      </c>
+      <c r="K101">
+        <v>28.9</v>
+      </c>
+      <c r="L101">
+        <v>140.7938775510204</v>
+      </c>
+      <c r="M101">
+        <v>362.8214964000001</v>
+      </c>
+      <c r="N101">
+        <v>-222.0276188489796</v>
+      </c>
+      <c r="O101">
+        <v>-55.50690471224491</v>
+      </c>
+      <c r="P101">
+        <v>-166.5207141367347</v>
+      </c>
+      <c r="Q101">
+        <v>-137.6207141367347</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>5.051592166235077</v>
+      </c>
+      <c r="T101">
+        <v>72.25402198828633</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.09701318620038385</v>
+      </c>
+      <c r="W101">
+        <v>0.2156332511353484</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.3880527448015354</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/spain/spain_oilfield_svcs_equip.xlsx
+++ b/research/traditional_assets/database/data/spain/spain_oilfield_svcs_equip.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09746933780179359</v>
+        <v>0.0972594144572891</v>
       </c>
       <c r="C2">
-        <v>1629.801043272804</v>
+        <v>1613.958329056399</v>
       </c>
       <c r="D2">
-        <v>570.2010432728043</v>
+        <v>570.7153290563987</v>
       </c>
       <c r="E2">
-        <v>-726.7</v>
+        <v>-710.3430000000001</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>16.357</v>
       </c>
       <c r="G2">
         <v>1059.6</v>
@@ -1451,28 +1451,28 @@
         <v>180.9</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.8227570999999999</v>
       </c>
       <c r="N2">
-        <v>180.9</v>
+        <v>180.0772429</v>
       </c>
       <c r="O2">
-        <v>45.225</v>
+        <v>45.019310725</v>
       </c>
       <c r="P2">
-        <v>135.675</v>
+        <v>135.057932175</v>
       </c>
       <c r="Q2">
-        <v>169.775</v>
+        <v>169.157932175</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09746933780179359</v>
+        <v>0.0978607721790799</v>
       </c>
       <c r="T2">
-        <v>0.7993082229751833</v>
+        <v>0.8053635883007529</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>219.8704818226425</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.0972594144572891</v>
+        <v>0.09704949111278463</v>
       </c>
       <c r="C3">
-        <v>1613.958329056399</v>
+        <v>1598.116543384895</v>
       </c>
       <c r="D3">
-        <v>570.7153290563987</v>
+        <v>571.230543384895</v>
       </c>
       <c r="E3">
-        <v>-710.3430000000001</v>
+        <v>-693.9860000000001</v>
       </c>
       <c r="F3">
-        <v>16.357</v>
+        <v>32.714</v>
       </c>
       <c r="G3">
         <v>1059.6</v>
@@ -1533,28 +1533,28 @@
         <v>180.9</v>
       </c>
       <c r="M3">
-        <v>0.8227570999999999</v>
+        <v>1.6455142</v>
       </c>
       <c r="N3">
-        <v>180.0772429</v>
+        <v>179.2544858</v>
       </c>
       <c r="O3">
-        <v>45.019310725</v>
+        <v>44.81362145</v>
       </c>
       <c r="P3">
-        <v>135.057932175</v>
+        <v>134.44086435</v>
       </c>
       <c r="Q3">
-        <v>169.157932175</v>
+        <v>168.54086435</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.0978607721790799</v>
+        <v>0.09826019501304553</v>
       </c>
       <c r="T3">
-        <v>0.8053635883007529</v>
+        <v>0.8115425325105178</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>219.8704818226425</v>
+        <v>109.9352409113212</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09704949111278463</v>
+        <v>0.09683956776828012</v>
       </c>
       <c r="C4">
-        <v>1598.116543384895</v>
+        <v>1582.275688775303</v>
       </c>
       <c r="D4">
-        <v>571.230543384895</v>
+        <v>571.7466887753026</v>
       </c>
       <c r="E4">
-        <v>-693.9860000000001</v>
+        <v>-677.629</v>
       </c>
       <c r="F4">
-        <v>32.714</v>
+        <v>49.071</v>
       </c>
       <c r="G4">
         <v>1059.6</v>
@@ -1615,28 +1615,28 @@
         <v>180.9</v>
       </c>
       <c r="M4">
-        <v>1.6455142</v>
+        <v>2.4682713</v>
       </c>
       <c r="N4">
-        <v>179.2544858</v>
+        <v>178.4317287</v>
       </c>
       <c r="O4">
-        <v>44.81362145</v>
+        <v>44.607932175</v>
       </c>
       <c r="P4">
-        <v>134.44086435</v>
+        <v>133.823796525</v>
       </c>
       <c r="Q4">
-        <v>168.54086435</v>
+        <v>167.923796525</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09826019501304553</v>
+        <v>0.09866785336936096</v>
       </c>
       <c r="T4">
-        <v>0.8115425325105178</v>
+        <v>0.8178488776318241</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>109.9352409113212</v>
+        <v>73.29016060754749</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09683956776828012</v>
+        <v>0.09662964442377565</v>
       </c>
       <c r="C5">
-        <v>1582.275688775303</v>
+        <v>1566.435767753735</v>
       </c>
       <c r="D5">
-        <v>571.7466887753026</v>
+        <v>572.2637677537357</v>
       </c>
       <c r="E5">
-        <v>-677.629</v>
+        <v>-661.272</v>
       </c>
       <c r="F5">
-        <v>49.071</v>
+        <v>65.428</v>
       </c>
       <c r="G5">
         <v>1059.6</v>
@@ -1697,28 +1697,28 @@
         <v>180.9</v>
       </c>
       <c r="M5">
-        <v>2.4682713</v>
+        <v>3.2910284</v>
       </c>
       <c r="N5">
-        <v>178.4317287</v>
+        <v>177.6089716</v>
       </c>
       <c r="O5">
-        <v>44.607932175</v>
+        <v>44.4022429</v>
       </c>
       <c r="P5">
-        <v>133.823796525</v>
+        <v>133.2067287</v>
       </c>
       <c r="Q5">
-        <v>167.923796525</v>
+        <v>167.3067287</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09866785336936096</v>
+        <v>0.09908400460809964</v>
       </c>
       <c r="T5">
-        <v>0.8178488776318241</v>
+        <v>0.8242866049431579</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>73.29016060754749</v>
+        <v>54.96762045566062</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09662964442377565</v>
+        <v>0.09641972107927117</v>
       </c>
       <c r="C6">
-        <v>1566.435767753735</v>
+        <v>1550.596782855456</v>
       </c>
       <c r="D6">
-        <v>572.2637677537357</v>
+        <v>572.7817828554557</v>
       </c>
       <c r="E6">
-        <v>-661.272</v>
+        <v>-644.9150000000001</v>
       </c>
       <c r="F6">
-        <v>65.428</v>
+        <v>81.78500000000001</v>
       </c>
       <c r="G6">
         <v>1059.6</v>
@@ -1779,28 +1779,28 @@
         <v>180.9</v>
       </c>
       <c r="M6">
-        <v>3.2910284</v>
+        <v>4.113785500000001</v>
       </c>
       <c r="N6">
-        <v>177.6089716</v>
+        <v>176.7862145</v>
       </c>
       <c r="O6">
-        <v>44.4022429</v>
+        <v>44.196553625</v>
       </c>
       <c r="P6">
-        <v>133.2067287</v>
+        <v>132.589660875</v>
       </c>
       <c r="Q6">
-        <v>167.3067287</v>
+        <v>166.689660875</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09908400460809964</v>
+        <v>0.0995089169255486</v>
       </c>
       <c r="T6">
-        <v>0.8242866049431579</v>
+        <v>0.8308598633557827</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>54.96762045566062</v>
+        <v>43.97409636452848</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09641972107927117</v>
+        <v>0.09620979773476669</v>
       </c>
       <c r="C7">
-        <v>1550.596782855456</v>
+        <v>1534.758736624912</v>
       </c>
       <c r="D7">
-        <v>572.7817828554557</v>
+        <v>573.3007366249119</v>
       </c>
       <c r="E7">
-        <v>-644.9150000000001</v>
+        <v>-628.558</v>
       </c>
       <c r="F7">
-        <v>81.78500000000001</v>
+        <v>98.14200000000001</v>
       </c>
       <c r="G7">
         <v>1059.6</v>
@@ -1861,28 +1861,28 @@
         <v>180.9</v>
       </c>
       <c r="M7">
-        <v>4.113785500000001</v>
+        <v>4.9365426</v>
       </c>
       <c r="N7">
-        <v>176.7862145</v>
+        <v>175.9634574</v>
       </c>
       <c r="O7">
-        <v>44.196553625</v>
+        <v>43.99086435</v>
       </c>
       <c r="P7">
-        <v>132.589660875</v>
+        <v>131.97259305</v>
       </c>
       <c r="Q7">
-        <v>166.689660875</v>
+        <v>166.07259305</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.0995089169255486</v>
+        <v>0.09994286993060286</v>
       </c>
       <c r="T7">
-        <v>0.8308598633557827</v>
+        <v>0.8375729783303782</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>43.97409636452848</v>
+        <v>36.64508030377374</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09620979773476669</v>
+        <v>0.09599987439026221</v>
       </c>
       <c r="C8">
-        <v>1534.758736624912</v>
+        <v>1518.921631615783</v>
       </c>
       <c r="D8">
-        <v>573.3007366249119</v>
+        <v>573.8206316157828</v>
       </c>
       <c r="E8">
-        <v>-628.558</v>
+        <v>-612.201</v>
       </c>
       <c r="F8">
-        <v>98.142</v>
+        <v>114.499</v>
       </c>
       <c r="G8">
         <v>1059.6</v>
@@ -1943,28 +1943,28 @@
         <v>180.9</v>
       </c>
       <c r="M8">
-        <v>4.936542599999999</v>
+        <v>5.7592997</v>
       </c>
       <c r="N8">
-        <v>175.9634574</v>
+        <v>175.1407003</v>
       </c>
       <c r="O8">
-        <v>43.99086435</v>
+        <v>43.785175075</v>
       </c>
       <c r="P8">
-        <v>131.97259305</v>
+        <v>131.355525225</v>
       </c>
       <c r="Q8">
-        <v>166.07259305</v>
+        <v>165.455525225</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09994286993060286</v>
+        <v>0.1003861552583465</v>
       </c>
       <c r="T8">
-        <v>0.8375729783303782</v>
+        <v>0.8444304613689436</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>36.64508030377375</v>
+        <v>31.41006883180606</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.0959998743902622</v>
+        <v>0.09578995104575774</v>
       </c>
       <c r="C9">
-        <v>1518.921631615783</v>
+        <v>1503.085470391019</v>
       </c>
       <c r="D9">
-        <v>573.8206316157829</v>
+        <v>574.341470391019</v>
       </c>
       <c r="E9">
-        <v>-612.201</v>
+        <v>-595.8440000000001</v>
       </c>
       <c r="F9">
-        <v>114.499</v>
+        <v>130.856</v>
       </c>
       <c r="G9">
         <v>1059.6</v>
@@ -2025,28 +2025,28 @@
         <v>180.9</v>
       </c>
       <c r="M9">
-        <v>5.759299700000001</v>
+        <v>6.582056799999999</v>
       </c>
       <c r="N9">
-        <v>175.1407003</v>
+        <v>174.3179432</v>
       </c>
       <c r="O9">
-        <v>43.785175075</v>
+        <v>43.5794858</v>
       </c>
       <c r="P9">
-        <v>131.355525225</v>
+        <v>130.7384574</v>
       </c>
       <c r="Q9">
-        <v>165.455525225</v>
+        <v>164.8384574</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1003861552583465</v>
+        <v>0.1008390772236497</v>
       </c>
       <c r="T9">
-        <v>0.8444304613689436</v>
+        <v>0.8514370201257389</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>31.41006883180606</v>
+        <v>27.48381022783031</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09578995104575774</v>
+        <v>0.09558002770125325</v>
       </c>
       <c r="C10">
-        <v>1503.085470391019</v>
+        <v>1487.250255522885</v>
       </c>
       <c r="D10">
-        <v>574.341470391019</v>
+        <v>574.8632555228846</v>
       </c>
       <c r="E10">
-        <v>-595.8440000000001</v>
+        <v>-579.4870000000001</v>
       </c>
       <c r="F10">
-        <v>130.856</v>
+        <v>147.213</v>
       </c>
       <c r="G10">
         <v>1059.6</v>
@@ -2107,28 +2107,28 @@
         <v>180.9</v>
       </c>
       <c r="M10">
-        <v>6.582056799999999</v>
+        <v>7.4048139</v>
       </c>
       <c r="N10">
-        <v>174.3179432</v>
+        <v>173.4951861</v>
       </c>
       <c r="O10">
-        <v>43.5794858</v>
+        <v>43.373796525</v>
       </c>
       <c r="P10">
-        <v>130.7384574</v>
+        <v>130.121389575</v>
       </c>
       <c r="Q10">
-        <v>164.8384574</v>
+        <v>164.221389575</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1008390772236497</v>
+        <v>0.1013019535178607</v>
       </c>
       <c r="T10">
-        <v>0.8514370201257389</v>
+        <v>0.8585975691848809</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>27.48381022783031</v>
+        <v>24.43005353584916</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09558002770125325</v>
+        <v>0.09537010435674875</v>
       </c>
       <c r="C11">
-        <v>1487.250255522885</v>
+        <v>1471.415989593</v>
       </c>
       <c r="D11">
-        <v>574.8632555228846</v>
+        <v>575.3859895929999</v>
       </c>
       <c r="E11">
-        <v>-579.4870000000001</v>
+        <v>-563.1300000000001</v>
       </c>
       <c r="F11">
-        <v>147.213</v>
+        <v>163.57</v>
       </c>
       <c r="G11">
         <v>1059.6</v>
@@ -2189,28 +2189,28 @@
         <v>180.9</v>
       </c>
       <c r="M11">
-        <v>7.4048139</v>
+        <v>8.227570999999999</v>
       </c>
       <c r="N11">
-        <v>173.4951861</v>
+        <v>172.672429</v>
       </c>
       <c r="O11">
-        <v>43.373796525</v>
+        <v>43.16810725</v>
       </c>
       <c r="P11">
-        <v>130.121389575</v>
+        <v>129.50432175</v>
       </c>
       <c r="Q11">
-        <v>164.221389575</v>
+        <v>163.60432175</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1013019535178607</v>
+        <v>0.1017751159519431</v>
       </c>
       <c r="T11">
-        <v>0.8585975691848809</v>
+        <v>0.8659172415564486</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>24.43005353584916</v>
+        <v>21.98704818226424</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09537010435674875</v>
+        <v>0.09516018101224427</v>
       </c>
       <c r="C12">
-        <v>1471.415989593</v>
+        <v>1455.582675192383</v>
       </c>
       <c r="D12">
-        <v>575.3859895929999</v>
+        <v>575.9096751923832</v>
       </c>
       <c r="E12">
-        <v>-563.13</v>
+        <v>-546.773</v>
       </c>
       <c r="F12">
-        <v>163.57</v>
+        <v>179.927</v>
       </c>
       <c r="G12">
         <v>1059.6</v>
@@ -2271,28 +2271,28 @@
         <v>180.9</v>
       </c>
       <c r="M12">
-        <v>8.227571000000001</v>
+        <v>9.0503281</v>
       </c>
       <c r="N12">
-        <v>172.672429</v>
+        <v>171.8496719</v>
       </c>
       <c r="O12">
-        <v>43.16810725</v>
+        <v>42.962417975</v>
       </c>
       <c r="P12">
-        <v>129.50432175</v>
+        <v>128.887253925</v>
       </c>
       <c r="Q12">
-        <v>163.60432175</v>
+        <v>162.987253925</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1017751159519431</v>
+        <v>0.1022589112497127</v>
       </c>
       <c r="T12">
-        <v>0.8659172415564486</v>
+        <v>0.8734014009476021</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>21.98704818226424</v>
+        <v>19.98822562024022</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09516018101224427</v>
+        <v>0.09495025766773978</v>
       </c>
       <c r="C13">
-        <v>1455.582675192383</v>
+        <v>1439.750314921495</v>
       </c>
       <c r="D13">
-        <v>575.9096751923832</v>
+        <v>576.4343149214951</v>
       </c>
       <c r="E13">
-        <v>-546.773</v>
+        <v>-530.4160000000001</v>
       </c>
       <c r="F13">
-        <v>179.927</v>
+        <v>196.284</v>
       </c>
       <c r="G13">
         <v>1059.6</v>
@@ -2353,28 +2353,28 @@
         <v>180.9</v>
       </c>
       <c r="M13">
-        <v>9.0503281</v>
+        <v>9.873085199999998</v>
       </c>
       <c r="N13">
-        <v>171.8496719</v>
+        <v>171.0269148</v>
       </c>
       <c r="O13">
-        <v>42.962417975</v>
+        <v>42.7567287</v>
       </c>
       <c r="P13">
-        <v>128.887253925</v>
+        <v>128.2701861</v>
       </c>
       <c r="Q13">
-        <v>162.987253925</v>
+        <v>162.3701861</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1022589112497127</v>
+        <v>0.1027537018951588</v>
       </c>
       <c r="T13">
-        <v>0.8734014009476021</v>
+        <v>0.8810556548703725</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>19.98822562024022</v>
+        <v>18.32254015188687</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09495025766773978</v>
+        <v>0.0947403343232353</v>
       </c>
       <c r="C14">
-        <v>1439.750314921495</v>
+        <v>1423.91891139028</v>
       </c>
       <c r="D14">
-        <v>576.4343149214951</v>
+        <v>576.95991139028</v>
       </c>
       <c r="E14">
-        <v>-530.4160000000001</v>
+        <v>-514.059</v>
       </c>
       <c r="F14">
-        <v>196.284</v>
+        <v>212.641</v>
       </c>
       <c r="G14">
         <v>1059.6</v>
@@ -2435,28 +2435,28 @@
         <v>180.9</v>
       </c>
       <c r="M14">
-        <v>9.873085199999998</v>
+        <v>10.6958423</v>
       </c>
       <c r="N14">
-        <v>171.0269148</v>
+        <v>170.2041577</v>
       </c>
       <c r="O14">
-        <v>42.7567287</v>
+        <v>42.551039425</v>
       </c>
       <c r="P14">
-        <v>128.2701861</v>
+        <v>127.653118275</v>
       </c>
       <c r="Q14">
-        <v>162.3701861</v>
+        <v>161.753118275</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1027537018951588</v>
+        <v>0.1032598670382015</v>
       </c>
       <c r="T14">
-        <v>0.8810556548703725</v>
+        <v>0.8888858686534366</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>18.32254015188687</v>
+        <v>16.91311398635711</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.0947403343232353</v>
+        <v>0.09453041097873081</v>
       </c>
       <c r="C15">
-        <v>1423.91891139028</v>
+        <v>1408.08846721821</v>
       </c>
       <c r="D15">
-        <v>576.95991139028</v>
+        <v>577.4864672182105</v>
       </c>
       <c r="E15">
-        <v>-514.059</v>
+        <v>-497.702</v>
       </c>
       <c r="F15">
-        <v>212.641</v>
+        <v>228.998</v>
       </c>
       <c r="G15">
         <v>1059.6</v>
@@ -2517,28 +2517,28 @@
         <v>180.9</v>
       </c>
       <c r="M15">
-        <v>10.6958423</v>
+        <v>11.5185994</v>
       </c>
       <c r="N15">
-        <v>170.2041577</v>
+        <v>169.3814006</v>
       </c>
       <c r="O15">
-        <v>42.551039425</v>
+        <v>42.34535015</v>
       </c>
       <c r="P15">
-        <v>127.653118275</v>
+        <v>127.03605045</v>
       </c>
       <c r="Q15">
-        <v>161.753118275</v>
+        <v>161.13605045</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1032598670382015</v>
+        <v>0.1037778034636405</v>
       </c>
       <c r="T15">
-        <v>0.8888858686534366</v>
+        <v>0.8968981804314557</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>16.91311398635711</v>
+        <v>15.70503441590303</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09453041097873081</v>
+        <v>0.09432048763422633</v>
       </c>
       <c r="C16">
-        <v>1408.08846721821</v>
+        <v>1392.25898503433</v>
       </c>
       <c r="D16">
-        <v>577.4864672182105</v>
+        <v>578.0139850343299</v>
       </c>
       <c r="E16">
-        <v>-497.702</v>
+        <v>-481.345</v>
       </c>
       <c r="F16">
-        <v>228.998</v>
+        <v>245.355</v>
       </c>
       <c r="G16">
         <v>1059.6</v>
@@ -2599,28 +2599,28 @@
         <v>180.9</v>
       </c>
       <c r="M16">
-        <v>11.5185994</v>
+        <v>12.3413565</v>
       </c>
       <c r="N16">
-        <v>169.3814006</v>
+        <v>168.5586435</v>
       </c>
       <c r="O16">
-        <v>42.34535015</v>
+        <v>42.139660875</v>
       </c>
       <c r="P16">
-        <v>127.03605045</v>
+        <v>126.418982625</v>
       </c>
       <c r="Q16">
-        <v>161.13605045</v>
+        <v>160.518982625</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1037778034636405</v>
+        <v>0.1043079266285016</v>
       </c>
       <c r="T16">
-        <v>0.8968981804314557</v>
+        <v>0.905099017192487</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>15.70503441590303</v>
+        <v>14.65803212150949</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09432048763422633</v>
+        <v>0.09411056428972184</v>
       </c>
       <c r="C17">
-        <v>1392.25898503433</v>
+        <v>1376.430467477297</v>
       </c>
       <c r="D17">
-        <v>578.0139850343299</v>
+        <v>578.5424674772972</v>
       </c>
       <c r="E17">
-        <v>-481.345</v>
+        <v>-464.9880000000001</v>
       </c>
       <c r="F17">
-        <v>245.355</v>
+        <v>261.712</v>
       </c>
       <c r="G17">
         <v>1059.6</v>
@@ -2681,28 +2681,28 @@
         <v>180.9</v>
       </c>
       <c r="M17">
-        <v>12.3413565</v>
+        <v>13.1641136</v>
       </c>
       <c r="N17">
-        <v>168.5586435</v>
+        <v>167.7358864</v>
       </c>
       <c r="O17">
-        <v>42.139660875</v>
+        <v>41.9339716</v>
       </c>
       <c r="P17">
-        <v>126.418982625</v>
+        <v>125.8019148</v>
       </c>
       <c r="Q17">
-        <v>160.518982625</v>
+        <v>159.9019148</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1043079266285016</v>
+        <v>0.1048506717734784</v>
       </c>
       <c r="T17">
-        <v>0.905099017192487</v>
+        <v>0.913495111971638</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>14.6580321215095</v>
+        <v>13.74190511391515</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09411056428972184</v>
+        <v>0.09390064094521736</v>
       </c>
       <c r="C18">
-        <v>1376.430467477297</v>
+        <v>1360.60291719543</v>
       </c>
       <c r="D18">
-        <v>578.5424674772972</v>
+        <v>579.07191719543</v>
       </c>
       <c r="E18">
-        <v>-464.9880000000001</v>
+        <v>-448.631</v>
       </c>
       <c r="F18">
-        <v>261.712</v>
+        <v>278.069</v>
       </c>
       <c r="G18">
         <v>1059.6</v>
@@ -2763,28 +2763,28 @@
         <v>180.9</v>
       </c>
       <c r="M18">
-        <v>13.1641136</v>
+        <v>13.9868707</v>
       </c>
       <c r="N18">
-        <v>167.7358864</v>
+        <v>166.9131293</v>
       </c>
       <c r="O18">
-        <v>41.9339716</v>
+        <v>41.728282325</v>
       </c>
       <c r="P18">
-        <v>125.8019148</v>
+        <v>125.184846975</v>
       </c>
       <c r="Q18">
-        <v>159.9019148</v>
+        <v>159.284846975</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1048506717734784</v>
+        <v>0.1054064951147197</v>
       </c>
       <c r="T18">
-        <v>0.913495111971638</v>
+        <v>0.9220935222876363</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>13.74190511391515</v>
+        <v>12.93355775427308</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09390064094521736</v>
+        <v>0.09389321760071287</v>
       </c>
       <c r="C19">
-        <v>1360.60291719543</v>
+        <v>1344.264657425368</v>
       </c>
       <c r="D19">
-        <v>579.07191719543</v>
+        <v>579.0906574253682</v>
       </c>
       <c r="E19">
-        <v>-448.631</v>
+        <v>-432.274</v>
       </c>
       <c r="F19">
-        <v>278.069</v>
+        <v>294.426</v>
       </c>
       <c r="G19">
         <v>1059.6</v>
@@ -2845,45 +2845,45 @@
         <v>180.9</v>
       </c>
       <c r="M19">
-        <v>13.9868707</v>
+        <v>15.2512668</v>
       </c>
       <c r="N19">
-        <v>166.9131293</v>
+        <v>165.6487332</v>
       </c>
       <c r="O19">
-        <v>41.728282325</v>
+        <v>41.4121833</v>
       </c>
       <c r="P19">
-        <v>125.184846975</v>
+        <v>124.2365499</v>
       </c>
       <c r="Q19">
-        <v>159.284846975</v>
+        <v>158.3365499</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1054064951147197</v>
+        <v>0.1059758751228206</v>
       </c>
       <c r="T19">
-        <v>0.9220935222876363</v>
+        <v>0.9309016499284147</v>
       </c>
       <c r="U19">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V19">
         <v>0.25</v>
       </c>
       <c r="W19">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y19">
-        <v>12.93355775427308</v>
+        <v>11.86130977657541</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09389321760071288</v>
+        <v>0.09369454425620841</v>
       </c>
       <c r="C20">
-        <v>1344.264657425368</v>
+        <v>1328.409659225821</v>
       </c>
       <c r="D20">
-        <v>579.0906574253682</v>
+        <v>579.5926592258213</v>
       </c>
       <c r="E20">
-        <v>-432.2740000000001</v>
+        <v>-415.917</v>
       </c>
       <c r="F20">
-        <v>294.426</v>
+        <v>310.783</v>
       </c>
       <c r="G20">
         <v>1059.6</v>
@@ -2927,28 +2927,28 @@
         <v>180.9</v>
       </c>
       <c r="M20">
-        <v>15.2512668</v>
+        <v>16.0985594</v>
       </c>
       <c r="N20">
-        <v>165.6487332</v>
+        <v>164.8014406</v>
       </c>
       <c r="O20">
-        <v>41.4121833</v>
+        <v>41.20036015</v>
       </c>
       <c r="P20">
-        <v>124.2365499</v>
+        <v>123.60108045</v>
       </c>
       <c r="Q20">
-        <v>158.3365499</v>
+        <v>157.70108045</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1059758751228206</v>
+        <v>0.1065593138965536</v>
       </c>
       <c r="T20">
-        <v>0.9309016499284147</v>
+        <v>0.9399272622022991</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>11.86130977657541</v>
+        <v>11.23703031465039</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09369454425620841</v>
+        <v>0.09349587091170392</v>
       </c>
       <c r="C21">
-        <v>1328.409659225821</v>
+        <v>1312.555532131524</v>
       </c>
       <c r="D21">
-        <v>579.5926592258213</v>
+        <v>580.0955321315239</v>
       </c>
       <c r="E21">
-        <v>-415.917</v>
+        <v>-399.56</v>
       </c>
       <c r="F21">
-        <v>310.783</v>
+        <v>327.14</v>
       </c>
       <c r="G21">
         <v>1059.6</v>
@@ -3009,28 +3009,28 @@
         <v>180.9</v>
       </c>
       <c r="M21">
-        <v>16.0985594</v>
+        <v>16.945852</v>
       </c>
       <c r="N21">
-        <v>164.8014406</v>
+        <v>163.954148</v>
       </c>
       <c r="O21">
-        <v>41.20036015</v>
+        <v>40.988537</v>
       </c>
       <c r="P21">
-        <v>123.60108045</v>
+        <v>122.965611</v>
       </c>
       <c r="Q21">
-        <v>157.70108045</v>
+        <v>157.065611</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1065593138965536</v>
+        <v>0.1071573386396299</v>
       </c>
       <c r="T21">
-        <v>0.9399272622022991</v>
+        <v>0.9491785147830302</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>11.23703031465039</v>
+        <v>10.67517879891787</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09349587091170392</v>
+        <v>0.09329719756719942</v>
       </c>
       <c r="C22">
-        <v>1312.555532131524</v>
+        <v>1296.70227841184</v>
       </c>
       <c r="D22">
-        <v>580.0955321315239</v>
+        <v>580.5992784118405</v>
       </c>
       <c r="E22">
-        <v>-399.56</v>
+        <v>-383.203</v>
       </c>
       <c r="F22">
-        <v>327.14</v>
+        <v>343.497</v>
       </c>
       <c r="G22">
         <v>1059.6</v>
@@ -3091,28 +3091,28 @@
         <v>180.9</v>
       </c>
       <c r="M22">
-        <v>16.945852</v>
+        <v>17.7931446</v>
       </c>
       <c r="N22">
-        <v>163.954148</v>
+        <v>163.1068554</v>
       </c>
       <c r="O22">
-        <v>40.988537</v>
+        <v>40.77671385</v>
       </c>
       <c r="P22">
-        <v>122.965611</v>
+        <v>122.33014155</v>
       </c>
       <c r="Q22">
-        <v>157.065611</v>
+        <v>156.43014155</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1071573386396299</v>
+        <v>0.1077705032496195</v>
       </c>
       <c r="T22">
-        <v>0.9491785147830302</v>
+        <v>0.9586639762898559</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>10.67517879891787</v>
+        <v>10.16683695135035</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09329719756719942</v>
+        <v>0.09337902422269494</v>
       </c>
       <c r="C23">
-        <v>1296.70227841184</v>
+        <v>1280.137696876277</v>
       </c>
       <c r="D23">
-        <v>580.5992784118405</v>
+        <v>580.3916968762775</v>
       </c>
       <c r="E23">
-        <v>-383.203</v>
+        <v>-366.8460000000001</v>
       </c>
       <c r="F23">
-        <v>343.497</v>
+        <v>359.854</v>
       </c>
       <c r="G23">
         <v>1059.6</v>
@@ -3173,45 +3173,45 @@
         <v>180.9</v>
       </c>
       <c r="M23">
-        <v>17.7931446</v>
+        <v>19.252189</v>
       </c>
       <c r="N23">
-        <v>163.1068554</v>
+        <v>161.647811</v>
       </c>
       <c r="O23">
-        <v>40.77671385</v>
+        <v>40.41195275</v>
       </c>
       <c r="P23">
-        <v>122.33014155</v>
+        <v>121.23585825</v>
       </c>
       <c r="Q23">
-        <v>156.43014155</v>
+        <v>155.33585825</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1077705032496195</v>
+        <v>0.1083993900290961</v>
       </c>
       <c r="T23">
-        <v>0.9586639762898559</v>
+        <v>0.9683926547583951</v>
       </c>
       <c r="U23">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V23">
         <v>0.25</v>
       </c>
       <c r="W23">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y23">
-        <v>10.16683695135035</v>
+        <v>9.396334099982088</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09337902422269494</v>
+        <v>0.09319310087819047</v>
       </c>
       <c r="C24">
-        <v>1280.137696876277</v>
+        <v>1264.252570270387</v>
       </c>
       <c r="D24">
-        <v>580.3916968762775</v>
+        <v>580.8635702703866</v>
       </c>
       <c r="E24">
-        <v>-366.8460000000001</v>
+        <v>-350.489</v>
       </c>
       <c r="F24">
-        <v>359.854</v>
+        <v>376.211</v>
       </c>
       <c r="G24">
         <v>1059.6</v>
@@ -3255,28 +3255,28 @@
         <v>180.9</v>
       </c>
       <c r="M24">
-        <v>19.252189</v>
+        <v>20.1272885</v>
       </c>
       <c r="N24">
-        <v>161.647811</v>
+        <v>160.7727115</v>
       </c>
       <c r="O24">
-        <v>40.41195275</v>
+        <v>40.193177875</v>
       </c>
       <c r="P24">
-        <v>121.23585825</v>
+        <v>120.579533625</v>
       </c>
       <c r="Q24">
-        <v>155.33585825</v>
+        <v>154.679533625</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1083993900290961</v>
+        <v>0.1090446115301175</v>
       </c>
       <c r="T24">
-        <v>0.9683926547583951</v>
+        <v>0.9783740261741692</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>9.396334099982088</v>
+        <v>8.987797834765473</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09319310087819047</v>
+        <v>0.09300717753368598</v>
       </c>
       <c r="C25">
-        <v>1264.252570270387</v>
+        <v>1248.36821157927</v>
       </c>
       <c r="D25">
-        <v>580.8635702703866</v>
+        <v>581.3362115792696</v>
       </c>
       <c r="E25">
-        <v>-350.489</v>
+        <v>-334.132</v>
       </c>
       <c r="F25">
-        <v>376.211</v>
+        <v>392.568</v>
       </c>
       <c r="G25">
         <v>1059.6</v>
@@ -3337,28 +3337,28 @@
         <v>180.9</v>
       </c>
       <c r="M25">
-        <v>20.1272885</v>
+        <v>21.002388</v>
       </c>
       <c r="N25">
-        <v>160.7727115</v>
+        <v>159.897612</v>
       </c>
       <c r="O25">
-        <v>40.193177875</v>
+        <v>39.974403</v>
       </c>
       <c r="P25">
-        <v>120.579533625</v>
+        <v>119.923209</v>
       </c>
       <c r="Q25">
-        <v>154.679533625</v>
+        <v>154.023209</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1090446115301175</v>
+        <v>0.1097068125443237</v>
       </c>
       <c r="T25">
-        <v>0.9783740261741692</v>
+        <v>0.9886180652587795</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>8.987797834765473</v>
+        <v>8.613306258316911</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09300717753368598</v>
+        <v>0.09282125418918151</v>
       </c>
       <c r="C26">
-        <v>1248.36821157927</v>
+        <v>1232.484622678981</v>
       </c>
       <c r="D26">
-        <v>581.3362115792696</v>
+        <v>581.8096226789806</v>
       </c>
       <c r="E26">
-        <v>-334.1320000000001</v>
+        <v>-317.775</v>
       </c>
       <c r="F26">
-        <v>392.568</v>
+        <v>408.925</v>
       </c>
       <c r="G26">
         <v>1059.6</v>
@@ -3419,28 +3419,28 @@
         <v>180.9</v>
       </c>
       <c r="M26">
-        <v>21.002388</v>
+        <v>21.8774875</v>
       </c>
       <c r="N26">
-        <v>159.897612</v>
+        <v>159.0225125</v>
       </c>
       <c r="O26">
-        <v>39.974403</v>
+        <v>39.755628125</v>
       </c>
       <c r="P26">
-        <v>119.923209</v>
+        <v>119.266884375</v>
       </c>
       <c r="Q26">
-        <v>154.023209</v>
+        <v>153.366884375</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1097068125443237</v>
+        <v>0.110386672252242</v>
       </c>
       <c r="T26">
-        <v>0.9886180652587795</v>
+        <v>0.9991352787189791</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>8.613306258316911</v>
+        <v>8.268774007984234</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09282125418918151</v>
+        <v>0.092635330844677</v>
       </c>
       <c r="C27">
-        <v>1232.484622678981</v>
+        <v>1216.601805451689</v>
       </c>
       <c r="D27">
-        <v>581.8096226789806</v>
+        <v>582.2838054516898</v>
       </c>
       <c r="E27">
-        <v>-317.775</v>
+        <v>-301.418</v>
       </c>
       <c r="F27">
-        <v>408.925</v>
+        <v>425.282</v>
       </c>
       <c r="G27">
         <v>1059.6</v>
@@ -3501,28 +3501,28 @@
         <v>180.9</v>
       </c>
       <c r="M27">
-        <v>21.8774875</v>
+        <v>22.752587</v>
       </c>
       <c r="N27">
-        <v>159.0225125</v>
+        <v>158.147413</v>
       </c>
       <c r="O27">
-        <v>39.755628125</v>
+        <v>39.53685325</v>
       </c>
       <c r="P27">
-        <v>119.266884375</v>
+        <v>118.61055975</v>
       </c>
       <c r="Q27">
-        <v>153.366884375</v>
+        <v>152.71055975</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.110386672252242</v>
+        <v>0.1110849065468608</v>
       </c>
       <c r="T27">
-        <v>0.9991352787189791</v>
+        <v>1.009936741191617</v>
       </c>
       <c r="U27">
         <v>0.0535</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>8.268774007984234</v>
+        <v>7.950744238446379</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.092635330844677</v>
+        <v>0.09244940750017254</v>
       </c>
       <c r="C28">
-        <v>1216.601805451689</v>
+        <v>1200.719761785707</v>
       </c>
       <c r="D28">
-        <v>582.2838054516898</v>
+        <v>582.7587617857076</v>
       </c>
       <c r="E28">
-        <v>-301.418</v>
+        <v>-285.061</v>
       </c>
       <c r="F28">
-        <v>425.282</v>
+        <v>441.6390000000001</v>
       </c>
       <c r="G28">
         <v>1059.6</v>
@@ -3583,28 +3583,28 @@
         <v>180.9</v>
       </c>
       <c r="M28">
-        <v>22.752587</v>
+        <v>23.6276865</v>
       </c>
       <c r="N28">
-        <v>158.147413</v>
+        <v>157.2723135</v>
       </c>
       <c r="O28">
-        <v>39.53685325</v>
+        <v>39.318078375</v>
       </c>
       <c r="P28">
-        <v>118.61055975</v>
+        <v>117.954235125</v>
       </c>
       <c r="Q28">
-        <v>152.71055975</v>
+        <v>152.054235125</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1110849065468608</v>
+        <v>0.1118022705481816</v>
       </c>
       <c r="T28">
-        <v>1.009936741191617</v>
+        <v>1.021034134142957</v>
       </c>
       <c r="U28">
         <v>0.0535</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>7.950744238446379</v>
+        <v>7.656272229615031</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09244940750017254</v>
+        <v>0.09243148415566804</v>
       </c>
       <c r="C29">
-        <v>1200.719761785707</v>
+        <v>1184.40858938051</v>
       </c>
       <c r="D29">
-        <v>582.7587617857076</v>
+        <v>582.8045893805106</v>
       </c>
       <c r="E29">
-        <v>-285.061</v>
+        <v>-268.704</v>
       </c>
       <c r="F29">
-        <v>441.6390000000001</v>
+        <v>457.996</v>
       </c>
       <c r="G29">
         <v>1059.6</v>
@@ -3665,45 +3665,45 @@
         <v>180.9</v>
       </c>
       <c r="M29">
-        <v>23.6276865</v>
+        <v>24.8691828</v>
       </c>
       <c r="N29">
-        <v>157.2723135</v>
+        <v>156.0308172</v>
       </c>
       <c r="O29">
-        <v>39.318078375</v>
+        <v>39.0077043</v>
       </c>
       <c r="P29">
-        <v>117.954235125</v>
+        <v>117.0231129</v>
       </c>
       <c r="Q29">
-        <v>152.054235125</v>
+        <v>151.1231129</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1118022705481816</v>
+        <v>0.1125395613273167</v>
       </c>
       <c r="T29">
-        <v>1.021034134142957</v>
+        <v>1.032439788009612</v>
       </c>
       <c r="U29">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V29">
         <v>0.25</v>
       </c>
       <c r="W29">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y29">
-        <v>7.656272229615031</v>
+        <v>7.274062901656745</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09243148415566804</v>
+        <v>0.09225156081116354</v>
       </c>
       <c r="C30">
-        <v>1184.40858938051</v>
+        <v>1168.512028965329</v>
       </c>
       <c r="D30">
-        <v>582.8045893805106</v>
+        <v>583.2650289653294</v>
       </c>
       <c r="E30">
-        <v>-268.704</v>
+        <v>-252.347</v>
       </c>
       <c r="F30">
-        <v>457.996</v>
+        <v>474.3530000000001</v>
       </c>
       <c r="G30">
         <v>1059.6</v>
@@ -3747,28 +3747,28 @@
         <v>180.9</v>
       </c>
       <c r="M30">
-        <v>24.8691828</v>
+        <v>25.75736790000001</v>
       </c>
       <c r="N30">
-        <v>156.0308172</v>
+        <v>155.1426321</v>
       </c>
       <c r="O30">
-        <v>39.0077043</v>
+        <v>38.785658025</v>
       </c>
       <c r="P30">
-        <v>117.0231129</v>
+        <v>116.356974075</v>
       </c>
       <c r="Q30">
-        <v>151.1231129</v>
+        <v>150.456974075</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1125395613273167</v>
+        <v>0.1132976208607937</v>
       </c>
       <c r="T30">
-        <v>1.032439788009612</v>
+        <v>1.04416672790068</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>7.274062901656745</v>
+        <v>7.0232331464272</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09225156081116354</v>
+        <v>0.09207163746665906</v>
       </c>
       <c r="C31">
-        <v>1168.512028965329</v>
+        <v>1152.616196657784</v>
       </c>
       <c r="D31">
-        <v>583.2650289653294</v>
+        <v>583.7261966577846</v>
       </c>
       <c r="E31">
-        <v>-252.347</v>
+        <v>-235.9900000000001</v>
       </c>
       <c r="F31">
-        <v>474.353</v>
+        <v>490.71</v>
       </c>
       <c r="G31">
         <v>1059.6</v>
@@ -3829,28 +3829,28 @@
         <v>180.9</v>
       </c>
       <c r="M31">
-        <v>25.7573679</v>
+        <v>26.645553</v>
       </c>
       <c r="N31">
-        <v>155.1426321</v>
+        <v>154.254447</v>
       </c>
       <c r="O31">
-        <v>38.785658025</v>
+        <v>38.56361175</v>
       </c>
       <c r="P31">
-        <v>116.356974075</v>
+        <v>115.69083525</v>
       </c>
       <c r="Q31">
-        <v>150.456974075</v>
+        <v>149.79083525</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1132976208607937</v>
+        <v>0.1140773392380844</v>
       </c>
       <c r="T31">
-        <v>1.04416672790068</v>
+        <v>1.056228723217207</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>7.023233146427201</v>
+        <v>6.789125374879628</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09207163746665906</v>
+        <v>0.09189171412215458</v>
       </c>
       <c r="C32">
-        <v>1152.616196657784</v>
+        <v>1136.721094186312</v>
       </c>
       <c r="D32">
-        <v>583.7261966577846</v>
+        <v>584.1880941863124</v>
       </c>
       <c r="E32">
-        <v>-235.9900000000001</v>
+        <v>-219.633</v>
       </c>
       <c r="F32">
-        <v>490.71</v>
+        <v>507.067</v>
       </c>
       <c r="G32">
         <v>1059.6</v>
@@ -3911,28 +3911,28 @@
         <v>180.9</v>
       </c>
       <c r="M32">
-        <v>26.645553</v>
+        <v>27.5337381</v>
       </c>
       <c r="N32">
-        <v>154.254447</v>
+        <v>153.3662619</v>
       </c>
       <c r="O32">
-        <v>38.56361175</v>
+        <v>38.341565475</v>
       </c>
       <c r="P32">
-        <v>115.69083525</v>
+        <v>115.024696425</v>
       </c>
       <c r="Q32">
-        <v>149.79083525</v>
+        <v>149.124696425</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1140773392380844</v>
+        <v>0.1148796581480501</v>
       </c>
       <c r="T32">
-        <v>1.056228723217207</v>
+        <v>1.068640341586386</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>6.789125374879628</v>
+        <v>6.570121330528672</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09189171412215458</v>
+        <v>0.09171179077765011</v>
       </c>
       <c r="C33">
-        <v>1136.721094186312</v>
+        <v>1120.826723284823</v>
       </c>
       <c r="D33">
-        <v>584.1880941863124</v>
+        <v>584.6507232848236</v>
       </c>
       <c r="E33">
-        <v>-219.633</v>
+        <v>-203.2760000000001</v>
       </c>
       <c r="F33">
-        <v>507.067</v>
+        <v>523.424</v>
       </c>
       <c r="G33">
         <v>1059.6</v>
@@ -3993,28 +3993,28 @@
         <v>180.9</v>
       </c>
       <c r="M33">
-        <v>27.5337381</v>
+        <v>28.4219232</v>
       </c>
       <c r="N33">
-        <v>153.3662619</v>
+        <v>152.4780768</v>
       </c>
       <c r="O33">
-        <v>38.341565475</v>
+        <v>38.1195192</v>
       </c>
       <c r="P33">
-        <v>115.024696425</v>
+        <v>114.3585576</v>
       </c>
       <c r="Q33">
-        <v>149.124696425</v>
+        <v>148.4585576</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1148796581480501</v>
+        <v>0.1157055746730149</v>
       </c>
       <c r="T33">
-        <v>1.068640341586386</v>
+        <v>1.08141700755466</v>
       </c>
       <c r="U33">
         <v>0.0543</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>6.570121330528672</v>
+        <v>6.364805038949652</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09171179077765011</v>
+        <v>0.09153186743314562</v>
       </c>
       <c r="C34">
-        <v>1120.826723284823</v>
+        <v>1104.933085692726</v>
       </c>
       <c r="D34">
-        <v>584.6507232848236</v>
+        <v>585.1140856927263</v>
       </c>
       <c r="E34">
-        <v>-203.2760000000001</v>
+        <v>-186.919</v>
       </c>
       <c r="F34">
-        <v>523.424</v>
+        <v>539.7810000000001</v>
       </c>
       <c r="G34">
         <v>1059.6</v>
@@ -4075,28 +4075,28 @@
         <v>180.9</v>
       </c>
       <c r="M34">
-        <v>28.4219232</v>
+        <v>29.3101083</v>
       </c>
       <c r="N34">
-        <v>152.4780768</v>
+        <v>151.5898917</v>
       </c>
       <c r="O34">
-        <v>38.1195192</v>
+        <v>37.897472925</v>
       </c>
       <c r="P34">
-        <v>114.3585576</v>
+        <v>113.692418775</v>
       </c>
       <c r="Q34">
-        <v>148.4585576</v>
+        <v>147.792418775</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1157055746730149</v>
+        <v>0.1165561454226054</v>
       </c>
       <c r="T34">
-        <v>1.08141700755466</v>
+        <v>1.094575066536912</v>
       </c>
       <c r="U34">
         <v>0.0543</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>6.364805038949652</v>
+        <v>6.17193215898148</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09153186743314562</v>
+        <v>0.09160694408864115</v>
       </c>
       <c r="C35">
-        <v>1104.933085692726</v>
+        <v>1088.382649087809</v>
       </c>
       <c r="D35">
-        <v>585.1140856927263</v>
+        <v>584.9206490878092</v>
       </c>
       <c r="E35">
-        <v>-186.919</v>
+        <v>-170.562</v>
       </c>
       <c r="F35">
-        <v>539.7810000000001</v>
+        <v>556.138</v>
       </c>
       <c r="G35">
         <v>1059.6</v>
@@ -4157,45 +4157,45 @@
         <v>180.9</v>
       </c>
       <c r="M35">
-        <v>29.3101083</v>
+        <v>30.7544314</v>
       </c>
       <c r="N35">
-        <v>151.5898917</v>
+        <v>150.1455686</v>
       </c>
       <c r="O35">
-        <v>37.897472925</v>
+        <v>37.53639215</v>
       </c>
       <c r="P35">
-        <v>113.692418775</v>
+        <v>112.60917645</v>
       </c>
       <c r="Q35">
-        <v>147.792418775</v>
+        <v>146.70917645</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1165561454226054</v>
+        <v>0.1174324910433957</v>
       </c>
       <c r="T35">
-        <v>1.094575066536912</v>
+        <v>1.108131854579232</v>
       </c>
       <c r="U35">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V35">
         <v>0.25</v>
       </c>
       <c r="W35">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y35">
-        <v>6.17193215898148</v>
+        <v>5.882079159493093</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09160694408864115</v>
+        <v>0.09143452074413666</v>
       </c>
       <c r="C36">
-        <v>1088.382649087809</v>
+        <v>1072.470092092766</v>
       </c>
       <c r="D36">
-        <v>584.9206490878092</v>
+        <v>585.3650920927668</v>
       </c>
       <c r="E36">
-        <v>-170.562</v>
+        <v>-154.2049999999999</v>
       </c>
       <c r="F36">
-        <v>556.138</v>
+        <v>572.4950000000001</v>
       </c>
       <c r="G36">
         <v>1059.6</v>
@@ -4239,28 +4239,28 @@
         <v>180.9</v>
       </c>
       <c r="M36">
-        <v>30.7544314</v>
+        <v>31.65897350000001</v>
       </c>
       <c r="N36">
-        <v>150.1455686</v>
+        <v>149.2410265</v>
       </c>
       <c r="O36">
-        <v>37.53639215</v>
+        <v>37.310256625</v>
       </c>
       <c r="P36">
-        <v>112.60917645</v>
+        <v>111.930769875</v>
       </c>
       <c r="Q36">
-        <v>146.70917645</v>
+        <v>146.030769875</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1174324910433957</v>
+        <v>0.1183358011448256</v>
       </c>
       <c r="T36">
-        <v>1.108131854579232</v>
+        <v>1.122105774561315</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.882079159493093</v>
+        <v>5.714019754936147</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09143452074413666</v>
+        <v>0.09126209739963216</v>
       </c>
       <c r="C37">
-        <v>1072.470092092766</v>
+        <v>1056.558211017745</v>
       </c>
       <c r="D37">
-        <v>585.3650920927668</v>
+        <v>585.8102110177449</v>
       </c>
       <c r="E37">
-        <v>-154.2049999999999</v>
+        <v>-137.848</v>
       </c>
       <c r="F37">
-        <v>572.4950000000001</v>
+        <v>588.8520000000001</v>
       </c>
       <c r="G37">
         <v>1059.6</v>
@@ -4321,28 +4321,28 @@
         <v>180.9</v>
       </c>
       <c r="M37">
-        <v>31.65897350000001</v>
+        <v>32.56351560000001</v>
       </c>
       <c r="N37">
-        <v>149.2410265</v>
+        <v>148.3364844</v>
       </c>
       <c r="O37">
-        <v>37.310256625</v>
+        <v>37.0841211</v>
       </c>
       <c r="P37">
-        <v>111.930769875</v>
+        <v>111.2523633</v>
       </c>
       <c r="Q37">
-        <v>146.030769875</v>
+        <v>145.3523633</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1183358011448256</v>
+        <v>0.1192673396869253</v>
       </c>
       <c r="T37">
-        <v>1.122105774561315</v>
+        <v>1.136516379542839</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.714019754936147</v>
+        <v>5.555296983965698</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09126209739963217</v>
+        <v>0.09108967405512769</v>
       </c>
       <c r="C38">
-        <v>1056.558211017745</v>
+        <v>1040.647007405851</v>
       </c>
       <c r="D38">
-        <v>585.8102110177449</v>
+        <v>586.2560074058513</v>
       </c>
       <c r="E38">
-        <v>-137.8480000000001</v>
+        <v>-121.491</v>
       </c>
       <c r="F38">
-        <v>588.852</v>
+        <v>605.2090000000001</v>
       </c>
       <c r="G38">
         <v>1059.6</v>
@@ -4403,28 +4403,28 @@
         <v>180.9</v>
       </c>
       <c r="M38">
-        <v>32.5635156</v>
+        <v>33.4680577</v>
       </c>
       <c r="N38">
-        <v>148.3364844</v>
+        <v>147.4319423</v>
       </c>
       <c r="O38">
-        <v>37.0841211</v>
+        <v>36.857985575</v>
       </c>
       <c r="P38">
-        <v>111.2523633</v>
+        <v>110.573956725</v>
       </c>
       <c r="Q38">
-        <v>145.3523633</v>
+        <v>144.673956725</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1192673396869253</v>
+        <v>0.1202284508811551</v>
       </c>
       <c r="T38">
-        <v>1.136516379542839</v>
+        <v>1.151384464047585</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.555296983965699</v>
+        <v>5.405153822236897</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09108967405512769</v>
+        <v>0.09091725071062319</v>
       </c>
       <c r="C39">
-        <v>1040.647007405851</v>
+        <v>1024.736482804894</v>
       </c>
       <c r="D39">
-        <v>586.2560074058513</v>
+        <v>586.702482804894</v>
       </c>
       <c r="E39">
-        <v>-121.491</v>
+        <v>-105.134</v>
       </c>
       <c r="F39">
-        <v>605.2090000000001</v>
+        <v>621.566</v>
       </c>
       <c r="G39">
         <v>1059.6</v>
@@ -4485,28 +4485,28 @@
         <v>180.9</v>
       </c>
       <c r="M39">
-        <v>33.4680577</v>
+        <v>34.3725998</v>
       </c>
       <c r="N39">
-        <v>147.4319423</v>
+        <v>146.5274002</v>
       </c>
       <c r="O39">
-        <v>36.857985575</v>
+        <v>36.63185005</v>
       </c>
       <c r="P39">
-        <v>110.573956725</v>
+        <v>109.89555015</v>
       </c>
       <c r="Q39">
-        <v>144.673956725</v>
+        <v>143.99555015</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1202284508811551</v>
+        <v>0.1212205656622955</v>
       </c>
       <c r="T39">
-        <v>1.151384464047585</v>
+        <v>1.166732164181518</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.405153822236897</v>
+        <v>5.26291293217803</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09091725071062319</v>
+        <v>0.0907448273661187</v>
       </c>
       <c r="C40">
-        <v>1024.736482804894</v>
+        <v>1008.8266387674</v>
       </c>
       <c r="D40">
-        <v>586.702482804894</v>
+        <v>587.1496387673999</v>
       </c>
       <c r="E40">
-        <v>-105.134</v>
+        <v>-88.77700000000004</v>
       </c>
       <c r="F40">
-        <v>621.566</v>
+        <v>637.923</v>
       </c>
       <c r="G40">
         <v>1059.6</v>
@@ -4567,28 +4567,28 @@
         <v>180.9</v>
       </c>
       <c r="M40">
-        <v>34.3725998</v>
+        <v>35.2771419</v>
       </c>
       <c r="N40">
-        <v>146.5274002</v>
+        <v>145.6228581</v>
       </c>
       <c r="O40">
-        <v>36.63185005</v>
+        <v>36.405714525</v>
       </c>
       <c r="P40">
-        <v>109.89555015</v>
+        <v>109.217143575</v>
       </c>
       <c r="Q40">
-        <v>143.99555015</v>
+        <v>143.317143575</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1212205656622955</v>
+        <v>0.1222452087969159</v>
       </c>
       <c r="T40">
-        <v>1.166732164181518</v>
+        <v>1.182583067598529</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.26291293217803</v>
+        <v>5.127966446737569</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.0907448273661187</v>
+        <v>0.09057240402161423</v>
       </c>
       <c r="C41">
-        <v>1008.8266387674</v>
+        <v>992.9174768506324</v>
       </c>
       <c r="D41">
-        <v>587.1496387673999</v>
+        <v>587.5974768506326</v>
       </c>
       <c r="E41">
-        <v>-88.77700000000004</v>
+        <v>-72.41999999999996</v>
       </c>
       <c r="F41">
-        <v>637.923</v>
+        <v>654.2800000000001</v>
       </c>
       <c r="G41">
         <v>1059.6</v>
@@ -4649,28 +4649,28 @@
         <v>180.9</v>
       </c>
       <c r="M41">
-        <v>35.2771419</v>
+        <v>36.181684</v>
       </c>
       <c r="N41">
-        <v>145.6228581</v>
+        <v>144.718316</v>
       </c>
       <c r="O41">
-        <v>36.405714525</v>
+        <v>36.179579</v>
       </c>
       <c r="P41">
-        <v>109.217143575</v>
+        <v>108.538737</v>
       </c>
       <c r="Q41">
-        <v>143.317143575</v>
+        <v>142.638737</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1222452087969159</v>
+        <v>0.1233040067026904</v>
       </c>
       <c r="T41">
-        <v>1.182583067598529</v>
+        <v>1.198962334462775</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.127966446737569</v>
+        <v>4.99976728556913</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09057240402161423</v>
+        <v>0.09039998067710975</v>
       </c>
       <c r="C42">
-        <v>992.9174768506324</v>
+        <v>977.00899861661</v>
       </c>
       <c r="D42">
-        <v>587.5974768506326</v>
+        <v>588.0459986166102</v>
       </c>
       <c r="E42">
-        <v>-72.41999999999996</v>
+        <v>-56.06299999999999</v>
       </c>
       <c r="F42">
-        <v>654.2800000000001</v>
+        <v>670.6370000000001</v>
       </c>
       <c r="G42">
         <v>1059.6</v>
@@ -4731,28 +4731,28 @@
         <v>180.9</v>
       </c>
       <c r="M42">
-        <v>36.181684</v>
+        <v>37.0862261</v>
       </c>
       <c r="N42">
-        <v>144.718316</v>
+        <v>143.8137739</v>
       </c>
       <c r="O42">
-        <v>36.179579</v>
+        <v>35.953443475</v>
       </c>
       <c r="P42">
-        <v>108.538737</v>
+        <v>107.860330425</v>
       </c>
       <c r="Q42">
-        <v>142.638737</v>
+        <v>141.960330425</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1233040067026904</v>
+        <v>0.1243986960628979</v>
       </c>
       <c r="T42">
-        <v>1.198962334462775</v>
+        <v>1.215896830712249</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.99976728556913</v>
+        <v>4.877821742018662</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09039998067710975</v>
+        <v>0.09022755733260526</v>
       </c>
       <c r="C43">
-        <v>977.00899861661</v>
+        <v>961.1012056321239</v>
       </c>
       <c r="D43">
-        <v>588.0459986166102</v>
+        <v>588.4952056321241</v>
       </c>
       <c r="E43">
-        <v>-56.06299999999999</v>
+        <v>-39.70600000000002</v>
       </c>
       <c r="F43">
-        <v>670.6370000000001</v>
+        <v>686.994</v>
       </c>
       <c r="G43">
         <v>1059.6</v>
@@ -4813,28 +4813,28 @@
         <v>180.9</v>
       </c>
       <c r="M43">
-        <v>37.0862261</v>
+        <v>37.99076820000001</v>
       </c>
       <c r="N43">
-        <v>143.8137739</v>
+        <v>142.9092318</v>
       </c>
       <c r="O43">
-        <v>35.953443475</v>
+        <v>35.72730795</v>
       </c>
       <c r="P43">
-        <v>107.860330425</v>
+        <v>107.18192385</v>
       </c>
       <c r="Q43">
-        <v>141.960330425</v>
+        <v>141.28192385</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1243986960628979</v>
+        <v>0.125531133332078</v>
       </c>
       <c r="T43">
-        <v>1.215896830712249</v>
+        <v>1.233415275108257</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.877821742018662</v>
+        <v>4.761683129113456</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09022755733260526</v>
+        <v>0.09005513398810079</v>
       </c>
       <c r="C44">
-        <v>961.1012056321239</v>
+        <v>945.1940994687562</v>
       </c>
       <c r="D44">
-        <v>588.4952056321241</v>
+        <v>588.9450994687562</v>
       </c>
       <c r="E44">
-        <v>-39.70600000000002</v>
+        <v>-23.34900000000005</v>
       </c>
       <c r="F44">
-        <v>686.994</v>
+        <v>703.351</v>
       </c>
       <c r="G44">
         <v>1059.6</v>
@@ -4895,28 +4895,28 @@
         <v>180.9</v>
       </c>
       <c r="M44">
-        <v>37.99076820000001</v>
+        <v>38.8953103</v>
       </c>
       <c r="N44">
-        <v>142.9092318</v>
+        <v>142.0046897</v>
       </c>
       <c r="O44">
-        <v>35.72730795</v>
+        <v>35.501172425</v>
       </c>
       <c r="P44">
-        <v>107.18192385</v>
+        <v>106.503517275</v>
       </c>
       <c r="Q44">
-        <v>141.28192385</v>
+        <v>140.603517275</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.125531133332078</v>
+        <v>0.1267033052422821</v>
       </c>
       <c r="T44">
-        <v>1.233415275108257</v>
+        <v>1.251548401763774</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.761683129113456</v>
+        <v>4.65094631215733</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09005513398810079</v>
+        <v>0.08988271064359631</v>
       </c>
       <c r="C45">
-        <v>945.1940994687562</v>
+        <v>929.2876817028986</v>
       </c>
       <c r="D45">
-        <v>588.9450994687562</v>
+        <v>589.3956817028986</v>
       </c>
       <c r="E45">
-        <v>-23.34900000000005</v>
+        <v>-6.992000000000075</v>
       </c>
       <c r="F45">
-        <v>703.351</v>
+        <v>719.708</v>
       </c>
       <c r="G45">
         <v>1059.6</v>
@@ -4977,28 +4977,28 @@
         <v>180.9</v>
       </c>
       <c r="M45">
-        <v>38.8953103</v>
+        <v>39.7998524</v>
       </c>
       <c r="N45">
-        <v>142.0046897</v>
+        <v>141.1001476</v>
       </c>
       <c r="O45">
-        <v>35.501172425</v>
+        <v>35.2750369</v>
       </c>
       <c r="P45">
-        <v>106.503517275</v>
+        <v>105.8251107</v>
       </c>
       <c r="Q45">
-        <v>140.603517275</v>
+        <v>139.9251107</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1267033052422821</v>
+        <v>0.1279173404349934</v>
       </c>
       <c r="T45">
-        <v>1.251548401763774</v>
+        <v>1.270329140085559</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.65094631215733</v>
+        <v>4.545242986881027</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08988271064359631</v>
+        <v>0.09055403729909181</v>
       </c>
       <c r="C46">
-        <v>929.2876817028986</v>
+        <v>911.1802213158462</v>
       </c>
       <c r="D46">
-        <v>589.3956817028986</v>
+        <v>587.6452213158464</v>
       </c>
       <c r="E46">
-        <v>-6.992000000000075</v>
+        <v>9.365000000000009</v>
       </c>
       <c r="F46">
-        <v>719.708</v>
+        <v>736.0650000000001</v>
       </c>
       <c r="G46">
         <v>1059.6</v>
@@ -5059,45 +5059,45 @@
         <v>180.9</v>
       </c>
       <c r="M46">
-        <v>39.7998524</v>
+        <v>42.544557</v>
       </c>
       <c r="N46">
-        <v>141.1001476</v>
+        <v>138.355443</v>
       </c>
       <c r="O46">
-        <v>35.2750369</v>
+        <v>34.58886075</v>
       </c>
       <c r="P46">
-        <v>105.8251107</v>
+        <v>103.76658225</v>
       </c>
       <c r="Q46">
-        <v>139.9251107</v>
+        <v>137.86658225</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1279173404349934</v>
+        <v>0.1291755223619851</v>
       </c>
       <c r="T46">
-        <v>1.270329140085559</v>
+        <v>1.289792814346318</v>
       </c>
       <c r="U46">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V46">
         <v>0.25</v>
       </c>
       <c r="W46">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y46">
-        <v>4.545242986881027</v>
+        <v>4.252012778038798</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09055403729909181</v>
+        <v>0.09040036395458734</v>
       </c>
       <c r="C47">
-        <v>911.1802213158462</v>
+        <v>895.2230008444128</v>
       </c>
       <c r="D47">
-        <v>587.6452213158464</v>
+        <v>588.0450008444129</v>
       </c>
       <c r="E47">
-        <v>9.365000000000009</v>
+        <v>25.72199999999998</v>
       </c>
       <c r="F47">
-        <v>736.0650000000001</v>
+        <v>752.422</v>
       </c>
       <c r="G47">
         <v>1059.6</v>
@@ -5141,28 +5141,28 @@
         <v>180.9</v>
       </c>
       <c r="M47">
-        <v>42.544557</v>
+        <v>43.4899916</v>
       </c>
       <c r="N47">
-        <v>138.355443</v>
+        <v>137.4100084</v>
       </c>
       <c r="O47">
-        <v>34.58886075</v>
+        <v>34.3525021</v>
       </c>
       <c r="P47">
-        <v>103.76658225</v>
+        <v>103.0575063</v>
       </c>
       <c r="Q47">
-        <v>137.86658225</v>
+        <v>137.1575063</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1291755223619851</v>
+        <v>0.1304803036196062</v>
       </c>
       <c r="T47">
-        <v>1.289792814346318</v>
+        <v>1.309977365431551</v>
       </c>
       <c r="U47">
         <v>0.0578</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>4.252012778038798</v>
+        <v>4.15957771764665</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09040036395458734</v>
+        <v>0.09024669061008285</v>
       </c>
       <c r="C48">
-        <v>895.2230008444128</v>
+        <v>879.2663246894102</v>
       </c>
       <c r="D48">
-        <v>588.0450008444129</v>
+        <v>588.4453246894104</v>
       </c>
       <c r="E48">
-        <v>25.72199999999998</v>
+        <v>42.07900000000006</v>
       </c>
       <c r="F48">
-        <v>752.422</v>
+        <v>768.7790000000001</v>
       </c>
       <c r="G48">
         <v>1059.6</v>
@@ -5223,28 +5223,28 @@
         <v>180.9</v>
       </c>
       <c r="M48">
-        <v>43.4899916</v>
+        <v>44.43542620000001</v>
       </c>
       <c r="N48">
-        <v>137.4100084</v>
+        <v>136.4645738</v>
       </c>
       <c r="O48">
-        <v>34.3525021</v>
+        <v>34.11614345</v>
       </c>
       <c r="P48">
-        <v>103.0575063</v>
+        <v>102.34843035</v>
       </c>
       <c r="Q48">
-        <v>137.1575063</v>
+        <v>136.44843035</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1304803036196062</v>
+        <v>0.1318343219058167</v>
       </c>
       <c r="T48">
-        <v>1.309977365431551</v>
+        <v>1.33092359768981</v>
       </c>
       <c r="U48">
         <v>0.0578</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.15957771764665</v>
+        <v>4.071076064079699</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09024669061008285</v>
+        <v>0.09135301726557836</v>
       </c>
       <c r="C49">
-        <v>879.2663246894102</v>
+        <v>860.0394128008071</v>
       </c>
       <c r="D49">
-        <v>588.4453246894104</v>
+        <v>585.5754128008073</v>
       </c>
       <c r="E49">
-        <v>42.07900000000006</v>
+        <v>58.43600000000004</v>
       </c>
       <c r="F49">
-        <v>768.7790000000001</v>
+        <v>785.1360000000001</v>
       </c>
       <c r="G49">
         <v>1059.6</v>
@@ -5305,45 +5305,45 @@
         <v>180.9</v>
       </c>
       <c r="M49">
-        <v>44.43542620000001</v>
+        <v>48.1288368</v>
       </c>
       <c r="N49">
-        <v>136.4645738</v>
+        <v>132.7711632</v>
       </c>
       <c r="O49">
-        <v>34.11614345</v>
+        <v>33.1927908</v>
       </c>
       <c r="P49">
-        <v>102.34843035</v>
+        <v>99.57837239999999</v>
       </c>
       <c r="Q49">
-        <v>136.44843035</v>
+        <v>133.6783724</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1318343219058167</v>
+        <v>0.1332404178184199</v>
       </c>
       <c r="T49">
-        <v>1.33092359768981</v>
+        <v>1.352675454265695</v>
       </c>
       <c r="U49">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V49">
         <v>0.25</v>
       </c>
       <c r="W49">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y49">
-        <v>4.071076064079699</v>
+        <v>3.758661376998</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09135301726557836</v>
+        <v>0.09122559392107386</v>
       </c>
       <c r="C50">
-        <v>860.0394128008072</v>
+        <v>844.0115332965994</v>
       </c>
       <c r="D50">
-        <v>585.5754128008073</v>
+        <v>585.9045332965995</v>
       </c>
       <c r="E50">
-        <v>58.43599999999992</v>
+        <v>74.79300000000001</v>
       </c>
       <c r="F50">
-        <v>785.136</v>
+        <v>801.4930000000001</v>
       </c>
       <c r="G50">
         <v>1059.6</v>
@@ -5387,28 +5387,28 @@
         <v>180.9</v>
       </c>
       <c r="M50">
-        <v>48.12883679999999</v>
+        <v>49.13152090000001</v>
       </c>
       <c r="N50">
-        <v>132.7711632</v>
+        <v>131.7684791</v>
       </c>
       <c r="O50">
-        <v>33.1927908</v>
+        <v>32.942119775</v>
       </c>
       <c r="P50">
-        <v>99.57837240000001</v>
+        <v>98.826359325</v>
       </c>
       <c r="Q50">
-        <v>133.6783724</v>
+        <v>132.926359325</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1332404178184199</v>
+        <v>0.1347016547472037</v>
       </c>
       <c r="T50">
-        <v>1.352675454265695</v>
+        <v>1.375280324824948</v>
       </c>
       <c r="U50">
         <v>0.0613</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.758661376998</v>
+        <v>3.681954001957224</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09122559392107386</v>
+        <v>0.09109817057656938</v>
       </c>
       <c r="C51">
-        <v>844.0115332965994</v>
+        <v>827.9840239623601</v>
       </c>
       <c r="D51">
-        <v>585.9045332965995</v>
+        <v>586.2340239623602</v>
       </c>
       <c r="E51">
-        <v>74.79300000000001</v>
+        <v>91.14999999999998</v>
       </c>
       <c r="F51">
-        <v>801.4930000000001</v>
+        <v>817.85</v>
       </c>
       <c r="G51">
         <v>1059.6</v>
@@ -5469,28 +5469,28 @@
         <v>180.9</v>
       </c>
       <c r="M51">
-        <v>49.13152090000001</v>
+        <v>50.134205</v>
       </c>
       <c r="N51">
-        <v>131.7684791</v>
+        <v>130.765795</v>
       </c>
       <c r="O51">
-        <v>32.942119775</v>
+        <v>32.69144875</v>
       </c>
       <c r="P51">
-        <v>98.826359325</v>
+        <v>98.07434624999999</v>
       </c>
       <c r="Q51">
-        <v>132.926359325</v>
+        <v>132.17434625</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1347016547472037</v>
+        <v>0.1362213411531388</v>
       </c>
       <c r="T51">
-        <v>1.375280324824948</v>
+        <v>1.398789390206571</v>
       </c>
       <c r="U51">
         <v>0.0613</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.681954001957224</v>
+        <v>3.60831492191808</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09109817057656938</v>
+        <v>0.09097074723206491</v>
       </c>
       <c r="C52">
-        <v>827.9840239623601</v>
+        <v>811.9568854229495</v>
       </c>
       <c r="D52">
-        <v>586.2340239623602</v>
+        <v>586.5638854229495</v>
       </c>
       <c r="E52">
-        <v>91.14999999999998</v>
+        <v>107.5069999999999</v>
       </c>
       <c r="F52">
-        <v>817.85</v>
+        <v>834.207</v>
       </c>
       <c r="G52">
         <v>1059.6</v>
@@ -5551,28 +5551,28 @@
         <v>180.9</v>
       </c>
       <c r="M52">
-        <v>50.134205</v>
+        <v>51.1368891</v>
       </c>
       <c r="N52">
-        <v>130.765795</v>
+        <v>129.7631109</v>
       </c>
       <c r="O52">
-        <v>32.69144875</v>
+        <v>32.440777725</v>
       </c>
       <c r="P52">
-        <v>98.07434624999999</v>
+        <v>97.32233317500001</v>
       </c>
       <c r="Q52">
-        <v>132.17434625</v>
+        <v>131.422333175</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1362213411531388</v>
+        <v>0.1378030555756427</v>
       </c>
       <c r="T52">
-        <v>1.398789390206571</v>
+        <v>1.42325800927724</v>
       </c>
       <c r="U52">
         <v>0.0613</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.60831492191808</v>
+        <v>3.537563648939294</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09097074723206491</v>
+        <v>0.09193532388756043</v>
       </c>
       <c r="C53">
-        <v>811.9568854229495</v>
+        <v>793.1120725003923</v>
       </c>
       <c r="D53">
-        <v>586.5638854229495</v>
+        <v>584.0760725003923</v>
       </c>
       <c r="E53">
-        <v>107.5069999999999</v>
+        <v>123.864</v>
       </c>
       <c r="F53">
-        <v>834.207</v>
+        <v>850.5640000000001</v>
       </c>
       <c r="G53">
         <v>1059.6</v>
@@ -5633,45 +5633,45 @@
         <v>180.9</v>
       </c>
       <c r="M53">
-        <v>51.1368891</v>
+        <v>54.52115240000001</v>
       </c>
       <c r="N53">
-        <v>129.7631109</v>
+        <v>126.3788476</v>
       </c>
       <c r="O53">
-        <v>32.440777725</v>
+        <v>31.5947119</v>
       </c>
       <c r="P53">
-        <v>97.32233317500001</v>
+        <v>94.78413570000001</v>
       </c>
       <c r="Q53">
-        <v>131.422333175</v>
+        <v>128.8841357</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1378030555756427</v>
+        <v>0.1394506747657509</v>
       </c>
       <c r="T53">
-        <v>1.42325800927724</v>
+        <v>1.44874615414252</v>
       </c>
       <c r="U53">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V53">
         <v>0.25</v>
       </c>
       <c r="W53">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y53">
-        <v>3.537563648939294</v>
+        <v>3.317978289835267</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09193532388756043</v>
+        <v>0.09182890054305595</v>
       </c>
       <c r="C54">
-        <v>793.1120725003923</v>
+        <v>777.0285208129203</v>
       </c>
       <c r="D54">
-        <v>584.0760725003923</v>
+        <v>584.3495208129204</v>
       </c>
       <c r="E54">
-        <v>123.864</v>
+        <v>140.221</v>
       </c>
       <c r="F54">
-        <v>850.5640000000001</v>
+        <v>866.921</v>
       </c>
       <c r="G54">
         <v>1059.6</v>
@@ -5715,28 +5715,28 @@
         <v>180.9</v>
       </c>
       <c r="M54">
-        <v>54.52115240000001</v>
+        <v>55.5696361</v>
       </c>
       <c r="N54">
-        <v>126.3788476</v>
+        <v>125.3303639</v>
       </c>
       <c r="O54">
-        <v>31.5947119</v>
+        <v>31.332590975</v>
       </c>
       <c r="P54">
-        <v>94.78413570000001</v>
+        <v>93.99777292500001</v>
       </c>
       <c r="Q54">
-        <v>128.8841357</v>
+        <v>128.097772925</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1394506747657509</v>
+        <v>0.1411684054107573</v>
       </c>
       <c r="T54">
-        <v>1.44874615414252</v>
+        <v>1.475318900916961</v>
       </c>
       <c r="U54">
         <v>0.0641</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.317978289835267</v>
+        <v>3.255374925876112</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09182890054305595</v>
+        <v>0.09172247719855145</v>
       </c>
       <c r="C55">
-        <v>777.0285208129203</v>
+        <v>760.9452252872967</v>
       </c>
       <c r="D55">
-        <v>584.3495208129204</v>
+        <v>584.6232252872969</v>
       </c>
       <c r="E55">
-        <v>140.221</v>
+        <v>156.5780000000001</v>
       </c>
       <c r="F55">
-        <v>866.921</v>
+        <v>883.2780000000001</v>
       </c>
       <c r="G55">
         <v>1059.6</v>
@@ -5797,28 +5797,28 @@
         <v>180.9</v>
       </c>
       <c r="M55">
-        <v>55.5696361</v>
+        <v>56.61811980000001</v>
       </c>
       <c r="N55">
-        <v>125.3303639</v>
+        <v>124.2818802</v>
       </c>
       <c r="O55">
-        <v>31.332590975</v>
+        <v>31.07047005</v>
       </c>
       <c r="P55">
-        <v>93.99777292500001</v>
+        <v>93.21141014999999</v>
       </c>
       <c r="Q55">
-        <v>128.097772925</v>
+        <v>127.31141015</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1411684054107573</v>
+        <v>0.142960819996851</v>
       </c>
       <c r="T55">
-        <v>1.475318900916961</v>
+        <v>1.503046984507682</v>
       </c>
       <c r="U55">
         <v>0.0641</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.255374925876112</v>
+        <v>3.195090205026553</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09172247719855145</v>
+        <v>0.09161605385404697</v>
       </c>
       <c r="C56">
-        <v>760.9452252872967</v>
+        <v>744.8621862836422</v>
       </c>
       <c r="D56">
-        <v>584.6232252872969</v>
+        <v>584.8971862836426</v>
       </c>
       <c r="E56">
-        <v>156.5780000000001</v>
+        <v>172.9350000000001</v>
       </c>
       <c r="F56">
-        <v>883.2780000000001</v>
+        <v>899.6350000000001</v>
       </c>
       <c r="G56">
         <v>1059.6</v>
@@ -5879,28 +5879,28 @@
         <v>180.9</v>
       </c>
       <c r="M56">
-        <v>56.61811980000001</v>
+        <v>57.66660350000001</v>
       </c>
       <c r="N56">
-        <v>124.2818802</v>
+        <v>123.2333965</v>
       </c>
       <c r="O56">
-        <v>31.07047005</v>
+        <v>30.808349125</v>
       </c>
       <c r="P56">
-        <v>93.21141014999999</v>
+        <v>92.42504737499999</v>
       </c>
       <c r="Q56">
-        <v>127.31141015</v>
+        <v>126.525047375</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.142960819996851</v>
+        <v>0.1448328974534377</v>
       </c>
       <c r="T56">
-        <v>1.503046984507682</v>
+        <v>1.532007427369102</v>
       </c>
       <c r="U56">
         <v>0.0641</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.195090205026553</v>
+        <v>3.136997655844253</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09161605385404697</v>
+        <v>0.09150963050954249</v>
       </c>
       <c r="C57">
-        <v>744.8621862836422</v>
+        <v>728.7794041627536</v>
       </c>
       <c r="D57">
-        <v>584.8971862836426</v>
+        <v>585.1714041627538</v>
       </c>
       <c r="E57">
-        <v>172.9350000000001</v>
+        <v>189.292</v>
       </c>
       <c r="F57">
-        <v>899.6350000000001</v>
+        <v>915.9920000000001</v>
       </c>
       <c r="G57">
         <v>1059.6</v>
@@ -5961,28 +5961,28 @@
         <v>180.9</v>
       </c>
       <c r="M57">
-        <v>57.66660350000001</v>
+        <v>58.71508720000001</v>
       </c>
       <c r="N57">
-        <v>123.2333965</v>
+        <v>122.1849128</v>
       </c>
       <c r="O57">
-        <v>30.808349125</v>
+        <v>30.5462282</v>
       </c>
       <c r="P57">
-        <v>92.42504737499999</v>
+        <v>91.6386846</v>
       </c>
       <c r="Q57">
-        <v>126.525047375</v>
+        <v>125.7386846</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1448328974534377</v>
+        <v>0.1467900693398693</v>
       </c>
       <c r="T57">
-        <v>1.532007427369102</v>
+        <v>1.562284253996949</v>
       </c>
       <c r="U57">
         <v>0.0641</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.136997655844253</v>
+        <v>3.08097984056132</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09150963050954249</v>
+        <v>0.091403207165038</v>
       </c>
       <c r="C58">
-        <v>728.7794041627536</v>
+        <v>712.6968792861035</v>
       </c>
       <c r="D58">
-        <v>585.1714041627538</v>
+        <v>585.4458792861037</v>
       </c>
       <c r="E58">
-        <v>189.292</v>
+        <v>205.6490000000001</v>
       </c>
       <c r="F58">
-        <v>915.9920000000001</v>
+        <v>932.3490000000002</v>
       </c>
       <c r="G58">
         <v>1059.6</v>
@@ -6043,28 +6043,28 @@
         <v>180.9</v>
       </c>
       <c r="M58">
-        <v>58.71508720000001</v>
+        <v>59.76357090000001</v>
       </c>
       <c r="N58">
-        <v>122.1849128</v>
+        <v>121.1364291</v>
       </c>
       <c r="O58">
-        <v>30.5462282</v>
+        <v>30.284107275</v>
       </c>
       <c r="P58">
-        <v>91.6386846</v>
+        <v>90.85232182499999</v>
       </c>
       <c r="Q58">
-        <v>125.7386846</v>
+        <v>124.952321825</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1467900693398693</v>
+        <v>0.1488382724768326</v>
       </c>
       <c r="T58">
-        <v>1.562284253996949</v>
+        <v>1.593969305119116</v>
       </c>
       <c r="U58">
         <v>0.0641</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.08097984056132</v>
+        <v>3.026927562656735</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.091403207165038</v>
+        <v>0.09468978382053353</v>
       </c>
       <c r="C59">
-        <v>712.6968792861035</v>
+        <v>687.9806206518419</v>
       </c>
       <c r="D59">
-        <v>585.4458792861037</v>
+        <v>577.0866206518421</v>
       </c>
       <c r="E59">
-        <v>205.6490000000001</v>
+        <v>222.0060000000001</v>
       </c>
       <c r="F59">
-        <v>932.3490000000002</v>
+        <v>948.7060000000001</v>
       </c>
       <c r="G59">
         <v>1059.6</v>
@@ -6125,45 +6125,45 @@
         <v>180.9</v>
       </c>
       <c r="M59">
-        <v>59.76357090000001</v>
+        <v>68.21196140000002</v>
       </c>
       <c r="N59">
-        <v>121.1364291</v>
+        <v>112.6880386</v>
       </c>
       <c r="O59">
-        <v>30.284107275</v>
+        <v>28.17200965</v>
       </c>
       <c r="P59">
-        <v>90.85232182499999</v>
+        <v>84.51602894999999</v>
       </c>
       <c r="Q59">
-        <v>124.952321825</v>
+        <v>118.61602895</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1488382724768326</v>
+        <v>0.1509840090965084</v>
       </c>
       <c r="T59">
-        <v>1.593969305119116</v>
+        <v>1.627163168199481</v>
       </c>
       <c r="U59">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V59">
         <v>0.25</v>
       </c>
       <c r="W59">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y59">
-        <v>3.026927562656735</v>
+        <v>2.652027537211383</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09468978382053353</v>
+        <v>0.09464186047602904</v>
       </c>
       <c r="C60">
-        <v>687.9806206518421</v>
+        <v>671.7437961131606</v>
       </c>
       <c r="D60">
-        <v>577.0866206518421</v>
+        <v>577.2067961131607</v>
       </c>
       <c r="E60">
-        <v>222.006</v>
+        <v>238.3629999999999</v>
       </c>
       <c r="F60">
-        <v>948.706</v>
+        <v>965.063</v>
       </c>
       <c r="G60">
         <v>1059.6</v>
@@ -6207,28 +6207,28 @@
         <v>180.9</v>
       </c>
       <c r="M60">
-        <v>68.21196140000001</v>
+        <v>69.3880297</v>
       </c>
       <c r="N60">
-        <v>112.6880386</v>
+        <v>111.5119703</v>
       </c>
       <c r="O60">
-        <v>28.17200965</v>
+        <v>27.877992575</v>
       </c>
       <c r="P60">
-        <v>84.51602894999999</v>
+        <v>83.63397772499999</v>
       </c>
       <c r="Q60">
-        <v>118.61602895</v>
+        <v>117.733977725</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1509840090965084</v>
+        <v>0.1532344157951928</v>
       </c>
       <c r="T60">
-        <v>1.62716316819948</v>
+        <v>1.661976244113033</v>
       </c>
       <c r="U60">
         <v>0.07190000000000001</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.652027537211384</v>
+        <v>2.607077917936615</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.09464186047602904</v>
+        <v>0.09459393713152456</v>
       </c>
       <c r="C61">
-        <v>671.7437961131606</v>
+        <v>655.5070216368068</v>
       </c>
       <c r="D61">
-        <v>577.2067961131607</v>
+        <v>577.3270216368068</v>
       </c>
       <c r="E61">
-        <v>238.3629999999999</v>
+        <v>254.7199999999999</v>
       </c>
       <c r="F61">
-        <v>965.063</v>
+        <v>981.42</v>
       </c>
       <c r="G61">
         <v>1059.6</v>
@@ -6289,28 +6289,28 @@
         <v>180.9</v>
       </c>
       <c r="M61">
-        <v>69.3880297</v>
+        <v>70.564098</v>
       </c>
       <c r="N61">
-        <v>111.5119703</v>
+        <v>110.335902</v>
       </c>
       <c r="O61">
-        <v>27.877992575</v>
+        <v>27.5839755</v>
       </c>
       <c r="P61">
-        <v>83.63397772499999</v>
+        <v>82.7519265</v>
       </c>
       <c r="Q61">
-        <v>117.733977725</v>
+        <v>116.8519265</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1532344157951928</v>
+        <v>0.1555973428288114</v>
       </c>
       <c r="T61">
-        <v>1.661976244113033</v>
+        <v>1.698529973822265</v>
       </c>
       <c r="U61">
         <v>0.07190000000000001</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.607077917936615</v>
+        <v>2.563626619304338</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.09459393713152456</v>
+        <v>0.09454601378702007</v>
       </c>
       <c r="C62">
-        <v>655.5070216368068</v>
+        <v>639.2702972540687</v>
       </c>
       <c r="D62">
-        <v>577.3270216368068</v>
+        <v>577.4472972540688</v>
       </c>
       <c r="E62">
-        <v>254.7199999999999</v>
+        <v>271.077</v>
       </c>
       <c r="F62">
-        <v>981.42</v>
+        <v>997.777</v>
       </c>
       <c r="G62">
         <v>1059.6</v>
@@ -6371,28 +6371,28 @@
         <v>180.9</v>
       </c>
       <c r="M62">
-        <v>70.564098</v>
+        <v>71.74016630000001</v>
       </c>
       <c r="N62">
-        <v>110.335902</v>
+        <v>109.1598337</v>
       </c>
       <c r="O62">
-        <v>27.5839755</v>
+        <v>27.289958425</v>
       </c>
       <c r="P62">
-        <v>82.7519265</v>
+        <v>81.869875275</v>
       </c>
       <c r="Q62">
-        <v>116.8519265</v>
+        <v>115.969875275</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1555973428288114</v>
+        <v>0.1580814456077438</v>
       </c>
       <c r="T62">
-        <v>1.698529973822265</v>
+        <v>1.736958253772995</v>
       </c>
       <c r="U62">
         <v>0.07190000000000001</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.563626619304338</v>
+        <v>2.521599953414102</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.09454601378702007</v>
+        <v>0.09631159044251558</v>
       </c>
       <c r="C63">
-        <v>639.2702972540687</v>
+        <v>618.5149763842314</v>
       </c>
       <c r="D63">
-        <v>577.4472972540688</v>
+        <v>573.0489763842315</v>
       </c>
       <c r="E63">
-        <v>271.077</v>
+        <v>287.434</v>
       </c>
       <c r="F63">
-        <v>997.777</v>
+        <v>1014.134</v>
       </c>
       <c r="G63">
         <v>1059.6</v>
@@ -6453,45 +6453,45 @@
         <v>180.9</v>
       </c>
       <c r="M63">
-        <v>71.74016630000001</v>
+        <v>76.87135720000001</v>
       </c>
       <c r="N63">
-        <v>109.1598337</v>
+        <v>104.0286428</v>
       </c>
       <c r="O63">
-        <v>27.289958425</v>
+        <v>26.0071607</v>
       </c>
       <c r="P63">
-        <v>81.869875275</v>
+        <v>78.0214821</v>
       </c>
       <c r="Q63">
-        <v>115.969875275</v>
+        <v>112.1214821</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1580814456077438</v>
+        <v>0.1606962906381989</v>
       </c>
       <c r="T63">
-        <v>1.736958253772995</v>
+        <v>1.777409074773763</v>
       </c>
       <c r="U63">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V63">
         <v>0.25</v>
       </c>
       <c r="W63">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y63">
-        <v>2.521599953414102</v>
+        <v>2.353282244378014</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.09631159044251558</v>
+        <v>0.0962929170980111</v>
       </c>
       <c r="C64">
-        <v>618.5149763842314</v>
+        <v>602.2041439329737</v>
       </c>
       <c r="D64">
-        <v>573.0489763842315</v>
+        <v>573.0951439329737</v>
       </c>
       <c r="E64">
-        <v>287.434</v>
+        <v>303.7909999999999</v>
       </c>
       <c r="F64">
-        <v>1014.134</v>
+        <v>1030.491</v>
       </c>
       <c r="G64">
         <v>1059.6</v>
@@ -6535,28 +6535,28 @@
         <v>180.9</v>
       </c>
       <c r="M64">
-        <v>76.87135720000001</v>
+        <v>78.11121780000001</v>
       </c>
       <c r="N64">
-        <v>104.0286428</v>
+        <v>102.7887822</v>
       </c>
       <c r="O64">
-        <v>26.0071607</v>
+        <v>25.69719555</v>
       </c>
       <c r="P64">
-        <v>78.0214821</v>
+        <v>77.09158665</v>
       </c>
       <c r="Q64">
-        <v>112.1214821</v>
+        <v>111.19158665</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1606962906381989</v>
+        <v>0.1634524786432733</v>
       </c>
       <c r="T64">
-        <v>1.777409074773763</v>
+        <v>1.820046426639438</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.353282244378014</v>
+        <v>2.315928557959315</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.0962929170980111</v>
+        <v>0.09627424375350663</v>
       </c>
       <c r="C65">
-        <v>602.2041439329737</v>
+        <v>585.8933189212694</v>
       </c>
       <c r="D65">
-        <v>573.0951439329737</v>
+        <v>573.1413189212694</v>
       </c>
       <c r="E65">
-        <v>303.7909999999999</v>
+        <v>320.1479999999999</v>
       </c>
       <c r="F65">
-        <v>1030.491</v>
+        <v>1046.848</v>
       </c>
       <c r="G65">
         <v>1059.6</v>
@@ -6617,28 +6617,28 @@
         <v>180.9</v>
       </c>
       <c r="M65">
-        <v>78.11121780000001</v>
+        <v>79.35107840000001</v>
       </c>
       <c r="N65">
-        <v>102.7887822</v>
+        <v>101.5489216</v>
       </c>
       <c r="O65">
-        <v>25.69719555</v>
+        <v>25.3872304</v>
       </c>
       <c r="P65">
-        <v>77.09158665</v>
+        <v>76.16169120000001</v>
       </c>
       <c r="Q65">
-        <v>111.19158665</v>
+        <v>110.2616912</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1634524786432733</v>
+        <v>0.1663617882041851</v>
       </c>
       <c r="T65">
-        <v>1.820046426639438</v>
+        <v>1.865052520275428</v>
       </c>
       <c r="U65">
         <v>0.07580000000000001</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.315928557959315</v>
+        <v>2.279742174241201</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.09627424375350663</v>
+        <v>0.09625557040900214</v>
       </c>
       <c r="C66">
-        <v>585.8933189212694</v>
+        <v>569.582501350917</v>
       </c>
       <c r="D66">
-        <v>573.1413189212694</v>
+        <v>573.1875013509173</v>
       </c>
       <c r="E66">
-        <v>320.1479999999999</v>
+        <v>336.5050000000001</v>
       </c>
       <c r="F66">
-        <v>1046.848</v>
+        <v>1063.205</v>
       </c>
       <c r="G66">
         <v>1059.6</v>
@@ -6699,28 +6699,28 @@
         <v>180.9</v>
       </c>
       <c r="M66">
-        <v>79.35107840000001</v>
+        <v>80.59093900000002</v>
       </c>
       <c r="N66">
-        <v>101.5489216</v>
+        <v>100.309061</v>
       </c>
       <c r="O66">
-        <v>25.3872304</v>
+        <v>25.07726525</v>
       </c>
       <c r="P66">
-        <v>76.16169120000001</v>
+        <v>75.23179574999999</v>
       </c>
       <c r="Q66">
-        <v>110.2616912</v>
+        <v>109.33179575</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1663617882041851</v>
+        <v>0.1694373440257204</v>
       </c>
       <c r="T66">
-        <v>1.865052520275428</v>
+        <v>1.912630390690617</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.279742174241201</v>
+        <v>2.244669217714413</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.09625557040900214</v>
+        <v>0.09623689706449765</v>
       </c>
       <c r="C67">
-        <v>569.582501350917</v>
+        <v>553.2716912237158</v>
       </c>
       <c r="D67">
-        <v>573.1875013509173</v>
+        <v>573.2336912237159</v>
       </c>
       <c r="E67">
-        <v>336.5050000000001</v>
+        <v>352.8620000000001</v>
       </c>
       <c r="F67">
-        <v>1063.205</v>
+        <v>1079.562</v>
       </c>
       <c r="G67">
         <v>1059.6</v>
@@ -6781,28 +6781,28 @@
         <v>180.9</v>
       </c>
       <c r="M67">
-        <v>80.59093900000002</v>
+        <v>81.83079960000002</v>
       </c>
       <c r="N67">
-        <v>100.309061</v>
+        <v>99.06920039999999</v>
       </c>
       <c r="O67">
-        <v>25.07726525</v>
+        <v>24.7673001</v>
       </c>
       <c r="P67">
-        <v>75.23179574999999</v>
+        <v>74.30190029999999</v>
       </c>
       <c r="Q67">
-        <v>109.33179575</v>
+        <v>108.4019003</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1694373440257204</v>
+        <v>0.1726938148955813</v>
       </c>
       <c r="T67">
-        <v>1.912630390690617</v>
+        <v>1.963006959365524</v>
       </c>
       <c r="U67">
         <v>0.07580000000000001</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.244669217714413</v>
+        <v>2.210659078052073</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.09623689706449765</v>
+        <v>0.09621822371999317</v>
       </c>
       <c r="C68">
-        <v>553.2716912237158</v>
+        <v>536.9608885414652</v>
       </c>
       <c r="D68">
-        <v>573.2336912237159</v>
+        <v>573.2798885414653</v>
       </c>
       <c r="E68">
-        <v>352.8620000000001</v>
+        <v>369.2190000000001</v>
       </c>
       <c r="F68">
-        <v>1079.562</v>
+        <v>1095.919</v>
       </c>
       <c r="G68">
         <v>1059.6</v>
@@ -6863,28 +6863,28 @@
         <v>180.9</v>
       </c>
       <c r="M68">
-        <v>81.83079960000002</v>
+        <v>83.07066020000002</v>
       </c>
       <c r="N68">
-        <v>99.06920039999999</v>
+        <v>97.82933979999999</v>
       </c>
       <c r="O68">
-        <v>24.7673001</v>
+        <v>24.45733495</v>
       </c>
       <c r="P68">
-        <v>74.30190029999999</v>
+        <v>73.37200485</v>
       </c>
       <c r="Q68">
-        <v>108.4019003</v>
+        <v>107.47200485</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1726938148955813</v>
+        <v>0.1761476476363429</v>
       </c>
       <c r="T68">
-        <v>1.963006959365524</v>
+        <v>2.016436653414667</v>
       </c>
       <c r="U68">
         <v>0.07580000000000001</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.210659078052073</v>
+        <v>2.177664166439356</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.09621822371999317</v>
+        <v>0.09619955037548869</v>
       </c>
       <c r="C69">
-        <v>536.9608885414652</v>
+        <v>520.6500933059649</v>
       </c>
       <c r="D69">
-        <v>573.2798885414653</v>
+        <v>573.3260933059652</v>
       </c>
       <c r="E69">
-        <v>369.2190000000001</v>
+        <v>385.576</v>
       </c>
       <c r="F69">
-        <v>1095.919</v>
+        <v>1112.276</v>
       </c>
       <c r="G69">
         <v>1059.6</v>
@@ -6945,28 +6945,28 @@
         <v>180.9</v>
       </c>
       <c r="M69">
-        <v>83.07066020000002</v>
+        <v>84.31052080000001</v>
       </c>
       <c r="N69">
-        <v>97.82933979999999</v>
+        <v>96.5894792</v>
       </c>
       <c r="O69">
-        <v>24.45733495</v>
+        <v>24.1473698</v>
       </c>
       <c r="P69">
-        <v>73.37200485</v>
+        <v>72.44210939999999</v>
       </c>
       <c r="Q69">
-        <v>107.47200485</v>
+        <v>106.5421094</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1761476476363429</v>
+        <v>0.1798173449234022</v>
       </c>
       <c r="T69">
-        <v>2.016436653414667</v>
+        <v>2.073205703341882</v>
       </c>
       <c r="U69">
         <v>0.07580000000000001</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.177664166439356</v>
+        <v>2.145639693403483</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.09619955037548869</v>
+        <v>0.09618087703098421</v>
       </c>
       <c r="C70">
-        <v>520.6500933059649</v>
+        <v>504.3393055190161</v>
       </c>
       <c r="D70">
-        <v>573.3260933059652</v>
+        <v>573.3723055190163</v>
       </c>
       <c r="E70">
-        <v>385.576</v>
+        <v>401.933</v>
       </c>
       <c r="F70">
-        <v>1112.276</v>
+        <v>1128.633</v>
       </c>
       <c r="G70">
         <v>1059.6</v>
@@ -7027,28 +7027,28 @@
         <v>180.9</v>
       </c>
       <c r="M70">
-        <v>84.31052080000001</v>
+        <v>85.55038140000001</v>
       </c>
       <c r="N70">
-        <v>96.5894792</v>
+        <v>95.3496186</v>
       </c>
       <c r="O70">
-        <v>24.1473698</v>
+        <v>23.83740465</v>
       </c>
       <c r="P70">
-        <v>72.44210939999999</v>
+        <v>71.51221395</v>
       </c>
       <c r="Q70">
-        <v>106.5421094</v>
+        <v>105.61221395</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1798173449234022</v>
+        <v>0.1837237968741426</v>
       </c>
       <c r="T70">
-        <v>2.073205703341882</v>
+        <v>2.13363727261924</v>
       </c>
       <c r="U70">
         <v>0.07580000000000001</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.145639693403483</v>
+        <v>2.114543465962853</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.09618087703098421</v>
+        <v>0.09616220368647971</v>
       </c>
       <c r="C71">
-        <v>504.3393055190161</v>
+        <v>488.02852518242</v>
       </c>
       <c r="D71">
-        <v>573.3723055190163</v>
+        <v>573.4185251824204</v>
       </c>
       <c r="E71">
-        <v>401.933</v>
+        <v>418.2900000000002</v>
       </c>
       <c r="F71">
-        <v>1128.633</v>
+        <v>1144.99</v>
       </c>
       <c r="G71">
         <v>1059.6</v>
@@ -7109,28 +7109,28 @@
         <v>180.9</v>
       </c>
       <c r="M71">
-        <v>85.55038140000001</v>
+        <v>86.79024200000002</v>
       </c>
       <c r="N71">
-        <v>95.3496186</v>
+        <v>94.10975799999999</v>
       </c>
       <c r="O71">
-        <v>23.83740465</v>
+        <v>23.5274395</v>
       </c>
       <c r="P71">
-        <v>71.51221395</v>
+        <v>70.58231849999999</v>
       </c>
       <c r="Q71">
-        <v>105.61221395</v>
+        <v>104.6823185</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1837237968741426</v>
+        <v>0.1878906789549324</v>
       </c>
       <c r="T71">
-        <v>2.13363727261924</v>
+        <v>2.198097613181754</v>
       </c>
       <c r="U71">
         <v>0.07580000000000001</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.114543465962853</v>
+        <v>2.084335702163383</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.09616220368647971</v>
+        <v>0.09614353034197524</v>
       </c>
       <c r="C72">
-        <v>488.02852518242</v>
+        <v>471.7177522979782</v>
       </c>
       <c r="D72">
-        <v>573.4185251824204</v>
+        <v>573.4647522979786</v>
       </c>
       <c r="E72">
-        <v>418.2900000000002</v>
+        <v>434.6470000000002</v>
       </c>
       <c r="F72">
-        <v>1144.99</v>
+        <v>1161.347</v>
       </c>
       <c r="G72">
         <v>1059.6</v>
@@ -7191,28 +7191,28 @@
         <v>180.9</v>
       </c>
       <c r="M72">
-        <v>86.79024200000002</v>
+        <v>88.03010260000002</v>
       </c>
       <c r="N72">
-        <v>94.10975799999999</v>
+        <v>92.86989739999999</v>
       </c>
       <c r="O72">
-        <v>23.5274395</v>
+        <v>23.21747435</v>
       </c>
       <c r="P72">
-        <v>70.58231849999999</v>
+        <v>69.65242304999998</v>
       </c>
       <c r="Q72">
-        <v>104.6823185</v>
+        <v>103.75242305</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1878906789549324</v>
+        <v>0.1923449322137077</v>
       </c>
       <c r="T72">
-        <v>2.198097613181754</v>
+        <v>2.267003494472719</v>
       </c>
       <c r="U72">
         <v>0.07580000000000001</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.084335702163383</v>
+        <v>2.054978861287843</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.09614353034197523</v>
+        <v>0.09612485699747075</v>
       </c>
       <c r="C73">
-        <v>471.7177522979784</v>
+        <v>455.406986867494</v>
       </c>
       <c r="D73">
-        <v>573.4647522979786</v>
+        <v>573.5109868674939</v>
       </c>
       <c r="E73">
-        <v>434.6469999999999</v>
+        <v>451.0039999999999</v>
       </c>
       <c r="F73">
-        <v>1161.347</v>
+        <v>1177.704</v>
       </c>
       <c r="G73">
         <v>1059.6</v>
@@ -7273,28 +7273,28 @@
         <v>180.9</v>
       </c>
       <c r="M73">
-        <v>88.03010260000001</v>
+        <v>89.26996320000001</v>
       </c>
       <c r="N73">
-        <v>92.8698974</v>
+        <v>91.6300368</v>
       </c>
       <c r="O73">
-        <v>23.21747435</v>
+        <v>22.9075092</v>
       </c>
       <c r="P73">
-        <v>69.65242305</v>
+        <v>68.72252760000001</v>
       </c>
       <c r="Q73">
-        <v>103.75242305</v>
+        <v>102.8225276</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1923449322137077</v>
+        <v>0.1971173464195384</v>
       </c>
       <c r="T73">
-        <v>2.267003494472718</v>
+        <v>2.340831224427323</v>
       </c>
       <c r="U73">
         <v>0.07580000000000001</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.054978861287843</v>
+        <v>2.026437488214401</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.09612485699747075</v>
+        <v>0.1038806836529663</v>
       </c>
       <c r="C74">
-        <v>455.406986867494</v>
+        <v>420.4675302806829</v>
       </c>
       <c r="D74">
-        <v>573.5109868674939</v>
+        <v>554.928530280683</v>
       </c>
       <c r="E74">
-        <v>451.0039999999999</v>
+        <v>467.3609999999999</v>
       </c>
       <c r="F74">
-        <v>1177.704</v>
+        <v>1194.061</v>
       </c>
       <c r="G74">
         <v>1059.6</v>
@@ -7355,45 +7355,45 @@
         <v>180.9</v>
       </c>
       <c r="M74">
-        <v>89.26996320000001</v>
+        <v>107.46549</v>
       </c>
       <c r="N74">
-        <v>91.6300368</v>
+        <v>73.43451000000002</v>
       </c>
       <c r="O74">
-        <v>22.9075092</v>
+        <v>18.3586275</v>
       </c>
       <c r="P74">
-        <v>68.72252760000001</v>
+        <v>55.07588250000001</v>
       </c>
       <c r="Q74">
-        <v>102.8225276</v>
+        <v>89.17588250000001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1971173464195384</v>
+        <v>0.2022432727887639</v>
       </c>
       <c r="T74">
-        <v>2.340831224427323</v>
+        <v>2.420127675119305</v>
       </c>
       <c r="U74">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V74">
         <v>0.25</v>
       </c>
       <c r="W74">
-        <v>0.05685</v>
+        <v>0.0675</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y74">
-        <v>2.026437488214401</v>
+        <v>1.683331086100292</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1038806836529663</v>
+        <v>0.1039685103084618</v>
       </c>
       <c r="C75">
-        <v>420.4675302806829</v>
+        <v>403.9069960915515</v>
       </c>
       <c r="D75">
-        <v>554.928530280683</v>
+        <v>554.7249960915517</v>
       </c>
       <c r="E75">
-        <v>467.3609999999999</v>
+        <v>483.7180000000001</v>
       </c>
       <c r="F75">
-        <v>1194.061</v>
+        <v>1210.418</v>
       </c>
       <c r="G75">
         <v>1059.6</v>
@@ -7437,28 +7437,28 @@
         <v>180.9</v>
       </c>
       <c r="M75">
-        <v>107.46549</v>
+        <v>108.93762</v>
       </c>
       <c r="N75">
-        <v>73.43451000000002</v>
+        <v>71.96238</v>
       </c>
       <c r="O75">
-        <v>18.3586275</v>
+        <v>17.990595</v>
       </c>
       <c r="P75">
-        <v>55.07588250000001</v>
+        <v>53.971785</v>
       </c>
       <c r="Q75">
-        <v>89.17588250000001</v>
+        <v>88.07178500000001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2022432727887639</v>
+        <v>0.2077635011863914</v>
       </c>
       <c r="T75">
-        <v>2.420127675119305</v>
+        <v>2.505523852787594</v>
       </c>
       <c r="U75">
         <v>0.09</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>1.683331086100292</v>
+        <v>1.660583368720558</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1039685103084618</v>
+        <v>0.1040563369639573</v>
       </c>
       <c r="C76">
-        <v>403.9069960915515</v>
+        <v>387.3466111503874</v>
       </c>
       <c r="D76">
-        <v>554.7249960915517</v>
+        <v>554.5216111503876</v>
       </c>
       <c r="E76">
-        <v>483.7180000000001</v>
+        <v>500.075</v>
       </c>
       <c r="F76">
-        <v>1210.418</v>
+        <v>1226.775</v>
       </c>
       <c r="G76">
         <v>1059.6</v>
@@ -7519,28 +7519,28 @@
         <v>180.9</v>
       </c>
       <c r="M76">
-        <v>108.93762</v>
+        <v>110.40975</v>
       </c>
       <c r="N76">
-        <v>71.96238</v>
+        <v>70.49025</v>
       </c>
       <c r="O76">
-        <v>17.990595</v>
+        <v>17.6225625</v>
       </c>
       <c r="P76">
-        <v>53.971785</v>
+        <v>52.8676875</v>
       </c>
       <c r="Q76">
-        <v>88.07178500000001</v>
+        <v>86.96768750000001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2077635011863914</v>
+        <v>0.2137253478558292</v>
       </c>
       <c r="T76">
-        <v>2.505523852787594</v>
+        <v>2.597751724669346</v>
       </c>
       <c r="U76">
         <v>0.09</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>1.660583368720558</v>
+        <v>1.638442257137617</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1040563369639573</v>
+        <v>0.1041441636194528</v>
       </c>
       <c r="C77">
-        <v>387.3466111503874</v>
+        <v>370.7863752930898</v>
       </c>
       <c r="D77">
-        <v>554.5216111503876</v>
+        <v>554.31837529309</v>
       </c>
       <c r="E77">
-        <v>500.075</v>
+        <v>516.432</v>
       </c>
       <c r="F77">
-        <v>1226.775</v>
+        <v>1243.132</v>
       </c>
       <c r="G77">
         <v>1059.6</v>
@@ -7601,28 +7601,28 @@
         <v>180.9</v>
       </c>
       <c r="M77">
-        <v>110.40975</v>
+        <v>111.88188</v>
       </c>
       <c r="N77">
-        <v>70.49025</v>
+        <v>69.01812000000001</v>
       </c>
       <c r="O77">
-        <v>17.6225625</v>
+        <v>17.25453</v>
       </c>
       <c r="P77">
-        <v>52.8676875</v>
+        <v>51.76359000000001</v>
       </c>
       <c r="Q77">
-        <v>86.96768750000001</v>
+        <v>85.86359000000002</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2137253478558292</v>
+        <v>0.2201840150810534</v>
       </c>
       <c r="T77">
-        <v>2.597751724669346</v>
+        <v>2.697665252541244</v>
       </c>
       <c r="U77">
         <v>0.09</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>1.638442257137617</v>
+        <v>1.616883806385806</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1041441636194528</v>
+        <v>0.1042319902749483</v>
       </c>
       <c r="C78">
-        <v>370.7863752930898</v>
+        <v>354.2262883557978</v>
       </c>
       <c r="D78">
-        <v>554.31837529309</v>
+        <v>554.115288355798</v>
       </c>
       <c r="E78">
-        <v>516.432</v>
+        <v>532.789</v>
       </c>
       <c r="F78">
-        <v>1243.132</v>
+        <v>1259.489</v>
       </c>
       <c r="G78">
         <v>1059.6</v>
@@ -7683,28 +7683,28 @@
         <v>180.9</v>
       </c>
       <c r="M78">
-        <v>111.88188</v>
+        <v>113.35401</v>
       </c>
       <c r="N78">
-        <v>69.01812000000001</v>
+        <v>67.54599</v>
       </c>
       <c r="O78">
-        <v>17.25453</v>
+        <v>16.8864975</v>
       </c>
       <c r="P78">
-        <v>51.76359000000001</v>
+        <v>50.6594925</v>
       </c>
       <c r="Q78">
-        <v>85.86359000000002</v>
+        <v>84.75949249999999</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2201840150810534</v>
+        <v>0.2272043055432536</v>
       </c>
       <c r="T78">
-        <v>2.697665252541244</v>
+        <v>2.806266913271568</v>
       </c>
       <c r="U78">
         <v>0.09</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>1.616883806385806</v>
+        <v>1.595885315393783</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1042319902749483</v>
+        <v>0.1043198169304438</v>
       </c>
       <c r="C79">
-        <v>354.2262883557978</v>
+        <v>337.6663501748912</v>
       </c>
       <c r="D79">
-        <v>554.115288355798</v>
+        <v>553.9123501748912</v>
       </c>
       <c r="E79">
-        <v>532.789</v>
+        <v>549.146</v>
       </c>
       <c r="F79">
-        <v>1259.489</v>
+        <v>1275.846</v>
       </c>
       <c r="G79">
         <v>1059.6</v>
@@ -7765,28 +7765,28 @@
         <v>180.9</v>
       </c>
       <c r="M79">
-        <v>113.35401</v>
+        <v>114.82614</v>
       </c>
       <c r="N79">
-        <v>67.54599</v>
+        <v>66.07386000000001</v>
       </c>
       <c r="O79">
-        <v>16.8864975</v>
+        <v>16.518465</v>
       </c>
       <c r="P79">
-        <v>50.6594925</v>
+        <v>49.555395</v>
       </c>
       <c r="Q79">
-        <v>84.75949249999999</v>
+        <v>83.655395</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2272043055432536</v>
+        <v>0.2348628042292902</v>
       </c>
       <c r="T79">
-        <v>2.806266913271568</v>
+        <v>2.924741452250103</v>
       </c>
       <c r="U79">
         <v>0.09</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>1.595885315393783</v>
+        <v>1.575425247247709</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1043198169304438</v>
+        <v>0.1044076435859394</v>
       </c>
       <c r="C80">
-        <v>337.6663501748912</v>
+        <v>321.1065605869883</v>
       </c>
       <c r="D80">
-        <v>553.9123501748912</v>
+        <v>553.7095605869887</v>
       </c>
       <c r="E80">
-        <v>549.146</v>
+        <v>565.5030000000002</v>
       </c>
       <c r="F80">
-        <v>1275.846</v>
+        <v>1292.203</v>
       </c>
       <c r="G80">
         <v>1059.6</v>
@@ -7847,28 +7847,28 @@
         <v>180.9</v>
       </c>
       <c r="M80">
-        <v>114.82614</v>
+        <v>116.29827</v>
       </c>
       <c r="N80">
-        <v>66.07386000000001</v>
+        <v>64.60172999999999</v>
       </c>
       <c r="O80">
-        <v>16.518465</v>
+        <v>16.1504325</v>
       </c>
       <c r="P80">
-        <v>49.555395</v>
+        <v>48.4512975</v>
       </c>
       <c r="Q80">
-        <v>83.655395</v>
+        <v>82.5512975</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2348628042292902</v>
+        <v>0.2432506837425684</v>
       </c>
       <c r="T80">
-        <v>2.924741452250103</v>
+        <v>3.054499280655165</v>
       </c>
       <c r="U80">
         <v>0.09</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>1.575425247247709</v>
+        <v>1.555483155510396</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1044076435859394</v>
+        <v>0.1044954702414349</v>
       </c>
       <c r="C81">
-        <v>321.1065605869883</v>
+        <v>304.5469194289483</v>
       </c>
       <c r="D81">
-        <v>553.7095605869887</v>
+        <v>553.5069194289484</v>
       </c>
       <c r="E81">
-        <v>565.5030000000002</v>
+        <v>581.8600000000001</v>
       </c>
       <c r="F81">
-        <v>1292.203</v>
+        <v>1308.56</v>
       </c>
       <c r="G81">
         <v>1059.6</v>
@@ -7929,28 +7929,28 @@
         <v>180.9</v>
       </c>
       <c r="M81">
-        <v>116.29827</v>
+        <v>117.7704</v>
       </c>
       <c r="N81">
-        <v>64.60172999999999</v>
+        <v>63.1296</v>
       </c>
       <c r="O81">
-        <v>16.1504325</v>
+        <v>15.7824</v>
       </c>
       <c r="P81">
-        <v>48.4512975</v>
+        <v>47.3472</v>
       </c>
       <c r="Q81">
-        <v>82.5512975</v>
+        <v>81.44720000000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2432506837425684</v>
+        <v>0.2524773512071744</v>
       </c>
       <c r="T81">
-        <v>3.054499280655165</v>
+        <v>3.197232891900734</v>
       </c>
       <c r="U81">
         <v>0.09</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>1.555483155510396</v>
+        <v>1.536039616066516</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1044954702414349</v>
+        <v>0.1045832968969304</v>
       </c>
       <c r="C82">
-        <v>304.5469194289483</v>
+        <v>287.9874265378671</v>
       </c>
       <c r="D82">
-        <v>553.5069194289484</v>
+        <v>553.3044265378674</v>
       </c>
       <c r="E82">
-        <v>581.8600000000001</v>
+        <v>598.2170000000001</v>
       </c>
       <c r="F82">
-        <v>1308.56</v>
+        <v>1324.917</v>
       </c>
       <c r="G82">
         <v>1059.6</v>
@@ -8011,28 +8011,28 @@
         <v>180.9</v>
       </c>
       <c r="M82">
-        <v>117.7704</v>
+        <v>119.24253</v>
       </c>
       <c r="N82">
-        <v>63.1296</v>
+        <v>61.65747</v>
       </c>
       <c r="O82">
-        <v>15.7824</v>
+        <v>15.4143675</v>
       </c>
       <c r="P82">
-        <v>47.3472</v>
+        <v>46.24310250000001</v>
       </c>
       <c r="Q82">
-        <v>81.44720000000001</v>
+        <v>80.34310250000001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2524773512071744</v>
+        <v>0.2626752468259494</v>
       </c>
       <c r="T82">
-        <v>3.197232891900734</v>
+        <v>3.354991093803731</v>
       </c>
       <c r="U82">
         <v>0.09</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>1.536039616066516</v>
+        <v>1.517076164016312</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1045832968969304</v>
+        <v>0.1429090804592543</v>
       </c>
       <c r="C83">
-        <v>287.9874265378671</v>
+        <v>195.4591829876629</v>
       </c>
       <c r="D83">
-        <v>553.3044265378674</v>
+        <v>477.133182987663</v>
       </c>
       <c r="E83">
-        <v>598.2170000000001</v>
+        <v>614.5740000000001</v>
       </c>
       <c r="F83">
-        <v>1324.917</v>
+        <v>1341.274</v>
       </c>
       <c r="G83">
         <v>1059.6</v>
@@ -8093,45 +8093,45 @@
         <v>180.9</v>
       </c>
       <c r="M83">
-        <v>119.24253</v>
+        <v>196.8990232</v>
       </c>
       <c r="N83">
-        <v>61.65747</v>
+        <v>-15.99902320000004</v>
       </c>
       <c r="O83">
-        <v>15.4143675</v>
+        <v>-3.99975580000001</v>
       </c>
       <c r="P83">
-        <v>46.24310250000001</v>
+        <v>-11.99926740000003</v>
       </c>
       <c r="Q83">
-        <v>80.34310250000001</v>
+        <v>22.10073259999997</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2626752468259494</v>
+        <v>0.2787877419358422</v>
       </c>
       <c r="T83">
-        <v>3.354991093803731</v>
+        <v>3.604246268766272</v>
       </c>
       <c r="U83">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V83">
-        <v>0.25</v>
+        <v>0.2296862587990736</v>
       </c>
       <c r="W83">
-        <v>0.0675</v>
+        <v>0.113082057208296</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y83">
-        <v>1.517076164016312</v>
+        <v>0.9187450351962942</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1429090804592543</v>
+        <v>0.1439190804592543</v>
       </c>
       <c r="C84">
-        <v>195.4591829876629</v>
+        <v>177.3774410607775</v>
       </c>
       <c r="D84">
-        <v>477.133182987663</v>
+        <v>475.4084410607778</v>
       </c>
       <c r="E84">
-        <v>614.5740000000001</v>
+        <v>630.931</v>
       </c>
       <c r="F84">
-        <v>1341.274</v>
+        <v>1357.631</v>
       </c>
       <c r="G84">
         <v>1059.6</v>
@@ -8175,37 +8175,37 @@
         <v>180.9</v>
       </c>
       <c r="M84">
-        <v>196.8990232</v>
+        <v>199.3002308</v>
       </c>
       <c r="N84">
-        <v>-15.99902320000004</v>
+        <v>-18.40023080000003</v>
       </c>
       <c r="O84">
-        <v>-3.99975580000001</v>
+        <v>-4.600057700000008</v>
       </c>
       <c r="P84">
-        <v>-11.99926740000003</v>
+        <v>-13.80017310000002</v>
       </c>
       <c r="Q84">
-        <v>22.10073259999997</v>
+        <v>20.29982689999998</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2787877419358422</v>
+        <v>0.2924929032261859</v>
       </c>
       <c r="T84">
-        <v>3.604246268766272</v>
+        <v>3.816260755164288</v>
       </c>
       <c r="U84">
         <v>0.1468</v>
       </c>
       <c r="V84">
-        <v>0.2296862587990736</v>
+        <v>0.2269189544761932</v>
       </c>
       <c r="W84">
-        <v>0.113082057208296</v>
+        <v>0.1134882974828949</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.9187450351962942</v>
+        <v>0.9076758179047727</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1439190804592543</v>
+        <v>0.1449290804592543</v>
       </c>
       <c r="C85">
-        <v>177.3774410607775</v>
+        <v>159.3081234232675</v>
       </c>
       <c r="D85">
-        <v>475.4084410607778</v>
+        <v>473.6961234232677</v>
       </c>
       <c r="E85">
-        <v>630.931</v>
+        <v>647.288</v>
       </c>
       <c r="F85">
-        <v>1357.631</v>
+        <v>1373.988</v>
       </c>
       <c r="G85">
         <v>1059.6</v>
@@ -8257,37 +8257,37 @@
         <v>180.9</v>
       </c>
       <c r="M85">
-        <v>199.3002308</v>
+        <v>201.7014384</v>
       </c>
       <c r="N85">
-        <v>-18.40023080000003</v>
+        <v>-20.80143840000002</v>
       </c>
       <c r="O85">
-        <v>-4.600057700000008</v>
+        <v>-5.200359600000006</v>
       </c>
       <c r="P85">
-        <v>-13.80017310000002</v>
+        <v>-15.60107880000002</v>
       </c>
       <c r="Q85">
-        <v>20.29982689999998</v>
+        <v>18.49892119999998</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2924929032261859</v>
+        <v>0.3079112096778226</v>
       </c>
       <c r="T85">
-        <v>3.816260755164288</v>
+        <v>4.054777052362057</v>
       </c>
       <c r="U85">
         <v>0.1468</v>
       </c>
       <c r="V85">
-        <v>0.2269189544761932</v>
+        <v>0.2242175383514766</v>
       </c>
       <c r="W85">
-        <v>0.1134882974828949</v>
+        <v>0.1138848653700032</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.9076758179047727</v>
+        <v>0.8968701534059064</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1449290804592543</v>
+        <v>0.1459390804592543</v>
       </c>
       <c r="C86">
-        <v>159.3081234232675</v>
+        <v>141.2510963081809</v>
       </c>
       <c r="D86">
-        <v>473.6961234232677</v>
+        <v>471.9960963081811</v>
       </c>
       <c r="E86">
-        <v>647.288</v>
+        <v>663.645</v>
       </c>
       <c r="F86">
-        <v>1373.988</v>
+        <v>1390.345</v>
       </c>
       <c r="G86">
         <v>1059.6</v>
@@ -8339,37 +8339,37 @@
         <v>180.9</v>
       </c>
       <c r="M86">
-        <v>201.7014384</v>
+        <v>204.102646</v>
       </c>
       <c r="N86">
-        <v>-20.80143840000002</v>
+        <v>-23.20264600000002</v>
       </c>
       <c r="O86">
-        <v>-5.200359600000006</v>
+        <v>-5.800661500000004</v>
       </c>
       <c r="P86">
-        <v>-15.60107880000002</v>
+        <v>-17.40198450000001</v>
       </c>
       <c r="Q86">
-        <v>18.49892119999998</v>
+        <v>16.69801549999999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3079112096778224</v>
+        <v>0.3253852903230106</v>
       </c>
       <c r="T86">
-        <v>4.054777052362054</v>
+        <v>4.325095522519525</v>
       </c>
       <c r="U86">
         <v>0.1468</v>
       </c>
       <c r="V86">
-        <v>0.2242175383514766</v>
+        <v>0.2215796849591063</v>
       </c>
       <c r="W86">
-        <v>0.1138848653700032</v>
+        <v>0.1142721022480032</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.8968701534059064</v>
+        <v>0.8863187398364252</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1459390804592543</v>
+        <v>0.1469490804592543</v>
       </c>
       <c r="C87">
-        <v>141.2510963081809</v>
+        <v>123.2062278619803</v>
       </c>
       <c r="D87">
-        <v>471.9960963081811</v>
+        <v>470.3082278619804</v>
       </c>
       <c r="E87">
-        <v>663.645</v>
+        <v>680.002</v>
       </c>
       <c r="F87">
-        <v>1390.345</v>
+        <v>1406.702</v>
       </c>
       <c r="G87">
         <v>1059.6</v>
@@ -8421,37 +8421,37 @@
         <v>180.9</v>
       </c>
       <c r="M87">
-        <v>204.102646</v>
+        <v>206.5038536</v>
       </c>
       <c r="N87">
-        <v>-23.20264600000002</v>
+        <v>-25.60385360000001</v>
       </c>
       <c r="O87">
-        <v>-5.800661500000004</v>
+        <v>-6.400963400000002</v>
       </c>
       <c r="P87">
-        <v>-17.40198450000001</v>
+        <v>-19.20289020000001</v>
       </c>
       <c r="Q87">
-        <v>16.69801549999999</v>
+        <v>14.8971098</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3253852903230106</v>
+        <v>0.3453556682032256</v>
       </c>
       <c r="T87">
-        <v>4.325095522519525</v>
+        <v>4.634030916985205</v>
       </c>
       <c r="U87">
         <v>0.1468</v>
       </c>
       <c r="V87">
-        <v>0.2215796849591063</v>
+        <v>0.2190031769944655</v>
       </c>
       <c r="W87">
-        <v>0.1142721022480032</v>
+        <v>0.1146503336172125</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.8863187398364252</v>
+        <v>0.8760127079778621</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1469490804592543</v>
+        <v>0.1479590804592543</v>
       </c>
       <c r="C88">
-        <v>123.2062278619803</v>
+        <v>105.1733881104522</v>
       </c>
       <c r="D88">
-        <v>470.3082278619804</v>
+        <v>468.6323881104523</v>
       </c>
       <c r="E88">
-        <v>680.002</v>
+        <v>696.3589999999999</v>
       </c>
       <c r="F88">
-        <v>1406.702</v>
+        <v>1423.059</v>
       </c>
       <c r="G88">
         <v>1059.6</v>
@@ -8503,37 +8503,37 @@
         <v>180.9</v>
       </c>
       <c r="M88">
-        <v>206.5038536</v>
+        <v>208.9050612</v>
       </c>
       <c r="N88">
-        <v>-25.60385360000001</v>
+        <v>-28.0050612</v>
       </c>
       <c r="O88">
-        <v>-6.400963400000002</v>
+        <v>-7.0012653</v>
       </c>
       <c r="P88">
-        <v>-19.20289020000001</v>
+        <v>-21.0037959</v>
       </c>
       <c r="Q88">
-        <v>14.8971098</v>
+        <v>13.0962041</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3453556682032256</v>
+        <v>0.368398411911166</v>
       </c>
       <c r="T88">
-        <v>4.634030916985205</v>
+        <v>4.990494833676374</v>
       </c>
       <c r="U88">
         <v>0.1468</v>
       </c>
       <c r="V88">
-        <v>0.2190031769944655</v>
+        <v>0.2164858990979774</v>
       </c>
       <c r="W88">
-        <v>0.1146503336172125</v>
+        <v>0.1150198700124169</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.8760127079778621</v>
+        <v>0.8659435963919098</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1479590804592543</v>
+        <v>0.1489690804592543</v>
       </c>
       <c r="C89">
-        <v>105.1733881104522</v>
+        <v>87.15244892534383</v>
       </c>
       <c r="D89">
-        <v>468.6323881104523</v>
+        <v>466.9684489253438</v>
       </c>
       <c r="E89">
-        <v>696.3589999999999</v>
+        <v>712.7159999999999</v>
       </c>
       <c r="F89">
-        <v>1423.059</v>
+        <v>1439.416</v>
       </c>
       <c r="G89">
         <v>1059.6</v>
@@ -8585,37 +8585,37 @@
         <v>180.9</v>
       </c>
       <c r="M89">
-        <v>208.9050612</v>
+        <v>211.3062688</v>
       </c>
       <c r="N89">
-        <v>-28.0050612</v>
+        <v>-30.40626879999999</v>
       </c>
       <c r="O89">
-        <v>-7.0012653</v>
+        <v>-7.601567199999998</v>
       </c>
       <c r="P89">
-        <v>-21.0037959</v>
+        <v>-22.80470159999999</v>
       </c>
       <c r="Q89">
-        <v>13.0962041</v>
+        <v>11.29529840000001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.368398411911166</v>
+        <v>0.3952816129037632</v>
       </c>
       <c r="T89">
-        <v>4.990494833676374</v>
+        <v>5.406369403149407</v>
       </c>
       <c r="U89">
         <v>0.1468</v>
       </c>
       <c r="V89">
-        <v>0.2164858990979774</v>
+        <v>0.2140258320627731</v>
       </c>
       <c r="W89">
-        <v>0.1150198700124169</v>
+        <v>0.1153810078531849</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.8659435963919098</v>
+        <v>0.8561033282510926</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1489690804592543</v>
+        <v>0.1499790804592543</v>
       </c>
       <c r="C90">
-        <v>87.15244892534383</v>
+        <v>69.14328399170608</v>
       </c>
       <c r="D90">
-        <v>466.9684489253438</v>
+        <v>465.3162839917063</v>
       </c>
       <c r="E90">
-        <v>712.7159999999999</v>
+        <v>729.0730000000001</v>
       </c>
       <c r="F90">
-        <v>1439.416</v>
+        <v>1455.773</v>
       </c>
       <c r="G90">
         <v>1059.6</v>
@@ -8667,37 +8667,37 @@
         <v>180.9</v>
       </c>
       <c r="M90">
-        <v>211.3062688</v>
+        <v>213.7074764</v>
       </c>
       <c r="N90">
-        <v>-30.40626879999999</v>
+        <v>-32.80747640000004</v>
       </c>
       <c r="O90">
-        <v>-7.601567199999998</v>
+        <v>-8.20186910000001</v>
       </c>
       <c r="P90">
-        <v>-22.80470159999999</v>
+        <v>-24.60560730000003</v>
       </c>
       <c r="Q90">
-        <v>11.29529840000001</v>
+        <v>9.49439269999997</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3952816129037632</v>
+        <v>0.4270526686222872</v>
       </c>
       <c r="T90">
-        <v>5.406369403149407</v>
+        <v>5.897857530708444</v>
       </c>
       <c r="U90">
         <v>0.1468</v>
       </c>
       <c r="V90">
-        <v>0.2140258320627731</v>
+        <v>0.2116210474328543</v>
       </c>
       <c r="W90">
-        <v>0.1153810078531849</v>
+        <v>0.115734030236857</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.8561033282510926</v>
+        <v>0.8464841897314173</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1499790804592543</v>
+        <v>0.1509890804592543</v>
       </c>
       <c r="C91">
-        <v>69.14328399170608</v>
+        <v>51.14576877593072</v>
       </c>
       <c r="D91">
-        <v>465.3162839917063</v>
+        <v>463.675768775931</v>
       </c>
       <c r="E91">
-        <v>729.0730000000001</v>
+        <v>745.4300000000001</v>
       </c>
       <c r="F91">
-        <v>1455.773</v>
+        <v>1472.13</v>
       </c>
       <c r="G91">
         <v>1059.6</v>
@@ -8749,37 +8749,37 @@
         <v>180.9</v>
       </c>
       <c r="M91">
-        <v>213.7074764</v>
+        <v>216.108684</v>
       </c>
       <c r="N91">
-        <v>-32.80747640000004</v>
+        <v>-35.20868400000003</v>
       </c>
       <c r="O91">
-        <v>-8.20186910000001</v>
+        <v>-8.802171000000008</v>
       </c>
       <c r="P91">
-        <v>-24.60560730000003</v>
+        <v>-26.40651300000003</v>
       </c>
       <c r="Q91">
-        <v>9.49439269999997</v>
+        <v>7.693486999999976</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4270526686222872</v>
+        <v>0.465177935484516</v>
       </c>
       <c r="T91">
-        <v>5.897857530708444</v>
+        <v>6.487643283779289</v>
       </c>
       <c r="U91">
         <v>0.1468</v>
       </c>
       <c r="V91">
-        <v>0.2116210474328543</v>
+        <v>0.2092697024613782</v>
       </c>
       <c r="W91">
-        <v>0.115734030236857</v>
+        <v>0.1160792076786697</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.8464841897314173</v>
+        <v>0.8370788098455126</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1509890804592543</v>
+        <v>0.1519990804592543</v>
       </c>
       <c r="C92">
-        <v>51.14576877593072</v>
+        <v>33.15978049445766</v>
       </c>
       <c r="D92">
-        <v>463.675768775931</v>
+        <v>462.0467804944579</v>
       </c>
       <c r="E92">
-        <v>745.4300000000001</v>
+        <v>761.787</v>
       </c>
       <c r="F92">
-        <v>1472.13</v>
+        <v>1488.487</v>
       </c>
       <c r="G92">
         <v>1059.6</v>
@@ -8831,37 +8831,37 @@
         <v>180.9</v>
       </c>
       <c r="M92">
-        <v>216.108684</v>
+        <v>218.5098916</v>
       </c>
       <c r="N92">
-        <v>-35.20868400000003</v>
+        <v>-37.60989160000003</v>
       </c>
       <c r="O92">
-        <v>-8.802171000000008</v>
+        <v>-9.402472900000006</v>
       </c>
       <c r="P92">
-        <v>-26.40651300000003</v>
+        <v>-28.20741870000002</v>
       </c>
       <c r="Q92">
-        <v>7.693486999999976</v>
+        <v>5.892581299999982</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.465177935484516</v>
+        <v>0.5117754838716844</v>
       </c>
       <c r="T92">
-        <v>6.487643283779289</v>
+        <v>7.208492537532543</v>
       </c>
       <c r="U92">
         <v>0.1468</v>
       </c>
       <c r="V92">
-        <v>0.2092697024613782</v>
+        <v>0.206970035401363</v>
       </c>
       <c r="W92">
-        <v>0.1160792076786697</v>
+        <v>0.1164167988030799</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.8370788098455126</v>
+        <v>0.8278801416054521</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1519990804592543</v>
+        <v>0.1530090804592543</v>
       </c>
       <c r="C93">
-        <v>33.15978049445766</v>
+        <v>15.18519808314159</v>
       </c>
       <c r="D93">
-        <v>462.0467804944579</v>
+        <v>460.4291980831417</v>
       </c>
       <c r="E93">
-        <v>761.787</v>
+        <v>778.144</v>
       </c>
       <c r="F93">
-        <v>1488.487</v>
+        <v>1504.844</v>
       </c>
       <c r="G93">
         <v>1059.6</v>
@@ -8913,37 +8913,37 @@
         <v>180.9</v>
       </c>
       <c r="M93">
-        <v>218.5098916</v>
+        <v>220.9110992</v>
       </c>
       <c r="N93">
-        <v>-37.60989160000003</v>
+        <v>-40.01109920000002</v>
       </c>
       <c r="O93">
-        <v>-9.402472900000006</v>
+        <v>-10.0027748</v>
       </c>
       <c r="P93">
-        <v>-28.20741870000002</v>
+        <v>-30.00832440000001</v>
       </c>
       <c r="Q93">
-        <v>5.892581299999982</v>
+        <v>4.091675599999988</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5117754838716844</v>
+        <v>0.5700224193556451</v>
       </c>
       <c r="T93">
-        <v>7.208492537532543</v>
+        <v>8.109554104724115</v>
       </c>
       <c r="U93">
         <v>0.1468</v>
       </c>
       <c r="V93">
-        <v>0.206970035401363</v>
+        <v>0.2047203611035221</v>
       </c>
       <c r="W93">
-        <v>0.1164167988030799</v>
+        <v>0.116747050990003</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.8278801416054521</v>
+        <v>0.8188814444140885</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1530090804592543</v>
+        <v>0.1540190804592543</v>
       </c>
       <c r="C94">
-        <v>15.18519808314159</v>
+        <v>-2.778097832740968</v>
       </c>
       <c r="D94">
-        <v>460.4291980831417</v>
+        <v>458.8229021672593</v>
       </c>
       <c r="E94">
-        <v>778.144</v>
+        <v>794.501</v>
       </c>
       <c r="F94">
-        <v>1504.844</v>
+        <v>1521.201</v>
       </c>
       <c r="G94">
         <v>1059.6</v>
@@ -8995,37 +8995,37 @@
         <v>180.9</v>
       </c>
       <c r="M94">
-        <v>220.9110992</v>
+        <v>223.3123068</v>
       </c>
       <c r="N94">
-        <v>-40.01109920000002</v>
+        <v>-42.41230680000001</v>
       </c>
       <c r="O94">
-        <v>-10.0027748</v>
+        <v>-10.6030767</v>
       </c>
       <c r="P94">
-        <v>-30.00832440000001</v>
+        <v>-31.80923010000001</v>
       </c>
       <c r="Q94">
-        <v>4.091675599999988</v>
+        <v>2.290769899999994</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5700224193556451</v>
+        <v>0.6449113364064516</v>
       </c>
       <c r="T94">
-        <v>8.109554104724115</v>
+        <v>9.268061833970417</v>
       </c>
       <c r="U94">
         <v>0.1468</v>
       </c>
       <c r="V94">
-        <v>0.2047203611035221</v>
+        <v>0.2025190668981079</v>
       </c>
       <c r="W94">
-        <v>0.116747050990003</v>
+        <v>0.1170702009793578</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.8188814444140885</v>
+        <v>0.8100762675924317</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1540190804592543</v>
+        <v>0.1550290804592543</v>
       </c>
       <c r="C95">
-        <v>-2.778097832740968</v>
+        <v>-20.73022496785711</v>
       </c>
       <c r="D95">
-        <v>458.8229021672593</v>
+        <v>457.2277750321433</v>
       </c>
       <c r="E95">
-        <v>794.501</v>
+        <v>810.8580000000002</v>
       </c>
       <c r="F95">
-        <v>1521.201</v>
+        <v>1537.558</v>
       </c>
       <c r="G95">
         <v>1059.6</v>
@@ -9077,37 +9077,37 @@
         <v>180.9</v>
       </c>
       <c r="M95">
-        <v>223.3123068</v>
+        <v>225.7135144000001</v>
       </c>
       <c r="N95">
-        <v>-42.41230680000001</v>
+        <v>-44.81351440000006</v>
       </c>
       <c r="O95">
-        <v>-10.6030767</v>
+        <v>-11.20337860000001</v>
       </c>
       <c r="P95">
-        <v>-31.80923010000001</v>
+        <v>-33.61013580000004</v>
       </c>
       <c r="Q95">
-        <v>2.290769899999994</v>
+        <v>0.4898641999999569</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6449113364064516</v>
+        <v>0.7447632258075271</v>
       </c>
       <c r="T95">
-        <v>9.268061833970417</v>
+        <v>10.81273880629882</v>
       </c>
       <c r="U95">
         <v>0.1468</v>
       </c>
       <c r="V95">
-        <v>0.2025190668981079</v>
+        <v>0.2003646087396174</v>
       </c>
       <c r="W95">
-        <v>0.1170702009793578</v>
+        <v>0.1173864754370242</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.8100762675924317</v>
+        <v>0.8014584349584695</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1550290804592543</v>
+        <v>0.2099561292126431</v>
       </c>
       <c r="C96">
-        <v>-20.73022496785711</v>
+        <v>-109.7884090392222</v>
       </c>
       <c r="D96">
-        <v>457.2277750321433</v>
+        <v>384.5265909607781</v>
       </c>
       <c r="E96">
-        <v>810.8580000000002</v>
+        <v>827.2150000000001</v>
       </c>
       <c r="F96">
-        <v>1537.558</v>
+        <v>1553.915</v>
       </c>
       <c r="G96">
         <v>1059.6</v>
@@ -9159,45 +9159,45 @@
         <v>180.9</v>
       </c>
       <c r="M96">
-        <v>225.7135144000001</v>
+        <v>312.0261320000001</v>
       </c>
       <c r="N96">
-        <v>-44.81351440000006</v>
+        <v>-131.1261320000001</v>
       </c>
       <c r="O96">
-        <v>-11.20337860000001</v>
+        <v>-32.78153300000002</v>
       </c>
       <c r="P96">
-        <v>-33.61013580000004</v>
+        <v>-98.34459900000004</v>
       </c>
       <c r="Q96">
-        <v>0.4898641999999569</v>
+        <v>-64.24459900000005</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7447632258075271</v>
+        <v>0.9368968460368087</v>
       </c>
       <c r="T96">
-        <v>10.81273880629882</v>
+        <v>13.78498480543228</v>
       </c>
       <c r="U96">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.2003646087396174</v>
+        <v>0.1449397834409587</v>
       </c>
       <c r="W96">
-        <v>0.1173864754370242</v>
+        <v>0.1716960914850555</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y96">
-        <v>0.8014584349584695</v>
+        <v>0.5797591337638348</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2099561292126431</v>
+        <v>0.2115061292126431</v>
       </c>
       <c r="C97">
-        <v>-109.7884090392222</v>
+        <v>-127.8630657800747</v>
       </c>
       <c r="D97">
-        <v>384.5265909607781</v>
+        <v>382.8089342199254</v>
       </c>
       <c r="E97">
-        <v>827.2150000000001</v>
+        <v>843.5720000000001</v>
       </c>
       <c r="F97">
-        <v>1553.915</v>
+        <v>1570.272</v>
       </c>
       <c r="G97">
         <v>1059.6</v>
@@ -9241,37 +9241,37 @@
         <v>180.9</v>
       </c>
       <c r="M97">
-        <v>312.0261320000001</v>
+        <v>315.3106176000001</v>
       </c>
       <c r="N97">
-        <v>-131.1261320000001</v>
+        <v>-134.4106176000001</v>
       </c>
       <c r="O97">
-        <v>-32.78153300000002</v>
+        <v>-33.60265440000001</v>
       </c>
       <c r="P97">
-        <v>-98.34459900000004</v>
+        <v>-100.8079632</v>
       </c>
       <c r="Q97">
-        <v>-64.24459900000005</v>
+        <v>-66.70796320000005</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.9368968460368087</v>
+        <v>1.159671057546012</v>
       </c>
       <c r="T97">
-        <v>13.78498480543228</v>
+        <v>17.23123100679035</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.1449397834409587</v>
+        <v>0.1434299940301154</v>
       </c>
       <c r="W97">
-        <v>0.1716960914850555</v>
+        <v>0.1719992571987528</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.5797591337638348</v>
+        <v>0.5737199761204614</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2115061292126431</v>
+        <v>0.2130561292126431</v>
       </c>
       <c r="C98">
-        <v>-127.8630657800745</v>
+        <v>-145.9224454277564</v>
       </c>
       <c r="D98">
-        <v>382.8089342199254</v>
+        <v>381.1065545722436</v>
       </c>
       <c r="E98">
-        <v>843.5719999999999</v>
+        <v>859.9289999999999</v>
       </c>
       <c r="F98">
-        <v>1570.272</v>
+        <v>1586.629</v>
       </c>
       <c r="G98">
         <v>1059.6</v>
@@ -9323,37 +9323,37 @@
         <v>180.9</v>
       </c>
       <c r="M98">
-        <v>315.3106176</v>
+        <v>318.5951032</v>
       </c>
       <c r="N98">
-        <v>-134.4106176</v>
+        <v>-137.6951032</v>
       </c>
       <c r="O98">
-        <v>-33.6026544</v>
+        <v>-34.42377579999999</v>
       </c>
       <c r="P98">
-        <v>-100.8079632</v>
+        <v>-103.2713274</v>
       </c>
       <c r="Q98">
-        <v>-66.70796319999999</v>
+        <v>-69.1713274</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.159671057546009</v>
+        <v>1.530961410061344</v>
       </c>
       <c r="T98">
-        <v>17.23123100679031</v>
+        <v>22.9749746757204</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.1434299940301154</v>
+        <v>0.1419513342978462</v>
       </c>
       <c r="W98">
-        <v>0.1719992571987528</v>
+        <v>0.1722961720729925</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.5737199761204617</v>
+        <v>0.5678053371913847</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2130561292126431</v>
+        <v>0.2146061292126431</v>
       </c>
       <c r="C99">
-        <v>-145.9224454277564</v>
+        <v>-163.9667508949901</v>
       </c>
       <c r="D99">
-        <v>381.1065545722436</v>
+        <v>379.4192491050101</v>
       </c>
       <c r="E99">
-        <v>859.9289999999999</v>
+        <v>876.2860000000001</v>
       </c>
       <c r="F99">
-        <v>1586.629</v>
+        <v>1602.986</v>
       </c>
       <c r="G99">
         <v>1059.6</v>
@@ -9405,37 +9405,37 @@
         <v>180.9</v>
       </c>
       <c r="M99">
-        <v>318.5951032</v>
+        <v>321.8795888</v>
       </c>
       <c r="N99">
-        <v>-137.6951032</v>
+        <v>-140.9795888</v>
       </c>
       <c r="O99">
-        <v>-34.42377579999999</v>
+        <v>-35.2448972</v>
       </c>
       <c r="P99">
-        <v>-103.2713274</v>
+        <v>-105.7346916</v>
       </c>
       <c r="Q99">
-        <v>-69.1713274</v>
+        <v>-71.63469160000002</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.530961410061344</v>
+        <v>2.273542115092017</v>
       </c>
       <c r="T99">
-        <v>22.9749746757204</v>
+        <v>34.46246201358061</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.1419513342978462</v>
+        <v>0.1405028512948069</v>
       </c>
       <c r="W99">
-        <v>0.1722961720729925</v>
+        <v>0.1725870274600028</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.5678053371913847</v>
+        <v>0.5620114051792277</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2146061292126431</v>
+        <v>0.2161561292126431</v>
       </c>
       <c r="C100">
-        <v>-163.9667508949901</v>
+        <v>-181.9961815168463</v>
       </c>
       <c r="D100">
-        <v>379.4192491050101</v>
+        <v>377.7468184831539</v>
       </c>
       <c r="E100">
-        <v>876.2860000000001</v>
+        <v>892.643</v>
       </c>
       <c r="F100">
-        <v>1602.986</v>
+        <v>1619.343</v>
       </c>
       <c r="G100">
         <v>1059.6</v>
@@ -9487,37 +9487,37 @@
         <v>180.9</v>
       </c>
       <c r="M100">
-        <v>321.8795888</v>
+        <v>325.1640744</v>
       </c>
       <c r="N100">
-        <v>-140.9795888</v>
+        <v>-144.2640744</v>
       </c>
       <c r="O100">
-        <v>-35.2448972</v>
+        <v>-36.0660186</v>
       </c>
       <c r="P100">
-        <v>-105.7346916</v>
+        <v>-108.1980558</v>
       </c>
       <c r="Q100">
-        <v>-71.63469160000002</v>
+        <v>-74.0980558</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.273542115092017</v>
+        <v>4.501284230184034</v>
       </c>
       <c r="T100">
-        <v>34.46246201358061</v>
+        <v>68.92492402716123</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.1405028512948069</v>
+        <v>0.1390836305746574</v>
       </c>
       <c r="W100">
-        <v>0.1725870274600028</v>
+        <v>0.1728720069806088</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.5620114051792277</v>
+        <v>0.5563345222986295</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2161561292126431</v>
-      </c>
-      <c r="C101">
-        <v>-181.9961815168463</v>
-      </c>
-      <c r="D101">
-        <v>377.7468184831539</v>
-      </c>
-      <c r="E101">
-        <v>892.643</v>
-      </c>
-      <c r="F101">
-        <v>1619.343</v>
-      </c>
-      <c r="G101">
-        <v>1059.6</v>
-      </c>
-      <c r="H101">
-        <v>909</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>215</v>
-      </c>
-      <c r="K101">
-        <v>34.1</v>
-      </c>
-      <c r="L101">
-        <v>180.9</v>
-      </c>
-      <c r="M101">
-        <v>325.1640744</v>
-      </c>
-      <c r="N101">
-        <v>-144.2640744</v>
-      </c>
-      <c r="O101">
-        <v>-36.0660186</v>
-      </c>
-      <c r="P101">
-        <v>-108.1980558</v>
-      </c>
-      <c r="Q101">
-        <v>-74.0980558</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.501284230184034</v>
-      </c>
-      <c r="T101">
-        <v>68.92492402716123</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.1390836305746574</v>
-      </c>
-      <c r="W101">
-        <v>0.1728720069806088</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.5563345222986295</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
